--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A65873-0AFB-4E43-A135-97B53A7D8603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -12,7 +18,18 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -46,14 +63,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,345 +73,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -408,327 +96,38 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
-    <cellStyle name="入力" xfId="2" builtinId="20"/>
-    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
-    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
-    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
-    <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
-    <cellStyle name="良い" xfId="13" builtinId="26"/>
-    <cellStyle name="警告文" xfId="14" builtinId="11"/>
-    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
-    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
-    <cellStyle name="説明文" xfId="17" builtinId="53"/>
-    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
-    <cellStyle name="出力" xfId="19" builtinId="21"/>
-    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
-    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
-    <cellStyle name="計算" xfId="22" builtinId="22"/>
-    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
-    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
-    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
-    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
-    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
-    <cellStyle name="集計" xfId="28" builtinId="25"/>
-    <cellStyle name="悪い" xfId="29" builtinId="27"/>
-    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
-    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
-    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
-    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
-    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
-    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
-    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
-    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
-    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
-    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
-    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
-    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
-    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
-    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
-    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
-    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
-    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Enemies"/>
@@ -755,7 +154,7 @@
             <v>1</v>
           </cell>
           <cell r="B2" t="str">
-            <v>スライム</v>
+            <v>ネレイドジェム</v>
           </cell>
         </row>
         <row r="3">
@@ -763,7 +162,7 @@
             <v>2</v>
           </cell>
           <cell r="B3" t="str">
-            <v>バット</v>
+            <v>カースド</v>
           </cell>
         </row>
         <row r="4">
@@ -771,7 +170,7 @@
             <v>3</v>
           </cell>
           <cell r="B4" t="str">
-            <v>ホーネット</v>
+            <v>ビー</v>
           </cell>
         </row>
         <row r="5">
@@ -779,7 +178,7 @@
             <v>4</v>
           </cell>
           <cell r="B5" t="str">
-            <v>スパイダー</v>
+            <v>ウルフ</v>
           </cell>
         </row>
         <row r="6">
@@ -787,7 +186,7 @@
             <v>5</v>
           </cell>
           <cell r="B6" t="str">
-            <v>ビッグラット</v>
+            <v>クロウ</v>
           </cell>
         </row>
         <row r="7">
@@ -795,7 +194,7 @@
             <v>6</v>
           </cell>
           <cell r="B7" t="str">
-            <v>ウィスプ</v>
+            <v>ネームレス</v>
           </cell>
         </row>
         <row r="8">
@@ -803,7 +202,7 @@
             <v>7</v>
           </cell>
           <cell r="B8" t="str">
-            <v>スネーク</v>
+            <v>サーチャー</v>
           </cell>
         </row>
         <row r="9">
@@ -811,7 +210,7 @@
             <v>8</v>
           </cell>
           <cell r="B9" t="str">
-            <v>スコーピオン</v>
+            <v>シールド</v>
           </cell>
         </row>
         <row r="10">
@@ -819,7 +218,7 @@
             <v>9</v>
           </cell>
           <cell r="B10" t="str">
-            <v>ゼリーフィッシュ</v>
+            <v>ドライアド</v>
           </cell>
         </row>
         <row r="11">
@@ -827,7 +226,7 @@
             <v>10</v>
           </cell>
           <cell r="B11" t="str">
-            <v>マッドプラント</v>
+            <v>スコーピオン</v>
           </cell>
         </row>
         <row r="12">
@@ -835,7 +234,7 @@
             <v>11</v>
           </cell>
           <cell r="B12" t="str">
-            <v>ゴースト</v>
+            <v>スクイッド</v>
           </cell>
         </row>
         <row r="13">
@@ -843,7 +242,7 @@
             <v>12</v>
           </cell>
           <cell r="B13" t="str">
-            <v>スケルトン</v>
+            <v>クリーパー</v>
           </cell>
         </row>
         <row r="14">
@@ -851,7 +250,7 @@
             <v>13</v>
           </cell>
           <cell r="B14" t="str">
-            <v>オーク</v>
+            <v>インプ</v>
           </cell>
         </row>
         <row r="15">
@@ -859,7 +258,7 @@
             <v>14</v>
           </cell>
           <cell r="B15" t="str">
-            <v>インプ</v>
+            <v>ゴーストアーマー</v>
           </cell>
         </row>
         <row r="16">
@@ -867,310 +266,214 @@
             <v>15</v>
           </cell>
           <cell r="B16" t="str">
-            <v>ゲイザー</v>
+            <v>ソード</v>
           </cell>
         </row>
         <row r="17">
           <cell r="A17">
-            <v>16</v>
+            <v>101</v>
           </cell>
           <cell r="B17" t="str">
-            <v>パペット</v>
+            <v>アモン</v>
           </cell>
         </row>
         <row r="18">
           <cell r="A18">
-            <v>17</v>
+            <v>102</v>
           </cell>
           <cell r="B18" t="str">
-            <v>ゾンビ</v>
+            <v>ベリト</v>
           </cell>
         </row>
         <row r="19">
           <cell r="A19">
-            <v>18</v>
+            <v>103</v>
           </cell>
           <cell r="B19" t="str">
-            <v>コカトリス</v>
+            <v>パイモン</v>
           </cell>
         </row>
         <row r="20">
           <cell r="A20">
-            <v>19</v>
+            <v>104</v>
           </cell>
           <cell r="B20" t="str">
-            <v>サハギン</v>
+            <v>アンドラス</v>
           </cell>
         </row>
         <row r="21">
           <cell r="A21">
-            <v>20</v>
+            <v>105</v>
           </cell>
           <cell r="B21" t="str">
-            <v>ウェアウルフ</v>
+            <v>ビフロンス</v>
           </cell>
         </row>
         <row r="22">
           <cell r="A22">
-            <v>101</v>
+            <v>106</v>
           </cell>
           <cell r="B22" t="str">
-            <v>ベヒーモス</v>
+            <v>アイホート</v>
           </cell>
         </row>
         <row r="23">
           <cell r="A23">
-            <v>102</v>
+            <v>107</v>
           </cell>
           <cell r="B23" t="str">
-            <v>ミノタウロス</v>
+            <v>ビヤーキー</v>
           </cell>
         </row>
         <row r="24">
           <cell r="A24">
-            <v>103</v>
+            <v>201</v>
           </cell>
           <cell r="B24" t="str">
-            <v>シルフ</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="25">
           <cell r="A25">
-            <v>104</v>
+            <v>202</v>
           </cell>
           <cell r="B25" t="str">
-            <v>イヴィルキング</v>
+            <v>ザガン</v>
           </cell>
         </row>
         <row r="26">
           <cell r="A26">
-            <v>105</v>
+            <v>203</v>
           </cell>
           <cell r="B26" t="str">
-            <v>ケルベロス</v>
+            <v>アスタロト</v>
           </cell>
         </row>
         <row r="27">
           <cell r="A27">
-            <v>106</v>
+            <v>204</v>
           </cell>
           <cell r="B27" t="str">
-            <v>ガルーダ</v>
+            <v>デカラビア</v>
           </cell>
         </row>
         <row r="28">
           <cell r="A28">
-            <v>107</v>
+            <v>205</v>
           </cell>
           <cell r="B28" t="str">
-            <v>ドラゴン</v>
+            <v>インドラ</v>
           </cell>
         </row>
         <row r="29">
           <cell r="A29">
-            <v>108</v>
+            <v>206</v>
           </cell>
           <cell r="B29" t="str">
-            <v>ラミア</v>
+            <v>ズルワーン</v>
           </cell>
         </row>
         <row r="30">
           <cell r="A30">
-            <v>109</v>
+            <v>207</v>
           </cell>
           <cell r="B30" t="str">
-            <v>コピーパペット</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="31">
           <cell r="A31">
-            <v>110</v>
+            <v>301</v>
           </cell>
           <cell r="B31" t="str">
-            <v>ヴァンパイア</v>
+            <v>デビルドラゴン</v>
           </cell>
         </row>
         <row r="32">
           <cell r="A32">
-            <v>111</v>
+            <v>1001</v>
           </cell>
           <cell r="B32" t="str">
-            <v>デス</v>
+            <v>ミカ</v>
           </cell>
         </row>
         <row r="33">
           <cell r="A33">
-            <v>112</v>
+            <v>1002</v>
           </cell>
           <cell r="B33" t="str">
-            <v>エナメルスライム</v>
+            <v>エリザベート</v>
           </cell>
         </row>
         <row r="34">
           <cell r="A34">
-            <v>113</v>
+            <v>1003</v>
           </cell>
           <cell r="B34" t="str">
-            <v>デーモン</v>
+            <v>アリエス</v>
           </cell>
         </row>
         <row r="35">
           <cell r="A35">
-            <v>114</v>
+            <v>1004</v>
           </cell>
           <cell r="B35" t="str">
-            <v>キメラ</v>
+            <v>シイナ</v>
           </cell>
         </row>
         <row r="36">
           <cell r="A36">
-            <v>201</v>
+            <v>1005</v>
           </cell>
           <cell r="B36" t="str">
-            <v>アンリマユ</v>
+            <v>レダ</v>
           </cell>
         </row>
         <row r="37">
           <cell r="A37">
-            <v>202</v>
+            <v>1006</v>
           </cell>
           <cell r="B37" t="str">
-            <v>ザガン</v>
+            <v>リシェリ</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38">
-            <v>203</v>
+            <v>1007</v>
           </cell>
           <cell r="B38" t="str">
-            <v>アスタロト</v>
+            <v>ユニ</v>
           </cell>
         </row>
         <row r="39">
           <cell r="A39">
-            <v>204</v>
+            <v>1008</v>
           </cell>
           <cell r="B39" t="str">
-            <v>デカラビア</v>
+            <v>マリーベル</v>
           </cell>
         </row>
         <row r="40">
           <cell r="A40">
-            <v>205</v>
+            <v>1009</v>
           </cell>
           <cell r="B40" t="str">
-            <v>インドラ</v>
+            <v>ナツキ</v>
           </cell>
         </row>
         <row r="41">
           <cell r="A41">
-            <v>206</v>
+            <v>1010</v>
           </cell>
           <cell r="B41" t="str">
-            <v>ズルワーン</v>
+            <v>メリアドール</v>
           </cell>
         </row>
         <row r="42">
           <cell r="A42">
-            <v>207</v>
+            <v>1011</v>
           </cell>
           <cell r="B42" t="str">
-            <v>アンリマユ</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>301</v>
-          </cell>
-          <cell r="B43" t="str">
-            <v>デビルドラゴン</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>1001</v>
-          </cell>
-          <cell r="B44" t="str">
-            <v>ミカ</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45">
-            <v>1002</v>
-          </cell>
-          <cell r="B45" t="str">
-            <v>エリザベート</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46">
-            <v>1003</v>
-          </cell>
-          <cell r="B46" t="str">
-            <v>アリエス</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47">
-            <v>1004</v>
-          </cell>
-          <cell r="B47" t="str">
-            <v>シイナ</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48">
-            <v>1005</v>
-          </cell>
-          <cell r="B48" t="str">
-            <v>レダ</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49">
-            <v>1006</v>
-          </cell>
-          <cell r="B49" t="str">
-            <v>リシェリ</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50">
-            <v>1007</v>
-          </cell>
-          <cell r="B50" t="str">
-            <v>ユニ</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51">
-            <v>1008</v>
-          </cell>
-          <cell r="B51" t="str">
-            <v>マリーベル</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52">
-            <v>1009</v>
-          </cell>
-          <cell r="B52" t="str">
-            <v>ナツキ</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53">
-            <v>1010</v>
-          </cell>
-          <cell r="B53" t="str">
-            <v>メリアドール</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54">
-            <v>1011</v>
-          </cell>
-          <cell r="B54" t="str">
             <v>セリナ</v>
           </cell>
         </row>
@@ -1433,21 +736,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H116"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H127"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.54545454545454"/>
-    <col min="4" max="4" width="16.5454545454545" customWidth="1"/>
-    <col min="8" max="8" width="10.2727272727273" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875"/>
+    <col min="4" max="4" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1473,7 +776,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1485,7 +788,7 @@
       </c>
       <c r="D2" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C2,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E2">
         <v>40</v>
@@ -1500,7 +803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1512,7 +815,7 @@
       </c>
       <c r="D3" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C3,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E3">
         <v>40</v>
@@ -1527,7 +830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1539,7 +842,7 @@
       </c>
       <c r="D4" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C4,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>サーチャー</v>
       </c>
       <c r="E4">
         <v>40</v>
@@ -1554,7 +857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1566,7 +869,7 @@
       </c>
       <c r="D5" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C5,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1581,7 +884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1593,7 +896,7 @@
       </c>
       <c r="D6" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C6,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1608,7 +911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1620,7 +923,7 @@
       </c>
       <c r="D7" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C7,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1635,7 +938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1647,7 +950,7 @@
       </c>
       <c r="D8" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C8,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1662,7 +965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1011</v>
       </c>
@@ -1670,17 +973,17 @@
         <v>1011</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C9,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ウルフ</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1689,22 +992,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>1021</v>
+        <v>1011</v>
       </c>
       <c r="B10">
-        <v>1021</v>
+        <v>1011</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C10,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ウルフ</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1716,7 +1019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1031</v>
       </c>
@@ -1724,11 +1027,11 @@
         <v>1031</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C11,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>ウルフ</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -1743,22 +1046,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>1041</v>
+        <v>1031</v>
       </c>
       <c r="B12">
-        <v>1041</v>
+        <v>1031</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D12" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C12,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ウルフ</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1770,25 +1073,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>1041</v>
+        <v>1032</v>
       </c>
       <c r="B13">
-        <v>1041</v>
+        <v>1032</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1797,22 +1100,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>1042</v>
+        <v>1032</v>
       </c>
       <c r="B14">
-        <v>1042</v>
+        <v>1032</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D14" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C14,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1824,25 +1127,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>1042</v>
+        <v>1032</v>
       </c>
       <c r="B15">
-        <v>1042</v>
+        <v>1032</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1851,22 +1154,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>1101</v>
+        <v>1041</v>
       </c>
       <c r="B16">
-        <v>1101</v>
+        <v>1041</v>
       </c>
       <c r="C16">
-        <v>101</v>
+        <v>3</v>
       </c>
       <c r="D16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C16,[1]TextData!A:A))</f>
-        <v>ベヒーモス</v>
+        <v>ビー</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1878,19 +1181,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>2011</v>
+        <v>1041</v>
       </c>
       <c r="B17">
-        <v>2011</v>
+        <v>1041</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C17,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>ビー</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1905,25 +1208,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>2021</v>
+        <v>1042</v>
       </c>
       <c r="B18">
-        <v>2021</v>
+        <v>1042</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>サーチャー</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1932,22 +1235,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>2021</v>
+        <v>1042</v>
       </c>
       <c r="B19">
-        <v>2021</v>
+        <v>1042</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>サーチャー</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1959,22 +1262,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>2031</v>
+        <v>1051</v>
       </c>
       <c r="B20">
-        <v>2031</v>
+        <v>1051</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1986,22 +1289,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>2101</v>
+        <v>1051</v>
       </c>
       <c r="B21">
-        <v>2101</v>
+        <v>1051</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C21,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2013,22 +1316,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>2101</v>
+        <v>1052</v>
       </c>
       <c r="B22">
-        <v>2101</v>
+        <v>1052</v>
       </c>
       <c r="C22">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>ミノタウロス</v>
+        <v>カースド</v>
       </c>
       <c r="E22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -2040,22 +1343,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>2101</v>
+        <v>1052</v>
       </c>
       <c r="B23">
-        <v>2101</v>
+        <v>1052</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>カースド</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2067,25 +1370,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>2102</v>
+        <v>1061</v>
       </c>
       <c r="B24">
-        <v>2102</v>
+        <v>1061</v>
       </c>
       <c r="C24">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>ミノタウロス</v>
+        <v>ビー</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -2094,22 +1397,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>2102</v>
+        <v>1071</v>
       </c>
       <c r="B25">
-        <v>2102</v>
+        <v>1071</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D25" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C25,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>サーチャー</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2121,52 +1424,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>2201</v>
+        <v>1101</v>
       </c>
       <c r="B26">
-        <v>2201</v>
+        <v>1101</v>
       </c>
       <c r="C26">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
-        <v>ゼリーフィッシュ</v>
+        <v>アモン</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>2201</v>
+        <v>2041</v>
       </c>
       <c r="B27">
-        <v>2201</v>
+        <v>2041</v>
       </c>
       <c r="C27">
         <v>4</v>
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -2175,19 +1478,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>2201</v>
+        <v>2041</v>
       </c>
       <c r="B28">
-        <v>2201</v>
+        <v>2041</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>カースド</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2202,19 +1505,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>2201</v>
+        <v>2041</v>
       </c>
       <c r="B29">
-        <v>2201</v>
+        <v>2041</v>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>ゼリーフィッシュ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2226,79 +1529,79 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>2201</v>
+        <v>2042</v>
       </c>
       <c r="B30">
-        <v>2201</v>
+        <v>2042</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>スクイッド</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>2202</v>
+        <v>2042</v>
       </c>
       <c r="B31">
-        <v>2202</v>
+        <v>2042</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>カースド</v>
       </c>
       <c r="E31">
         <v>5</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>2202</v>
+        <v>2042</v>
       </c>
       <c r="B32">
-        <v>2202</v>
+        <v>2042</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2310,25 +1613,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>2202</v>
+        <v>2101</v>
       </c>
       <c r="B33">
-        <v>2202</v>
+        <v>2101</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="D33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>ベリト</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -2337,19 +1640,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>2202</v>
+        <v>2101</v>
       </c>
       <c r="B34">
-        <v>2202</v>
+        <v>2101</v>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>ウルフ</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2361,103 +1664,103 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>2202</v>
+        <v>2102</v>
       </c>
       <c r="B35">
-        <v>2202</v>
+        <v>2102</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>ベリト</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>2203</v>
+        <v>2102</v>
       </c>
       <c r="B36">
-        <v>2203</v>
+        <v>2102</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ウルフ</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="B37">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>ドライアド</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="B38">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>ウルフ</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2472,19 +1775,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="B39">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="C39">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C39,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ウルフ</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2496,22 +1799,22 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="B40">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>ドライアド</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2523,76 +1826,76 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="B41">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>ウルフ</v>
       </c>
       <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>2202</v>
+      </c>
+      <c r="B42">
+        <v>2202</v>
+      </c>
+      <c r="C42">
         <v>5</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42">
-        <v>2204</v>
-      </c>
-      <c r="B42">
-        <v>2204</v>
-      </c>
-      <c r="C42">
-        <v>14</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>クロウ</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="B43">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="C43">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D43" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C43,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ビー</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -2607,19 +1910,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="B44">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="C44">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D44" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C44,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>ビー</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2631,22 +1934,22 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="B45">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="C45">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C45,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>クロウ</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2658,76 +1961,76 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="B46">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="C46">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C46,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>ビー</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="B47">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>シールド</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="B48">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D48" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C48,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>サーチャー</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2742,19 +2045,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="B49">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="C49">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C49,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>サーチャー</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2766,22 +2069,22 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="B50">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>シールド</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2793,76 +2096,76 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>3041</v>
+        <v>2203</v>
       </c>
       <c r="B51">
-        <v>3041</v>
+        <v>2203</v>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>サーチャー</v>
       </c>
       <c r="E51">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>3041</v>
+        <v>2204</v>
       </c>
       <c r="B52">
-        <v>3041</v>
+        <v>2204</v>
       </c>
       <c r="C52">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C52,[1]TextData!A:A))</f>
-        <v>オーク</v>
+        <v>ネームレス</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>3041</v>
+        <v>2204</v>
       </c>
       <c r="B53">
-        <v>3041</v>
+        <v>2204</v>
       </c>
       <c r="C53">
         <v>14</v>
       </c>
       <c r="D53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C53,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2877,19 +2180,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>3041</v>
+        <v>2204</v>
       </c>
       <c r="B54">
-        <v>3041</v>
+        <v>2204</v>
       </c>
       <c r="C54">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D54" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C54,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2904,49 +2207,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>3042</v>
+        <v>2204</v>
       </c>
       <c r="B55">
-        <v>3042</v>
+        <v>2204</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C55,[1]TextData!A:A))</f>
-        <v>バット</v>
+        <v>ネームレス</v>
       </c>
       <c r="E55">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>3042</v>
+        <v>2204</v>
       </c>
       <c r="B56">
-        <v>3042</v>
+        <v>2204</v>
       </c>
       <c r="C56">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C56,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E56">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2955,52 +2258,52 @@
         <v>0</v>
       </c>
       <c r="H56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>3042</v>
+        <v>2205</v>
       </c>
       <c r="B57">
-        <v>3042</v>
+        <v>2205</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C57,[1]TextData!A:A))</f>
-        <v>スネーク</v>
+        <v>クリーパー</v>
       </c>
       <c r="E57">
         <v>5</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>3042</v>
+        <v>2205</v>
       </c>
       <c r="B58">
-        <v>3042</v>
+        <v>2205</v>
       </c>
       <c r="C58">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D58" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C58,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>カースド</v>
       </c>
       <c r="E58">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -3012,49 +2315,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>3101</v>
+        <v>2205</v>
       </c>
       <c r="B59">
-        <v>3101</v>
+        <v>2205</v>
       </c>
       <c r="C59">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="D59" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C59,[1]TextData!A:A))</f>
-        <v>シルフ</v>
+        <v>カースド</v>
       </c>
       <c r="E59">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>3101</v>
+        <v>2205</v>
       </c>
       <c r="B60">
-        <v>3101</v>
+        <v>2205</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C60,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>クリーパー</v>
       </c>
       <c r="E60">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -3063,52 +2366,52 @@
         <v>0</v>
       </c>
       <c r="H60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>3101</v>
+        <v>2205</v>
       </c>
       <c r="B61">
-        <v>3101</v>
+        <v>2205</v>
       </c>
       <c r="C61">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D61" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C61,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>カースド</v>
       </c>
       <c r="E61">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>3102</v>
+        <v>3041</v>
       </c>
       <c r="B62">
-        <v>3102</v>
+        <v>3041</v>
       </c>
       <c r="C62">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="D62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C62,[1]TextData!A:A))</f>
-        <v>シルフ</v>
+        <v>ネームレス</v>
       </c>
       <c r="E62">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F62">
         <v>1</v>
@@ -3120,22 +2423,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>3102</v>
+        <v>3041</v>
       </c>
       <c r="B63">
-        <v>3102</v>
+        <v>3041</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D63" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C63,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>インプ</v>
       </c>
       <c r="E63">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3147,52 +2450,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>3102</v>
+        <v>3041</v>
       </c>
       <c r="B64">
-        <v>3102</v>
+        <v>3041</v>
       </c>
       <c r="C64">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C64,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E64">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F64">
         <v>0</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64">
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="12" customHeight="1" spans="1:8">
+    <row r="65" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>4041</v>
-      </c>
-      <c r="B65" s="2">
-        <v>4041</v>
+        <v>3041</v>
+      </c>
+      <c r="B65">
+        <v>3041</v>
       </c>
       <c r="C65">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C65,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ネームレス</v>
       </c>
       <c r="E65">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -3201,25 +2504,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>4041</v>
-      </c>
-      <c r="B66" s="2">
-        <v>4041</v>
+        <v>3042</v>
+      </c>
+      <c r="B66">
+        <v>3042</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C66,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>カースド</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -3228,22 +2531,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>4041</v>
-      </c>
-      <c r="B67" s="2">
-        <v>4041</v>
+        <v>3042</v>
+      </c>
+      <c r="B67">
+        <v>3042</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C67,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>クリーパー</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -3255,22 +2558,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>4041</v>
-      </c>
-      <c r="B68" s="2">
-        <v>4041</v>
+        <v>3042</v>
+      </c>
+      <c r="B68">
+        <v>3042</v>
       </c>
       <c r="C68">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C68,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>サーチャー</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -3282,22 +2585,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>4041</v>
-      </c>
-      <c r="B69" s="2">
-        <v>4041</v>
+        <v>3042</v>
+      </c>
+      <c r="B69">
+        <v>3042</v>
       </c>
       <c r="C69">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C69,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>クリーパー</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -3309,19 +2612,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="2">
-        <v>4042</v>
-      </c>
-      <c r="B70" s="2">
-        <v>4042</v>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>3101</v>
+      </c>
+      <c r="B70">
+        <v>3101</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="D70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C70,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>パイモン</v>
       </c>
       <c r="E70">
         <v>15</v>
@@ -3336,19 +2639,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="2">
-        <v>4042</v>
-      </c>
-      <c r="B71" s="2">
-        <v>4042</v>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>3101</v>
+      </c>
+      <c r="B71">
+        <v>3101</v>
       </c>
       <c r="C71">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C71,[1]TextData!A:A))</f>
-        <v>ゲイザー</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E71">
         <v>5</v>
@@ -3363,19 +2666,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="2">
-        <v>4042</v>
-      </c>
-      <c r="B72" s="2">
-        <v>4042</v>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>3101</v>
+      </c>
+      <c r="B72">
+        <v>3101</v>
       </c>
       <c r="C72">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D72" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C72,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>クロウ</v>
       </c>
       <c r="E72">
         <v>5</v>
@@ -3384,85 +2687,85 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="2">
-        <v>4042</v>
-      </c>
-      <c r="B73" s="2">
-        <v>4042</v>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>3102</v>
+      </c>
+      <c r="B73">
+        <v>3102</v>
       </c>
       <c r="C73">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="D73" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C73,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>パイモン</v>
       </c>
       <c r="E73">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="2">
-        <v>4042</v>
-      </c>
-      <c r="B74" s="2">
-        <v>4042</v>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>3102</v>
+      </c>
+      <c r="B74">
+        <v>3102</v>
       </c>
       <c r="C74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C74,[1]TextData!A:A))</f>
-        <v>ホーネット</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E74">
+        <v>15</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>3102</v>
+      </c>
+      <c r="B75">
+        <v>3102</v>
+      </c>
+      <c r="C75">
         <v>5</v>
-      </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-      <c r="G74">
-        <v>1</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75">
-        <v>4101</v>
-      </c>
-      <c r="B75">
-        <v>4101</v>
-      </c>
-      <c r="C75">
-        <v>104</v>
       </c>
       <c r="D75" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C75,[1]TextData!A:A))</f>
-        <v>イヴィルキング</v>
+        <v>クロウ</v>
       </c>
       <c r="E75">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -3471,73 +2774,73 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>4102</v>
+        <v>4041</v>
       </c>
       <c r="B76">
-        <v>4102</v>
+        <v>4041</v>
       </c>
       <c r="C76">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="D76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C76,[1]TextData!A:A))</f>
-        <v>イヴィルキング</v>
+        <v>シールド</v>
       </c>
       <c r="E76">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>5041</v>
+        <v>4041</v>
       </c>
       <c r="B77">
-        <v>5041</v>
+        <v>4041</v>
       </c>
       <c r="C77">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C77,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E77">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>5041</v>
+        <v>4041</v>
       </c>
       <c r="B78">
-        <v>5041</v>
+        <v>4041</v>
       </c>
       <c r="C78">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C78,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3552,19 +2855,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>5041</v>
+        <v>4041</v>
       </c>
       <c r="B79">
-        <v>5041</v>
+        <v>4041</v>
       </c>
       <c r="C79">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C79,[1]TextData!A:A))</f>
-        <v>スケルトン</v>
+        <v>スクイッド</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -3579,19 +2882,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>5041</v>
+        <v>4041</v>
       </c>
       <c r="B80">
-        <v>5041</v>
+        <v>4041</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C80,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>スクイッド</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -3606,52 +2909,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>5041</v>
+        <v>4042</v>
       </c>
       <c r="B81">
-        <v>5041</v>
+        <v>4042</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C81,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ビー</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B82" s="2">
-        <v>5042</v>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>4042</v>
+      </c>
+      <c r="B82">
+        <v>4042</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C82,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ソード</v>
       </c>
       <c r="E82">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -3660,19 +2963,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
-      <c r="A83" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B83" s="2">
-        <v>5042</v>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>4042</v>
+      </c>
+      <c r="B83">
+        <v>4042</v>
       </c>
       <c r="C83">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C83,[1]TextData!A:A))</f>
-        <v>ウィスプ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E83">
         <v>5</v>
@@ -3681,25 +2984,25 @@
         <v>0</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B84" s="2">
-        <v>5042</v>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>4042</v>
+      </c>
+      <c r="B84">
+        <v>4042</v>
       </c>
       <c r="C84">
         <v>14</v>
       </c>
       <c r="D84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C84,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E84">
         <v>5</v>
@@ -3708,25 +3011,25 @@
         <v>0</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B85" s="2">
-        <v>5042</v>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>4042</v>
+      </c>
+      <c r="B85">
+        <v>4042</v>
       </c>
       <c r="C85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C85,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>ビー</v>
       </c>
       <c r="E85">
         <v>5</v>
@@ -3735,52 +3038,52 @@
         <v>0</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="2">
-        <v>5042</v>
-      </c>
-      <c r="B86" s="2">
-        <v>5042</v>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>4101</v>
+      </c>
+      <c r="B86">
+        <v>4101</v>
       </c>
       <c r="C86">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="D86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C86,[1]TextData!A:A))</f>
-        <v>スパイダー</v>
+        <v>アンドラス</v>
       </c>
       <c r="E86">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87">
-        <v>5101</v>
+        <v>4102</v>
       </c>
       <c r="B87">
-        <v>5101</v>
+        <v>4102</v>
       </c>
       <c r="C87">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C87,[1]TextData!A:A))</f>
-        <v>ケルベロス</v>
+        <v>アンドラス</v>
       </c>
       <c r="E87">
         <v>30</v>
@@ -3795,49 +3098,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88">
-        <v>5101</v>
+        <v>5041</v>
       </c>
       <c r="B88">
-        <v>5101</v>
+        <v>5041</v>
       </c>
       <c r="C88">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C88,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>クリーパー</v>
       </c>
       <c r="E88">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89">
-        <v>5101</v>
+        <v>5041</v>
       </c>
       <c r="B89">
-        <v>5101</v>
+        <v>5041</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C89,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>クリーパー</v>
       </c>
       <c r="E89">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -3849,22 +3152,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90">
-        <v>5101</v>
+        <v>5041</v>
       </c>
       <c r="B90">
-        <v>5101</v>
+        <v>5041</v>
       </c>
       <c r="C90">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C90,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>クリーパー</v>
       </c>
       <c r="E90">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -3876,22 +3179,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91">
-        <v>5101</v>
+        <v>5041</v>
       </c>
       <c r="B91">
-        <v>5101</v>
+        <v>5041</v>
       </c>
       <c r="C91">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C91,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E91">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -3903,52 +3206,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92">
-        <v>5102</v>
+        <v>5041</v>
       </c>
       <c r="B92">
-        <v>5102</v>
+        <v>5041</v>
       </c>
       <c r="C92">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="D92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C92,[1]TextData!A:A))</f>
-        <v>ケルベロス</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E92">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93">
-        <v>5102</v>
+        <v>5042</v>
       </c>
       <c r="B93">
-        <v>5102</v>
+        <v>5042</v>
       </c>
       <c r="C93">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C93,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ウルフ</v>
       </c>
       <c r="E93">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -3957,76 +3260,76 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94">
-        <v>5102</v>
+        <v>5042</v>
       </c>
       <c r="B94">
-        <v>5102</v>
+        <v>5042</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C94,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>ネームレス</v>
       </c>
       <c r="E94">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F94">
         <v>0</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95">
-        <v>5102</v>
+        <v>5042</v>
       </c>
       <c r="B95">
-        <v>5102</v>
+        <v>5042</v>
       </c>
       <c r="C95">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C95,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E95">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F95">
         <v>0</v>
       </c>
       <c r="G95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96">
-        <v>5102</v>
+        <v>5042</v>
       </c>
       <c r="B96">
-        <v>5102</v>
+        <v>5042</v>
       </c>
       <c r="C96">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C96,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>ウルフ</v>
       </c>
       <c r="E96">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -4038,103 +3341,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97">
-        <v>6021</v>
+        <v>5042</v>
       </c>
       <c r="B97">
-        <v>6021</v>
+        <v>5042</v>
       </c>
       <c r="C97">
-        <v>1002</v>
+        <v>4</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C97,[1]TextData!A:A))</f>
-        <v>エリザベート</v>
+        <v>ウルフ</v>
       </c>
       <c r="E97">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98">
-        <v>6021</v>
+        <v>5101</v>
       </c>
       <c r="B98">
-        <v>6021</v>
+        <v>5101</v>
       </c>
       <c r="C98">
-        <v>1003</v>
+        <v>105</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C98,[1]TextData!A:A))</f>
-        <v>アリエス</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99">
-        <v>6021</v>
+        <v>5101</v>
       </c>
       <c r="B99">
-        <v>6021</v>
+        <v>5101</v>
       </c>
       <c r="C99">
-        <v>1004</v>
+        <v>8</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C99,[1]TextData!A:A))</f>
-        <v>シイナ</v>
+        <v>シールド</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F99">
         <v>0</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99">
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100">
-        <v>6021</v>
+        <v>5101</v>
       </c>
       <c r="B100">
-        <v>6021</v>
+        <v>5101</v>
       </c>
       <c r="C100">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C100,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -4146,22 +3449,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101">
-        <v>6021</v>
+        <v>5101</v>
       </c>
       <c r="B101">
-        <v>6021</v>
+        <v>5101</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C101,[1]TextData!A:A))</f>
-        <v>スライム</v>
+        <v>シールド</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -4173,25 +3476,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102">
-        <v>6022</v>
+        <v>5101</v>
       </c>
       <c r="B102">
-        <v>6022</v>
+        <v>5101</v>
       </c>
       <c r="C102">
-        <v>1011</v>
+        <v>11</v>
       </c>
       <c r="D102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C102,[1]TextData!A:A))</f>
-        <v>セリナ</v>
+        <v>スクイッド</v>
       </c>
       <c r="E102">
         <v>10</v>
       </c>
       <c r="F102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -4200,103 +3503,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103">
-        <v>6022</v>
+        <v>5102</v>
       </c>
       <c r="B103">
-        <v>6022</v>
+        <v>5102</v>
       </c>
       <c r="C103">
-        <v>1005</v>
+        <v>105</v>
       </c>
       <c r="D103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C103,[1]TextData!A:A))</f>
-        <v>レダ</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103">
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104">
-        <v>6022</v>
+        <v>5102</v>
       </c>
       <c r="B104">
-        <v>6022</v>
+        <v>5102</v>
       </c>
       <c r="C104">
-        <v>1010</v>
+        <v>8</v>
       </c>
       <c r="D104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C104,[1]TextData!A:A))</f>
-        <v>メリアドール</v>
+        <v>シールド</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="G104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104">
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105">
-        <v>6022</v>
+        <v>5102</v>
       </c>
       <c r="B105">
-        <v>6022</v>
+        <v>5102</v>
       </c>
       <c r="C105">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C105,[1]TextData!A:A))</f>
-        <v>マッドプラント</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F105">
         <v>0</v>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105">
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106">
-        <v>6022</v>
+        <v>5102</v>
       </c>
       <c r="B106">
-        <v>6022</v>
+        <v>5102</v>
       </c>
       <c r="C106">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C106,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>シールド</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -4308,25 +3611,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107">
-        <v>6031</v>
+        <v>5102</v>
       </c>
       <c r="B107">
-        <v>6031</v>
+        <v>5102</v>
       </c>
       <c r="C107">
-        <v>1001</v>
+        <v>11</v>
       </c>
       <c r="D107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C107,[1]TextData!A:A))</f>
-        <v>ミカ</v>
+        <v>スクイッド</v>
       </c>
       <c r="E107">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -4335,46 +3638,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108">
-        <v>6031</v>
+        <v>6021</v>
       </c>
       <c r="B108">
-        <v>6031</v>
+        <v>6021</v>
       </c>
       <c r="C108">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="D108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C108,[1]TextData!A:A))</f>
-        <v>リシェリ</v>
+        <v>エリザベート</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109">
-        <v>6031</v>
+        <v>6021</v>
       </c>
       <c r="B109">
-        <v>6031</v>
+        <v>6021</v>
       </c>
       <c r="C109">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="D109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C109,[1]TextData!A:A))</f>
-        <v>マリーベル</v>
+        <v>アリエス</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -4389,19 +3692,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110">
-        <v>6031</v>
+        <v>6021</v>
       </c>
       <c r="B110">
-        <v>6031</v>
+        <v>6021</v>
       </c>
       <c r="C110">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="D110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C110,[1]TextData!A:A))</f>
-        <v>ユニ</v>
+        <v>シイナ</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -4410,25 +3713,25 @@
         <v>0</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110">
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111">
-        <v>6031</v>
+        <v>6021</v>
       </c>
       <c r="B111">
-        <v>6031</v>
+        <v>6021</v>
       </c>
       <c r="C111">
-        <v>1009</v>
+        <v>8</v>
       </c>
       <c r="D111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C111,[1]TextData!A:A))</f>
-        <v>ナツキ</v>
+        <v>シールド</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -4443,52 +3746,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112">
-        <v>6101</v>
+        <v>6021</v>
       </c>
       <c r="B112">
-        <v>6101</v>
+        <v>6021</v>
       </c>
       <c r="C112">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="D112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C112,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E112">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113">
-        <v>6101</v>
+        <v>6022</v>
       </c>
       <c r="B113">
-        <v>6101</v>
+        <v>6022</v>
       </c>
       <c r="C113">
-        <v>15</v>
+        <v>1011</v>
       </c>
       <c r="D113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C113,[1]TextData!A:A))</f>
-        <v>ゲイザー</v>
+        <v>セリナ</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -4497,19 +3800,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114">
-        <v>6101</v>
+        <v>6022</v>
       </c>
       <c r="B114">
-        <v>6101</v>
+        <v>6022</v>
       </c>
       <c r="C114">
-        <v>11</v>
+        <v>1005</v>
       </c>
       <c r="D114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C114,[1]TextData!A:A))</f>
-        <v>ゴースト</v>
+        <v>レダ</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4524,19 +3827,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115">
-        <v>6101</v>
+        <v>6022</v>
       </c>
       <c r="B115">
-        <v>6101</v>
+        <v>6022</v>
       </c>
       <c r="C115">
-        <v>5</v>
+        <v>1010</v>
       </c>
       <c r="D115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C115,[1]TextData!A:A))</f>
-        <v>ビッグラット</v>
+        <v>メリアドール</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4551,19 +3854,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116">
-        <v>6101</v>
+        <v>6022</v>
       </c>
       <c r="B116">
-        <v>6101</v>
+        <v>6022</v>
       </c>
       <c r="C116">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C116,[1]TextData!A:A))</f>
-        <v>オーク</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4578,9 +3881,306 @@
         <v>0</v>
       </c>
     </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>6022</v>
+      </c>
+      <c r="B117">
+        <v>6022</v>
+      </c>
+      <c r="C117">
+        <v>14</v>
+      </c>
+      <c r="D117" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C117,[1]TextData!A:A))</f>
+        <v>ゴーストアーマー</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>6031</v>
+      </c>
+      <c r="B118">
+        <v>6031</v>
+      </c>
+      <c r="C118">
+        <v>1001</v>
+      </c>
+      <c r="D118" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C118,[1]TextData!A:A))</f>
+        <v>ミカ</v>
+      </c>
+      <c r="E118">
+        <v>10</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>6031</v>
+      </c>
+      <c r="B119">
+        <v>6031</v>
+      </c>
+      <c r="C119">
+        <v>1006</v>
+      </c>
+      <c r="D119" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C119,[1]TextData!A:A))</f>
+        <v>リシェリ</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>6031</v>
+      </c>
+      <c r="B120">
+        <v>6031</v>
+      </c>
+      <c r="C120">
+        <v>1008</v>
+      </c>
+      <c r="D120" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C120,[1]TextData!A:A))</f>
+        <v>マリーベル</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>6031</v>
+      </c>
+      <c r="B121">
+        <v>6031</v>
+      </c>
+      <c r="C121">
+        <v>1007</v>
+      </c>
+      <c r="D121" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C121,[1]TextData!A:A))</f>
+        <v>ユニ</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>6031</v>
+      </c>
+      <c r="B122">
+        <v>6031</v>
+      </c>
+      <c r="C122">
+        <v>1009</v>
+      </c>
+      <c r="D122" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C122,[1]TextData!A:A))</f>
+        <v>ナツキ</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>6101</v>
+      </c>
+      <c r="B123">
+        <v>6101</v>
+      </c>
+      <c r="C123">
+        <v>201</v>
+      </c>
+      <c r="D123" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C123,[1]TextData!A:A))</f>
+        <v>アンリマユ</v>
+      </c>
+      <c r="E123">
+        <v>10</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123">
+        <v>1</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>6101</v>
+      </c>
+      <c r="B124">
+        <v>6101</v>
+      </c>
+      <c r="C124">
+        <v>15</v>
+      </c>
+      <c r="D124" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C124,[1]TextData!A:A))</f>
+        <v>ソード</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>6101</v>
+      </c>
+      <c r="B125">
+        <v>6101</v>
+      </c>
+      <c r="C125">
+        <v>11</v>
+      </c>
+      <c r="D125" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C125,[1]TextData!A:A))</f>
+        <v>スクイッド</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>6101</v>
+      </c>
+      <c r="B126">
+        <v>6101</v>
+      </c>
+      <c r="C126">
+        <v>5</v>
+      </c>
+      <c r="D126" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C126,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>1</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>6101</v>
+      </c>
+      <c r="B127">
+        <v>6101</v>
+      </c>
+      <c r="C127">
+        <v>13</v>
+      </c>
+      <c r="D127" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C127,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>1</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A65873-0AFB-4E43-A135-97B53A7D8603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -18,18 +12,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -63,8 +46,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -73,22 +62,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -96,9 +408,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -110,24 +664,68 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Enemies"/>
@@ -736,21 +1334,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H127"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="9.54296875"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
-    <col min="8" max="8" width="10.26953125" customWidth="1"/>
+    <col min="2" max="2" width="9.54545454545454"/>
+    <col min="4" max="4" width="16.5454545454545" customWidth="1"/>
+    <col min="8" max="8" width="10.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -776,7 +1374,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -803,7 +1401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>1</v>
       </c>
@@ -830,7 +1428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>1</v>
       </c>
@@ -857,7 +1455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>2</v>
       </c>
@@ -884,7 +1482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>3</v>
       </c>
@@ -911,7 +1509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>4</v>
       </c>
@@ -938,7 +1536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>5</v>
       </c>
@@ -965,7 +1563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>1011</v>
       </c>
@@ -992,7 +1590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>1011</v>
       </c>
@@ -1019,7 +1617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>1031</v>
       </c>
@@ -1046,7 +1644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>1031</v>
       </c>
@@ -1073,7 +1671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>1032</v>
       </c>
@@ -1100,7 +1698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>1032</v>
       </c>
@@ -1127,7 +1725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>1032</v>
       </c>
@@ -1154,7 +1752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>1041</v>
       </c>
@@ -1181,7 +1779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>1041</v>
       </c>
@@ -1208,7 +1806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>1042</v>
       </c>
@@ -1235,7 +1833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>1042</v>
       </c>
@@ -1262,7 +1860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>1051</v>
       </c>
@@ -1289,7 +1887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>1051</v>
       </c>
@@ -1316,7 +1914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>1052</v>
       </c>
@@ -1343,7 +1941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>1052</v>
       </c>
@@ -1370,7 +1968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>1061</v>
       </c>
@@ -1397,7 +1995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>1071</v>
       </c>
@@ -1424,7 +2022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>1101</v>
       </c>
@@ -1451,7 +2049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>2041</v>
       </c>
@@ -1478,7 +2076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>2041</v>
       </c>
@@ -1505,7 +2103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>2041</v>
       </c>
@@ -1532,7 +2130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>2042</v>
       </c>
@@ -1559,7 +2157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>2042</v>
       </c>
@@ -1586,7 +2184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>2042</v>
       </c>
@@ -1613,7 +2211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8">
       <c r="A33">
         <v>2101</v>
       </c>
@@ -1640,7 +2238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8">
       <c r="A34">
         <v>2101</v>
       </c>
@@ -1667,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8">
       <c r="A35">
         <v>2102</v>
       </c>
@@ -1694,7 +2292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8">
       <c r="A36">
         <v>2102</v>
       </c>
@@ -1721,7 +2319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8">
       <c r="A37">
         <v>2201</v>
       </c>
@@ -1748,7 +2346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8">
       <c r="A38">
         <v>2201</v>
       </c>
@@ -1775,7 +2373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8">
       <c r="A39">
         <v>2201</v>
       </c>
@@ -1802,7 +2400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8">
       <c r="A40">
         <v>2201</v>
       </c>
@@ -1829,7 +2427,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8">
       <c r="A41">
         <v>2201</v>
       </c>
@@ -1856,7 +2454,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8">
       <c r="A42">
         <v>2202</v>
       </c>
@@ -1883,7 +2481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8">
       <c r="A43">
         <v>2202</v>
       </c>
@@ -1910,7 +2508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8">
       <c r="A44">
         <v>2202</v>
       </c>
@@ -1937,7 +2535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8">
       <c r="A45">
         <v>2202</v>
       </c>
@@ -1964,7 +2562,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8">
       <c r="A46">
         <v>2202</v>
       </c>
@@ -1991,7 +2589,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8">
       <c r="A47">
         <v>2203</v>
       </c>
@@ -2018,7 +2616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8">
       <c r="A48">
         <v>2203</v>
       </c>
@@ -2045,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8">
       <c r="A49">
         <v>2203</v>
       </c>
@@ -2072,7 +2670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8">
       <c r="A50">
         <v>2203</v>
       </c>
@@ -2099,7 +2697,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8">
       <c r="A51">
         <v>2203</v>
       </c>
@@ -2126,7 +2724,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8">
       <c r="A52">
         <v>2204</v>
       </c>
@@ -2153,7 +2751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8">
       <c r="A53">
         <v>2204</v>
       </c>
@@ -2180,7 +2778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8">
       <c r="A54">
         <v>2204</v>
       </c>
@@ -2207,7 +2805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8">
       <c r="A55">
         <v>2204</v>
       </c>
@@ -2234,7 +2832,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8">
       <c r="A56">
         <v>2204</v>
       </c>
@@ -2261,7 +2859,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8">
       <c r="A57">
         <v>2205</v>
       </c>
@@ -2288,7 +2886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8">
       <c r="A58">
         <v>2205</v>
       </c>
@@ -2315,7 +2913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8">
       <c r="A59">
         <v>2205</v>
       </c>
@@ -2342,7 +2940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8">
       <c r="A60">
         <v>2205</v>
       </c>
@@ -2369,7 +2967,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8">
       <c r="A61">
         <v>2205</v>
       </c>
@@ -2396,7 +2994,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8">
       <c r="A62">
         <v>3041</v>
       </c>
@@ -2423,7 +3021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8">
       <c r="A63">
         <v>3041</v>
       </c>
@@ -2450,7 +3048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8">
       <c r="A64">
         <v>3041</v>
       </c>
@@ -2477,7 +3075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" ht="12" customHeight="1" spans="1:8">
       <c r="A65">
         <v>3041</v>
       </c>
@@ -2504,7 +3102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8">
       <c r="A66">
         <v>3042</v>
       </c>
@@ -2531,7 +3129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8">
       <c r="A67">
         <v>3042</v>
       </c>
@@ -2558,7 +3156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8">
       <c r="A68">
         <v>3042</v>
       </c>
@@ -2585,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8">
       <c r="A69">
         <v>3042</v>
       </c>
@@ -2612,7 +3210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8">
       <c r="A70">
         <v>3101</v>
       </c>
@@ -2639,7 +3237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8">
       <c r="A71">
         <v>3101</v>
       </c>
@@ -2666,7 +3264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8">
       <c r="A72">
         <v>3101</v>
       </c>
@@ -2693,7 +3291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8">
       <c r="A73">
         <v>3102</v>
       </c>
@@ -2720,7 +3318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8">
       <c r="A74">
         <v>3102</v>
       </c>
@@ -2747,7 +3345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8">
       <c r="A75">
         <v>3102</v>
       </c>
@@ -2774,7 +3372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8">
       <c r="A76">
         <v>4041</v>
       </c>
@@ -2801,7 +3399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8">
       <c r="A77">
         <v>4041</v>
       </c>
@@ -2828,7 +3426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8">
       <c r="A78">
         <v>4041</v>
       </c>
@@ -2855,7 +3453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8">
       <c r="A79">
         <v>4041</v>
       </c>
@@ -2882,7 +3480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8">
       <c r="A80">
         <v>4041</v>
       </c>
@@ -2909,7 +3507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8">
       <c r="A81">
         <v>4042</v>
       </c>
@@ -2936,7 +3534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8">
       <c r="A82">
         <v>4042</v>
       </c>
@@ -2963,7 +3561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8">
       <c r="A83">
         <v>4042</v>
       </c>
@@ -2990,7 +3588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8">
       <c r="A84">
         <v>4042</v>
       </c>
@@ -3017,7 +3615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8">
       <c r="A85">
         <v>4042</v>
       </c>
@@ -3044,7 +3642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8">
       <c r="A86">
         <v>4101</v>
       </c>
@@ -3071,7 +3669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8">
       <c r="A87">
         <v>4102</v>
       </c>
@@ -3098,7 +3696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8">
       <c r="A88">
         <v>5041</v>
       </c>
@@ -3125,7 +3723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8">
       <c r="A89">
         <v>5041</v>
       </c>
@@ -3152,7 +3750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8">
       <c r="A90">
         <v>5041</v>
       </c>
@@ -3179,7 +3777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8">
       <c r="A91">
         <v>5041</v>
       </c>
@@ -3206,7 +3804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8">
       <c r="A92">
         <v>5041</v>
       </c>
@@ -3233,7 +3831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8">
       <c r="A93">
         <v>5042</v>
       </c>
@@ -3260,7 +3858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8">
       <c r="A94">
         <v>5042</v>
       </c>
@@ -3287,7 +3885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8">
       <c r="A95">
         <v>5042</v>
       </c>
@@ -3314,7 +3912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8">
       <c r="A96">
         <v>5042</v>
       </c>
@@ -3341,7 +3939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8">
       <c r="A97">
         <v>5042</v>
       </c>
@@ -3368,7 +3966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8">
       <c r="A98">
         <v>5101</v>
       </c>
@@ -3395,7 +3993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8">
       <c r="A99">
         <v>5101</v>
       </c>
@@ -3422,7 +4020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8">
       <c r="A100">
         <v>5101</v>
       </c>
@@ -3449,7 +4047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8">
       <c r="A101">
         <v>5101</v>
       </c>
@@ -3476,7 +4074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8">
       <c r="A102">
         <v>5101</v>
       </c>
@@ -3503,7 +4101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8">
       <c r="A103">
         <v>5102</v>
       </c>
@@ -3530,7 +4128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8">
       <c r="A104">
         <v>5102</v>
       </c>
@@ -3557,7 +4155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8">
       <c r="A105">
         <v>5102</v>
       </c>
@@ -3584,7 +4182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8">
       <c r="A106">
         <v>5102</v>
       </c>
@@ -3611,7 +4209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8">
       <c r="A107">
         <v>5102</v>
       </c>
@@ -3638,7 +4236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8">
       <c r="A108">
         <v>6021</v>
       </c>
@@ -3665,7 +4263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8">
       <c r="A109">
         <v>6021</v>
       </c>
@@ -3692,7 +4290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8">
       <c r="A110">
         <v>6021</v>
       </c>
@@ -3719,7 +4317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8">
       <c r="A111">
         <v>6021</v>
       </c>
@@ -3746,7 +4344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8">
       <c r="A112">
         <v>6021</v>
       </c>
@@ -3773,7 +4371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8">
       <c r="A113">
         <v>6022</v>
       </c>
@@ -3800,7 +4398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8">
       <c r="A114">
         <v>6022</v>
       </c>
@@ -3827,7 +4425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8">
       <c r="A115">
         <v>6022</v>
       </c>
@@ -3854,7 +4452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8">
       <c r="A116">
         <v>6022</v>
       </c>
@@ -3881,7 +4479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8">
       <c r="A117">
         <v>6022</v>
       </c>
@@ -3908,7 +4506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8">
       <c r="A118">
         <v>6031</v>
       </c>
@@ -3935,7 +4533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8">
       <c r="A119">
         <v>6031</v>
       </c>
@@ -3962,7 +4560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8">
       <c r="A120">
         <v>6031</v>
       </c>
@@ -3989,7 +4587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8">
       <c r="A121">
         <v>6031</v>
       </c>
@@ -4016,7 +4614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8">
       <c r="A122">
         <v>6031</v>
       </c>
@@ -4043,7 +4641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8">
       <c r="A123">
         <v>6101</v>
       </c>
@@ -4070,7 +4668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8">
       <c r="A124">
         <v>6101</v>
       </c>
@@ -4097,7 +4695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8">
       <c r="A125">
         <v>6101</v>
       </c>
@@ -4124,7 +4722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8">
       <c r="A126">
         <v>6101</v>
       </c>
@@ -4151,7 +4749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8">
       <c r="A127">
         <v>6101</v>
       </c>
@@ -4179,8 +4777,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,53 +48,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -109,22 +71,51 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -132,6 +123,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -169,6 +167,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -176,15 +182,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -193,14 +201,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -221,121 +221,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -347,13 +233,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,7 +251,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -383,7 +347,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,7 +383,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,6 +424,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -435,24 +444,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -481,6 +472,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -495,17 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,16 +514,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -532,28 +532,28 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -562,97 +562,97 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1340,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1565,23 +1565,23 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B9">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C9,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1592,17 +1592,17 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10">
-        <v>1011</v>
+        <v>1020</v>
       </c>
       <c r="B10">
-        <v>1011</v>
+        <v>1020</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C10,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1619,23 +1619,23 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B11">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C11,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
-        <v>1031</v>
+        <v>1040</v>
       </c>
       <c r="B12">
-        <v>1031</v>
+        <v>1040</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -1662,7 +1662,7 @@
         <v>3</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1673,17 +1673,17 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>1032</v>
+        <v>1100</v>
       </c>
       <c r="B13">
-        <v>1032</v>
+        <v>1100</v>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>アモン</v>
       </c>
       <c r="E13">
         <v>5</v>
@@ -1700,20 +1700,20 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>1032</v>
+        <v>1110</v>
       </c>
       <c r="B14">
-        <v>1032</v>
+        <v>1110</v>
       </c>
       <c r="C14">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D14" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C14,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ビー</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1727,20 +1727,20 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>1032</v>
+        <v>1120</v>
       </c>
       <c r="B15">
-        <v>1032</v>
+        <v>1120</v>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>サーチャー</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1754,20 +1754,20 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>1041</v>
+        <v>2041</v>
       </c>
       <c r="B16">
-        <v>1041</v>
+        <v>2041</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C16,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1781,20 +1781,20 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>1041</v>
+        <v>2041</v>
       </c>
       <c r="B17">
-        <v>1041</v>
+        <v>2041</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C17,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>カースド</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1808,23 +1808,23 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>1042</v>
+        <v>2041</v>
       </c>
       <c r="B18">
-        <v>1042</v>
+        <v>2041</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1835,23 +1835,23 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>1042</v>
+        <v>2042</v>
       </c>
       <c r="B19">
-        <v>1042</v>
+        <v>2042</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>スクイッド</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1862,23 +1862,23 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>1051</v>
+        <v>2042</v>
       </c>
       <c r="B20">
-        <v>1051</v>
+        <v>2042</v>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>カースド</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>1051</v>
+        <v>2042</v>
       </c>
       <c r="B21">
-        <v>1051</v>
+        <v>2042</v>
       </c>
       <c r="C21">
         <v>14</v>
@@ -1902,7 +1902,7 @@
         <v>ゴーストアーマー</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1916,20 +1916,20 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>1052</v>
+        <v>2100</v>
       </c>
       <c r="B22">
-        <v>1052</v>
+        <v>2100</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ベリト</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1943,20 +1943,20 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>1052</v>
+        <v>2101</v>
       </c>
       <c r="B23">
-        <v>1052</v>
+        <v>2101</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1970,26 +1970,26 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>1061</v>
+        <v>2201</v>
       </c>
       <c r="B24">
-        <v>1061</v>
+        <v>2201</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ドライアド</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1997,20 +1997,20 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>1071</v>
+        <v>2201</v>
       </c>
       <c r="B25">
-        <v>1071</v>
+        <v>2201</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D25" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C25,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2024,23 +2024,23 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>1101</v>
+        <v>2201</v>
       </c>
       <c r="B26">
-        <v>1101</v>
+        <v>2201</v>
       </c>
       <c r="C26">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>ウルフ</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -2051,44 +2051,44 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>2041</v>
+        <v>2201</v>
       </c>
       <c r="B27">
-        <v>2041</v>
+        <v>2201</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ドライアド</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>2041</v>
+        <v>2201</v>
       </c>
       <c r="B28">
-        <v>2041</v>
+        <v>2201</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2100,31 +2100,31 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>2041</v>
+        <v>2202</v>
       </c>
       <c r="B29">
-        <v>2041</v>
+        <v>2202</v>
       </c>
       <c r="C29">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クロウ</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2132,23 +2132,23 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>2042</v>
+        <v>2202</v>
       </c>
       <c r="B30">
-        <v>2042</v>
+        <v>2202</v>
       </c>
       <c r="C30">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ビー</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -2159,20 +2159,20 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>2042</v>
+        <v>2202</v>
       </c>
       <c r="B31">
-        <v>2042</v>
+        <v>2202</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ビー</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2186,20 +2186,20 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>2042</v>
+        <v>2202</v>
       </c>
       <c r="B32">
-        <v>2042</v>
+        <v>2202</v>
       </c>
       <c r="C32">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クロウ</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2208,58 +2208,58 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>2101</v>
+        <v>2202</v>
       </c>
       <c r="B33">
-        <v>2101</v>
+        <v>2202</v>
       </c>
       <c r="C33">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="D33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>ビー</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>2101</v>
+        <v>2203</v>
       </c>
       <c r="B34">
-        <v>2101</v>
+        <v>2203</v>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>シールド</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2267,23 +2267,23 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>2102</v>
+        <v>2203</v>
       </c>
       <c r="B35">
-        <v>2102</v>
+        <v>2203</v>
       </c>
       <c r="C35">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>サーチャー</v>
       </c>
       <c r="E35">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -2294,20 +2294,20 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>2102</v>
+        <v>2203</v>
       </c>
       <c r="B36">
-        <v>2102</v>
+        <v>2203</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>サーチャー</v>
       </c>
       <c r="E36">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2321,44 +2321,44 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="B37">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>シールド</v>
       </c>
       <c r="E37">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="B38">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>サーチャー</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2370,31 +2370,31 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>2201</v>
+        <v>2204</v>
       </c>
       <c r="B39">
-        <v>2201</v>
+        <v>2204</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C39,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネームレス</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -2402,17 +2402,17 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>2201</v>
+        <v>2204</v>
       </c>
       <c r="B40">
-        <v>2201</v>
+        <v>2204</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2424,22 +2424,22 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>2201</v>
+        <v>2204</v>
       </c>
       <c r="B41">
-        <v>2201</v>
+        <v>2204</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2451,49 +2451,49 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="B42">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ネームレス</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="B43">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D43" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C43,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -2505,31 +2505,31 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="B44">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D44" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C44,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -2537,17 +2537,17 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="B45">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C45,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>カースド</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2559,22 +2559,22 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="B46">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C46,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>カースド</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2586,49 +2586,49 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="B47">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="C47">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>クリーパー</v>
       </c>
       <c r="E47">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="B48">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D48" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C48,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>カースド</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2640,31 +2640,31 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>2203</v>
+        <v>3041</v>
       </c>
       <c r="B49">
-        <v>2203</v>
+        <v>3041</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C49,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -2672,17 +2672,17 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>2203</v>
+        <v>3041</v>
       </c>
       <c r="B50">
-        <v>2203</v>
+        <v>3041</v>
       </c>
       <c r="C50">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>インプ</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2694,22 +2694,22 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>2203</v>
+        <v>3041</v>
       </c>
       <c r="B51">
-        <v>2203</v>
+        <v>3041</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2721,15 +2721,15 @@
         <v>0</v>
       </c>
       <c r="H51">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="12" customHeight="1" spans="1:8">
       <c r="A52">
-        <v>2204</v>
+        <v>3041</v>
       </c>
       <c r="B52">
-        <v>2204</v>
+        <v>3041</v>
       </c>
       <c r="C52">
         <v>6</v>
@@ -2739,13 +2739,13 @@
         <v>ネームレス</v>
       </c>
       <c r="E52">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -2753,23 +2753,23 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>2204</v>
+        <v>3042</v>
       </c>
       <c r="B53">
-        <v>2204</v>
+        <v>3042</v>
       </c>
       <c r="C53">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C53,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>カースド</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2780,20 +2780,20 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>2204</v>
+        <v>3042</v>
       </c>
       <c r="B54">
-        <v>2204</v>
+        <v>3042</v>
       </c>
       <c r="C54">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D54" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C54,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2807,20 +2807,20 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>2204</v>
+        <v>3042</v>
       </c>
       <c r="B55">
-        <v>2204</v>
+        <v>3042</v>
       </c>
       <c r="C55">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C55,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>サーチャー</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2829,25 +2829,25 @@
         <v>0</v>
       </c>
       <c r="H55">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>2204</v>
+        <v>3042</v>
       </c>
       <c r="B56">
-        <v>2204</v>
+        <v>3042</v>
       </c>
       <c r="C56">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C56,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2856,25 +2856,25 @@
         <v>0</v>
       </c>
       <c r="H56">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>2205</v>
+        <v>3100</v>
       </c>
       <c r="B57">
-        <v>2205</v>
+        <v>3100</v>
       </c>
       <c r="C57">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C57,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>パイモン</v>
       </c>
       <c r="E57">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -2888,20 +2888,20 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>2205</v>
+        <v>3101</v>
       </c>
       <c r="B58">
-        <v>2205</v>
+        <v>3101</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C58,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2915,26 +2915,26 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>2205</v>
+        <v>3101</v>
       </c>
       <c r="B59">
-        <v>2205</v>
+        <v>3101</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D59" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C59,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>クロウ</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -2942,44 +2942,44 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>2205</v>
+        <v>4041</v>
       </c>
       <c r="B60">
-        <v>2205</v>
+        <v>4041</v>
       </c>
       <c r="C60">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C60,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>シールド</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>2205</v>
+        <v>4041</v>
       </c>
       <c r="B61">
-        <v>2205</v>
+        <v>4041</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C61,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2991,31 +2991,31 @@
         <v>0</v>
       </c>
       <c r="H61">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>3041</v>
+        <v>4041</v>
       </c>
       <c r="B62">
-        <v>3041</v>
+        <v>4041</v>
       </c>
       <c r="C62">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C62,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E62">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -3023,17 +3023,17 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>3041</v>
+        <v>4041</v>
       </c>
       <c r="B63">
-        <v>3041</v>
+        <v>4041</v>
       </c>
       <c r="C63">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D63" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C63,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スクイッド</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -3050,17 +3050,17 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>3041</v>
+        <v>4041</v>
       </c>
       <c r="B64">
-        <v>3041</v>
+        <v>4041</v>
       </c>
       <c r="C64">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C64,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スクイッド</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -3075,28 +3075,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="12" customHeight="1" spans="1:8">
+    <row r="65" spans="1:8">
       <c r="A65">
-        <v>3041</v>
+        <v>4042</v>
       </c>
       <c r="B65">
-        <v>3041</v>
+        <v>4042</v>
       </c>
       <c r="C65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C65,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ビー</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -3104,23 +3104,23 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>3042</v>
+        <v>4042</v>
       </c>
       <c r="B66">
-        <v>3042</v>
+        <v>4042</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C66,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ソード</v>
       </c>
       <c r="E66">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -3131,17 +3131,17 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67">
-        <v>3042</v>
+        <v>4042</v>
       </c>
       <c r="B67">
-        <v>3042</v>
+        <v>4042</v>
       </c>
       <c r="C67">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C67,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E67">
         <v>5</v>
@@ -3158,17 +3158,17 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>3042</v>
+        <v>4042</v>
       </c>
       <c r="B68">
-        <v>3042</v>
+        <v>4042</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C68,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E68">
         <v>5</v>
@@ -3185,17 +3185,17 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>3042</v>
+        <v>4042</v>
       </c>
       <c r="B69">
-        <v>3042</v>
+        <v>4042</v>
       </c>
       <c r="C69">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C69,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ビー</v>
       </c>
       <c r="E69">
         <v>5</v>
@@ -3204,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -3212,20 +3212,20 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>3101</v>
+        <v>4101</v>
       </c>
       <c r="B70">
-        <v>3101</v>
+        <v>4101</v>
       </c>
       <c r="C70">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C70,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>アンドラス</v>
       </c>
       <c r="E70">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -3239,26 +3239,26 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>3101</v>
+        <v>4102</v>
       </c>
       <c r="B71">
-        <v>3101</v>
+        <v>4102</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="D71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C71,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>アンドラス</v>
       </c>
       <c r="E71">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -3266,23 +3266,23 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
-        <v>3101</v>
+        <v>5041</v>
       </c>
       <c r="B72">
-        <v>3101</v>
+        <v>5041</v>
       </c>
       <c r="C72">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D72" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C72,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>クリーパー</v>
       </c>
       <c r="E72">
         <v>5</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -3293,26 +3293,26 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>3102</v>
+        <v>5041</v>
       </c>
       <c r="B73">
-        <v>3102</v>
+        <v>5041</v>
       </c>
       <c r="C73">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="D73" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C73,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>クリーパー</v>
       </c>
       <c r="E73">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -3320,20 +3320,20 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74">
-        <v>3102</v>
+        <v>5041</v>
       </c>
       <c r="B74">
-        <v>3102</v>
+        <v>5041</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C74,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>クリーパー</v>
       </c>
       <c r="E74">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -3347,26 +3347,26 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>3102</v>
+        <v>5041</v>
       </c>
       <c r="B75">
-        <v>3102</v>
+        <v>5041</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D75" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C75,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E75">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F75">
         <v>0</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -3374,23 +3374,23 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>4041</v>
+        <v>5041</v>
       </c>
       <c r="B76">
-        <v>4041</v>
+        <v>5041</v>
       </c>
       <c r="C76">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C76,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E76">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -3401,23 +3401,23 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>4041</v>
+        <v>5042</v>
       </c>
       <c r="B77">
-        <v>4041</v>
+        <v>5042</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C77,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ウルフ</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -3428,26 +3428,26 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
-        <v>4041</v>
+        <v>5042</v>
       </c>
       <c r="B78">
-        <v>4041</v>
+        <v>5042</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C78,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ネームレス</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F78">
         <v>0</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -3455,26 +3455,26 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
-        <v>4041</v>
+        <v>5042</v>
       </c>
       <c r="B79">
-        <v>4041</v>
+        <v>5042</v>
       </c>
       <c r="C79">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C79,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F79">
         <v>0</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -3482,20 +3482,20 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
-        <v>4041</v>
+        <v>5042</v>
       </c>
       <c r="B80">
-        <v>4041</v>
+        <v>5042</v>
       </c>
       <c r="C80">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C80,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -3509,26 +3509,26 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81">
-        <v>4042</v>
+        <v>5042</v>
       </c>
       <c r="B81">
-        <v>4042</v>
+        <v>5042</v>
       </c>
       <c r="C81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C81,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E81">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -3536,26 +3536,26 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82">
-        <v>4042</v>
+        <v>5101</v>
       </c>
       <c r="B82">
-        <v>4042</v>
+        <v>5101</v>
       </c>
       <c r="C82">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C82,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E82">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -3563,20 +3563,20 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83">
-        <v>4042</v>
+        <v>5101</v>
       </c>
       <c r="B83">
-        <v>4042</v>
+        <v>5101</v>
       </c>
       <c r="C83">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C83,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>シールド</v>
       </c>
       <c r="E83">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -3590,20 +3590,20 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84">
-        <v>4042</v>
+        <v>5101</v>
       </c>
       <c r="B84">
-        <v>4042</v>
+        <v>5101</v>
       </c>
       <c r="C84">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C84,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E84">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -3617,26 +3617,26 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85">
-        <v>4042</v>
+        <v>5101</v>
       </c>
       <c r="B85">
-        <v>4042</v>
+        <v>5101</v>
       </c>
       <c r="C85">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C85,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>シールド</v>
       </c>
       <c r="E85">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F85">
         <v>0</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -3644,26 +3644,26 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86">
-        <v>4101</v>
+        <v>5101</v>
       </c>
       <c r="B86">
-        <v>4101</v>
+        <v>5101</v>
       </c>
       <c r="C86">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="D86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C86,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>スクイッド</v>
       </c>
       <c r="E86">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -3671,20 +3671,20 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87">
-        <v>4102</v>
+        <v>5102</v>
       </c>
       <c r="B87">
-        <v>4102</v>
+        <v>5102</v>
       </c>
       <c r="C87">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C87,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E87">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -3698,26 +3698,26 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88">
-        <v>5041</v>
+        <v>5102</v>
       </c>
       <c r="B88">
-        <v>5041</v>
+        <v>5102</v>
       </c>
       <c r="C88">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C88,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>シールド</v>
       </c>
       <c r="E88">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -3725,20 +3725,20 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89">
-        <v>5041</v>
+        <v>5102</v>
       </c>
       <c r="B89">
-        <v>5041</v>
+        <v>5102</v>
       </c>
       <c r="C89">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C89,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -3752,20 +3752,20 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90">
-        <v>5041</v>
+        <v>5102</v>
       </c>
       <c r="B90">
-        <v>5041</v>
+        <v>5102</v>
       </c>
       <c r="C90">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C90,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>シールド</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -3779,20 +3779,20 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91">
-        <v>5041</v>
+        <v>5102</v>
       </c>
       <c r="B91">
-        <v>5041</v>
+        <v>5102</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C91,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スクイッド</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -3806,26 +3806,26 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92">
-        <v>5041</v>
+        <v>6021</v>
       </c>
       <c r="B92">
-        <v>5041</v>
+        <v>6021</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="D92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C92,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>エリザベート</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -3833,23 +3833,23 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93">
-        <v>5042</v>
+        <v>6021</v>
       </c>
       <c r="B93">
-        <v>5042</v>
+        <v>6021</v>
       </c>
       <c r="C93">
-        <v>4</v>
+        <v>1003</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C93,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>アリエス</v>
       </c>
       <c r="E93">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -3860,20 +3860,20 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94">
-        <v>5042</v>
+        <v>6021</v>
       </c>
       <c r="B94">
-        <v>5042</v>
+        <v>6021</v>
       </c>
       <c r="C94">
-        <v>6</v>
+        <v>1004</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C94,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>シイナ</v>
       </c>
       <c r="E94">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -3887,26 +3887,26 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95">
-        <v>5042</v>
+        <v>6021</v>
       </c>
       <c r="B95">
-        <v>5042</v>
+        <v>6021</v>
       </c>
       <c r="C95">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C95,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>シールド</v>
       </c>
       <c r="E95">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F95">
         <v>0</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95">
         <v>0</v>
@@ -3914,20 +3914,20 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96">
-        <v>5042</v>
+        <v>6021</v>
       </c>
       <c r="B96">
-        <v>5042</v>
+        <v>6021</v>
       </c>
       <c r="C96">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C96,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E96">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -3941,23 +3941,23 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97">
-        <v>5042</v>
+        <v>6022</v>
       </c>
       <c r="B97">
-        <v>5042</v>
+        <v>6022</v>
       </c>
       <c r="C97">
-        <v>4</v>
+        <v>1011</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C97,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>セリナ</v>
       </c>
       <c r="E97">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -3968,26 +3968,26 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98">
-        <v>5101</v>
+        <v>6022</v>
       </c>
       <c r="B98">
-        <v>5101</v>
+        <v>6022</v>
       </c>
       <c r="C98">
-        <v>105</v>
+        <v>1005</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C98,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>レダ</v>
       </c>
       <c r="E98">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -3995,26 +3995,26 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99">
-        <v>5101</v>
+        <v>6022</v>
       </c>
       <c r="B99">
-        <v>5101</v>
+        <v>6022</v>
       </c>
       <c r="C99">
-        <v>8</v>
+        <v>1010</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C99,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>メリアドール</v>
       </c>
       <c r="E99">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F99">
         <v>0</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -4022,26 +4022,26 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100">
-        <v>5101</v>
+        <v>6022</v>
       </c>
       <c r="B100">
-        <v>5101</v>
+        <v>6022</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C100,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E100">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F100">
         <v>0</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -4049,20 +4049,20 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101">
-        <v>5101</v>
+        <v>6022</v>
       </c>
       <c r="B101">
-        <v>5101</v>
+        <v>6022</v>
       </c>
       <c r="C101">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C101,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E101">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -4076,23 +4076,23 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102">
-        <v>5101</v>
+        <v>6031</v>
       </c>
       <c r="B102">
-        <v>5101</v>
+        <v>6031</v>
       </c>
       <c r="C102">
-        <v>11</v>
+        <v>1001</v>
       </c>
       <c r="D102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C102,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ミカ</v>
       </c>
       <c r="E102">
         <v>10</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -4103,26 +4103,26 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103">
-        <v>5102</v>
+        <v>6031</v>
       </c>
       <c r="B103">
-        <v>5102</v>
+        <v>6031</v>
       </c>
       <c r="C103">
-        <v>105</v>
+        <v>1006</v>
       </c>
       <c r="D103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C103,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>リシェリ</v>
       </c>
       <c r="E103">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103">
         <v>0</v>
@@ -4130,20 +4130,20 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104">
-        <v>5102</v>
+        <v>6031</v>
       </c>
       <c r="B104">
-        <v>5102</v>
+        <v>6031</v>
       </c>
       <c r="C104">
-        <v>8</v>
+        <v>1008</v>
       </c>
       <c r="D104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C104,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>マリーベル</v>
       </c>
       <c r="E104">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -4157,20 +4157,20 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105">
-        <v>5102</v>
+        <v>6031</v>
       </c>
       <c r="B105">
-        <v>5102</v>
+        <v>6031</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>1007</v>
       </c>
       <c r="D105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C105,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ユニ</v>
       </c>
       <c r="E105">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -4184,20 +4184,20 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106">
-        <v>5102</v>
+        <v>6031</v>
       </c>
       <c r="B106">
-        <v>5102</v>
+        <v>6031</v>
       </c>
       <c r="C106">
-        <v>8</v>
+        <v>1009</v>
       </c>
       <c r="D106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C106,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ナツキ</v>
       </c>
       <c r="E106">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -4211,26 +4211,26 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107">
-        <v>5102</v>
+        <v>6101</v>
       </c>
       <c r="B107">
-        <v>5102</v>
+        <v>6101</v>
       </c>
       <c r="C107">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C107,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>アンリマユ</v>
       </c>
       <c r="E107">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -4238,26 +4238,26 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108">
-        <v>6021</v>
+        <v>6101</v>
       </c>
       <c r="B108">
-        <v>6021</v>
+        <v>6101</v>
       </c>
       <c r="C108">
-        <v>1002</v>
+        <v>15</v>
       </c>
       <c r="D108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C108,[1]TextData!A:A))</f>
-        <v>エリザベート</v>
+        <v>ソード</v>
       </c>
       <c r="E108">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -4265,17 +4265,17 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109">
-        <v>6021</v>
+        <v>6101</v>
       </c>
       <c r="B109">
-        <v>6021</v>
+        <v>6101</v>
       </c>
       <c r="C109">
-        <v>1003</v>
+        <v>11</v>
       </c>
       <c r="D109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C109,[1]TextData!A:A))</f>
-        <v>アリエス</v>
+        <v>スクイッド</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -4292,17 +4292,17 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110">
-        <v>6021</v>
+        <v>6101</v>
       </c>
       <c r="B110">
-        <v>6021</v>
+        <v>6101</v>
       </c>
       <c r="C110">
-        <v>1004</v>
+        <v>5</v>
       </c>
       <c r="D110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C110,[1]TextData!A:A))</f>
-        <v>シイナ</v>
+        <v>クロウ</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -4319,17 +4319,17 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111">
-        <v>6021</v>
+        <v>6101</v>
       </c>
       <c r="B111">
-        <v>6021</v>
+        <v>6101</v>
       </c>
       <c r="C111">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C111,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>インプ</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -4338,441 +4338,9 @@
         <v>0</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
-      <c r="A112">
-        <v>6021</v>
-      </c>
-      <c r="B112">
-        <v>6021</v>
-      </c>
-      <c r="C112">
-        <v>1</v>
-      </c>
-      <c r="D112" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C112,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
-      </c>
-      <c r="E112">
-        <v>0</v>
-      </c>
-      <c r="F112">
-        <v>0</v>
-      </c>
-      <c r="G112">
-        <v>0</v>
-      </c>
-      <c r="H112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
-      <c r="A113">
-        <v>6022</v>
-      </c>
-      <c r="B113">
-        <v>6022</v>
-      </c>
-      <c r="C113">
-        <v>1011</v>
-      </c>
-      <c r="D113" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C113,[1]TextData!A:A))</f>
-        <v>セリナ</v>
-      </c>
-      <c r="E113">
-        <v>10</v>
-      </c>
-      <c r="F113">
-        <v>1</v>
-      </c>
-      <c r="G113">
-        <v>0</v>
-      </c>
-      <c r="H113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8">
-      <c r="A114">
-        <v>6022</v>
-      </c>
-      <c r="B114">
-        <v>6022</v>
-      </c>
-      <c r="C114">
-        <v>1005</v>
-      </c>
-      <c r="D114" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C114,[1]TextData!A:A))</f>
-        <v>レダ</v>
-      </c>
-      <c r="E114">
-        <v>0</v>
-      </c>
-      <c r="F114">
-        <v>0</v>
-      </c>
-      <c r="G114">
-        <v>0</v>
-      </c>
-      <c r="H114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="A115">
-        <v>6022</v>
-      </c>
-      <c r="B115">
-        <v>6022</v>
-      </c>
-      <c r="C115">
-        <v>1010</v>
-      </c>
-      <c r="D115" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C115,[1]TextData!A:A))</f>
-        <v>メリアドール</v>
-      </c>
-      <c r="E115">
-        <v>0</v>
-      </c>
-      <c r="F115">
-        <v>0</v>
-      </c>
-      <c r="G115">
-        <v>1</v>
-      </c>
-      <c r="H115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
-      <c r="A116">
-        <v>6022</v>
-      </c>
-      <c r="B116">
-        <v>6022</v>
-      </c>
-      <c r="C116">
-        <v>10</v>
-      </c>
-      <c r="D116" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C116,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
-      </c>
-      <c r="E116">
-        <v>0</v>
-      </c>
-      <c r="F116">
-        <v>0</v>
-      </c>
-      <c r="G116">
-        <v>1</v>
-      </c>
-      <c r="H116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
-      <c r="A117">
-        <v>6022</v>
-      </c>
-      <c r="B117">
-        <v>6022</v>
-      </c>
-      <c r="C117">
-        <v>14</v>
-      </c>
-      <c r="D117" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C117,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
-      </c>
-      <c r="E117">
-        <v>0</v>
-      </c>
-      <c r="F117">
-        <v>0</v>
-      </c>
-      <c r="G117">
-        <v>0</v>
-      </c>
-      <c r="H117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8">
-      <c r="A118">
-        <v>6031</v>
-      </c>
-      <c r="B118">
-        <v>6031</v>
-      </c>
-      <c r="C118">
-        <v>1001</v>
-      </c>
-      <c r="D118" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C118,[1]TextData!A:A))</f>
-        <v>ミカ</v>
-      </c>
-      <c r="E118">
-        <v>10</v>
-      </c>
-      <c r="F118">
-        <v>1</v>
-      </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-      <c r="H118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8">
-      <c r="A119">
-        <v>6031</v>
-      </c>
-      <c r="B119">
-        <v>6031</v>
-      </c>
-      <c r="C119">
-        <v>1006</v>
-      </c>
-      <c r="D119" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C119,[1]TextData!A:A))</f>
-        <v>リシェリ</v>
-      </c>
-      <c r="E119">
-        <v>0</v>
-      </c>
-      <c r="F119">
-        <v>0</v>
-      </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-      <c r="H119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8">
-      <c r="A120">
-        <v>6031</v>
-      </c>
-      <c r="B120">
-        <v>6031</v>
-      </c>
-      <c r="C120">
-        <v>1008</v>
-      </c>
-      <c r="D120" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C120,[1]TextData!A:A))</f>
-        <v>マリーベル</v>
-      </c>
-      <c r="E120">
-        <v>0</v>
-      </c>
-      <c r="F120">
-        <v>0</v>
-      </c>
-      <c r="G120">
-        <v>0</v>
-      </c>
-      <c r="H120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8">
-      <c r="A121">
-        <v>6031</v>
-      </c>
-      <c r="B121">
-        <v>6031</v>
-      </c>
-      <c r="C121">
-        <v>1007</v>
-      </c>
-      <c r="D121" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C121,[1]TextData!A:A))</f>
-        <v>ユニ</v>
-      </c>
-      <c r="E121">
-        <v>0</v>
-      </c>
-      <c r="F121">
-        <v>0</v>
-      </c>
-      <c r="G121">
-        <v>0</v>
-      </c>
-      <c r="H121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8">
-      <c r="A122">
-        <v>6031</v>
-      </c>
-      <c r="B122">
-        <v>6031</v>
-      </c>
-      <c r="C122">
-        <v>1009</v>
-      </c>
-      <c r="D122" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C122,[1]TextData!A:A))</f>
-        <v>ナツキ</v>
-      </c>
-      <c r="E122">
-        <v>0</v>
-      </c>
-      <c r="F122">
-        <v>0</v>
-      </c>
-      <c r="G122">
-        <v>0</v>
-      </c>
-      <c r="H122">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8">
-      <c r="A123">
-        <v>6101</v>
-      </c>
-      <c r="B123">
-        <v>6101</v>
-      </c>
-      <c r="C123">
-        <v>201</v>
-      </c>
-      <c r="D123" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C123,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
-      </c>
-      <c r="E123">
-        <v>10</v>
-      </c>
-      <c r="F123">
-        <v>1</v>
-      </c>
-      <c r="G123">
-        <v>1</v>
-      </c>
-      <c r="H123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
-      <c r="A124">
-        <v>6101</v>
-      </c>
-      <c r="B124">
-        <v>6101</v>
-      </c>
-      <c r="C124">
-        <v>15</v>
-      </c>
-      <c r="D124" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C124,[1]TextData!A:A))</f>
-        <v>ソード</v>
-      </c>
-      <c r="E124">
-        <v>0</v>
-      </c>
-      <c r="F124">
-        <v>0</v>
-      </c>
-      <c r="G124">
-        <v>0</v>
-      </c>
-      <c r="H124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8">
-      <c r="A125">
-        <v>6101</v>
-      </c>
-      <c r="B125">
-        <v>6101</v>
-      </c>
-      <c r="C125">
-        <v>11</v>
-      </c>
-      <c r="D125" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C125,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
-      </c>
-      <c r="E125">
-        <v>0</v>
-      </c>
-      <c r="F125">
-        <v>0</v>
-      </c>
-      <c r="G125">
-        <v>0</v>
-      </c>
-      <c r="H125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
-      <c r="A126">
-        <v>6101</v>
-      </c>
-      <c r="B126">
-        <v>6101</v>
-      </c>
-      <c r="C126">
-        <v>5</v>
-      </c>
-      <c r="D126" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C126,[1]TextData!A:A))</f>
-        <v>クロウ</v>
-      </c>
-      <c r="E126">
-        <v>0</v>
-      </c>
-      <c r="F126">
-        <v>0</v>
-      </c>
-      <c r="G126">
-        <v>1</v>
-      </c>
-      <c r="H126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8">
-      <c r="A127">
-        <v>6101</v>
-      </c>
-      <c r="B127">
-        <v>6101</v>
-      </c>
-      <c r="C127">
-        <v>13</v>
-      </c>
-      <c r="D127" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C127,[1]TextData!A:A))</f>
-        <v>インプ</v>
-      </c>
-      <c r="E127">
-        <v>0</v>
-      </c>
-      <c r="F127">
-        <v>0</v>
-      </c>
-      <c r="G127">
-        <v>1</v>
-      </c>
-      <c r="H127">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,8 +48,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -62,9 +62,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -84,6 +108,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -92,16 +123,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -121,56 +190,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -179,30 +203,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -215,7 +215,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,7 +227,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -239,163 +389,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,17 +409,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -428,7 +428,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -450,9 +459,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -474,35 +485,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,7 +514,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -523,7 +523,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -532,127 +532,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1571,11 +1571,11 @@
         <v>1010</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C9,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E9">
         <v>1</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -50,8 +50,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -59,6 +59,34 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -72,14 +100,59 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -94,97 +167,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -205,6 +190,21 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,25 +215,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,7 +233,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,25 +269,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -293,73 +353,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,6 +371,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -389,13 +389,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,6 +406,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -426,9 +441,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -443,27 +460,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -491,21 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1340,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1605,7 +1605,7 @@
         <v>ビー</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B11">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -1632,7 +1632,7 @@
         <v>ビー</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1646,23 +1646,23 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="B12">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C12,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1673,23 +1673,23 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>1100</v>
+        <v>1030</v>
       </c>
       <c r="B13">
-        <v>1100</v>
+        <v>1030</v>
       </c>
       <c r="C13">
-        <v>101</v>
+        <v>3</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>ビー</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1700,23 +1700,23 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>1110</v>
+        <v>1040</v>
       </c>
       <c r="B14">
-        <v>1110</v>
+        <v>1040</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C14,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1727,23 +1727,23 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>1120</v>
+        <v>1100</v>
       </c>
       <c r="B15">
-        <v>1120</v>
+        <v>1100</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>アモン</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1754,23 +1754,23 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>2041</v>
+        <v>1110</v>
       </c>
       <c r="B16">
-        <v>2041</v>
+        <v>1110</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C16,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1781,20 +1781,20 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>2041</v>
+        <v>1120</v>
       </c>
       <c r="B17">
-        <v>2041</v>
+        <v>1120</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D17" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C17,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>サーチャー</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1814,17 +1814,17 @@
         <v>2041</v>
       </c>
       <c r="C18">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1835,23 +1835,23 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B19">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>カースド</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1862,20 +1862,20 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B20">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1895,17 +1895,17 @@
         <v>2042</v>
       </c>
       <c r="C21">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C21,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スクイッド</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1916,23 +1916,23 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>2100</v>
+        <v>2042</v>
       </c>
       <c r="B22">
-        <v>2100</v>
+        <v>2042</v>
       </c>
       <c r="C22">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>カースド</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1943,20 +1943,20 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>2101</v>
+        <v>2042</v>
       </c>
       <c r="B23">
-        <v>2101</v>
+        <v>2042</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1970,26 +1970,26 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>2201</v>
+        <v>2100</v>
       </c>
       <c r="B24">
-        <v>2201</v>
+        <v>2100</v>
       </c>
       <c r="C24">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ベリト</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="B25">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -2030,20 +2030,20 @@
         <v>2201</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ドライアド</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2057,11 +2057,11 @@
         <v>2201</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -2100,49 +2100,49 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="B29">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ドライアド</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="B30">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2165,20 +2165,20 @@
         <v>2202</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>クロウ</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -2192,11 +2192,11 @@
         <v>2202</v>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ビー</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2235,49 +2235,49 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="B34">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="C34">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>クロウ</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="B35">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ビー</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2289,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2300,20 +2300,20 @@
         <v>2203</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>シールド</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -2327,11 +2327,11 @@
         <v>2203</v>
       </c>
       <c r="C37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>サーチャー</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2343,7 +2343,7 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -2370,49 +2370,49 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="B39">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C39,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>シールド</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="B40">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="C40">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>サーチャー</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2435,20 +2435,20 @@
         <v>2204</v>
       </c>
       <c r="C41">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2462,11 +2462,11 @@
         <v>2204</v>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2505,49 +2505,49 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="B44">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C44">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D44" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C44,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="B45">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C45,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2570,20 +2570,20 @@
         <v>2205</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C46,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>クリーパー</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -2597,11 +2597,11 @@
         <v>2205</v>
       </c>
       <c r="C47">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>カースド</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2640,49 +2640,49 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>3041</v>
+        <v>2205</v>
       </c>
       <c r="B49">
-        <v>3041</v>
+        <v>2205</v>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C49,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>クリーパー</v>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>3041</v>
+        <v>2205</v>
       </c>
       <c r="B50">
-        <v>3041</v>
+        <v>2205</v>
       </c>
       <c r="C50">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>カースド</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2705,26 +2705,26 @@
         <v>3041</v>
       </c>
       <c r="C51">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51">
         <v>0</v>
       </c>
     </row>
-    <row r="52" ht="12" customHeight="1" spans="1:8">
+    <row r="52" spans="1:8">
       <c r="A52">
         <v>3041</v>
       </c>
@@ -2732,11 +2732,11 @@
         <v>3041</v>
       </c>
       <c r="C52">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C52,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>インプ</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2753,23 +2753,23 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="B53">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C53,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E53">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2778,22 +2778,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" ht="12" customHeight="1" spans="1:8">
       <c r="A54">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="B54">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="C54">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D54" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C54,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E54">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2813,17 +2813,17 @@
         <v>3042</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C55,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>カースド</v>
       </c>
       <c r="E55">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -2861,26 +2861,26 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>3100</v>
+        <v>3042</v>
       </c>
       <c r="B57">
-        <v>3100</v>
+        <v>3042</v>
       </c>
       <c r="C57">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C57,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>サーチャー</v>
       </c>
       <c r="E57">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -2888,17 +2888,17 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>3101</v>
+        <v>3042</v>
       </c>
       <c r="B58">
-        <v>3101</v>
+        <v>3042</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D58" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C58,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>クリーパー</v>
       </c>
       <c r="E58">
         <v>5</v>
@@ -2915,23 +2915,23 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="B59">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="C59">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="D59" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C59,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>パイモン</v>
       </c>
       <c r="E59">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -2942,23 +2942,23 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>4041</v>
+        <v>3101</v>
       </c>
       <c r="B60">
-        <v>4041</v>
+        <v>3101</v>
       </c>
       <c r="C60">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C60,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E60">
         <v>5</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -2969,26 +2969,26 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>4041</v>
+        <v>3101</v>
       </c>
       <c r="B61">
-        <v>4041</v>
+        <v>3101</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D61" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C61,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>クロウ</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -3002,17 +3002,17 @@
         <v>4041</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C62,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>シールド</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -3029,11 +3029,11 @@
         <v>4041</v>
       </c>
       <c r="C63">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D63" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C63,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -3056,11 +3056,11 @@
         <v>4041</v>
       </c>
       <c r="C64">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C64,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -3077,26 +3077,26 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="B65">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C65,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>スクイッド</v>
       </c>
       <c r="E65">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -3104,20 +3104,20 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="B66">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="C66">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C66,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>スクイッド</v>
       </c>
       <c r="E66">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3137,20 +3137,20 @@
         <v>4042</v>
       </c>
       <c r="C67">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C67,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ビー</v>
       </c>
       <c r="E67">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -3164,11 +3164,11 @@
         <v>4042</v>
       </c>
       <c r="C68">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C68,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ソード</v>
       </c>
       <c r="E68">
         <v>5</v>
@@ -3191,11 +3191,11 @@
         <v>4042</v>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C69,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E69">
         <v>5</v>
@@ -3204,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -3212,26 +3212,26 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>4101</v>
+        <v>4042</v>
       </c>
       <c r="B70">
-        <v>4101</v>
+        <v>4042</v>
       </c>
       <c r="C70">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="D70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C70,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E70">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -3239,23 +3239,23 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>4102</v>
+        <v>4042</v>
       </c>
       <c r="B71">
-        <v>4102</v>
+        <v>4042</v>
       </c>
       <c r="C71">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="D71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C71,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>ビー</v>
       </c>
       <c r="E71">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -3266,20 +3266,20 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
-        <v>5041</v>
+        <v>4101</v>
       </c>
       <c r="B72">
-        <v>5041</v>
+        <v>4101</v>
       </c>
       <c r="C72">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="D72" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C72,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>アンドラス</v>
       </c>
       <c r="E72">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -3293,26 +3293,26 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>5041</v>
+        <v>4102</v>
       </c>
       <c r="B73">
-        <v>5041</v>
+        <v>4102</v>
       </c>
       <c r="C73">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="D73" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C73,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>アンドラス</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -3333,13 +3333,13 @@
         <v>クリーパー</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -3353,11 +3353,11 @@
         <v>5041</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D75" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C75,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>クリーパー</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -3380,11 +3380,11 @@
         <v>5041</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C76,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>クリーパー</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -3401,23 +3401,23 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>5042</v>
+        <v>5041</v>
       </c>
       <c r="B77">
-        <v>5042</v>
+        <v>5041</v>
       </c>
       <c r="C77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C77,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E77">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -3428,26 +3428,26 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
-        <v>5042</v>
+        <v>5041</v>
       </c>
       <c r="B78">
-        <v>5042</v>
+        <v>5041</v>
       </c>
       <c r="C78">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C78,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E78">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F78">
         <v>0</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -3461,20 +3461,20 @@
         <v>5042</v>
       </c>
       <c r="C79">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C79,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E79">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -3488,11 +3488,11 @@
         <v>5042</v>
       </c>
       <c r="C80">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C80,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネームレス</v>
       </c>
       <c r="E80">
         <v>5</v>
@@ -3501,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -3515,11 +3515,11 @@
         <v>5042</v>
       </c>
       <c r="C81">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C81,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E81">
         <v>5</v>
@@ -3528,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -3536,26 +3536,26 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82">
-        <v>5101</v>
+        <v>5042</v>
       </c>
       <c r="B82">
-        <v>5101</v>
+        <v>5042</v>
       </c>
       <c r="C82">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C82,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>ウルフ</v>
       </c>
       <c r="E82">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -3563,20 +3563,20 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83">
-        <v>5101</v>
+        <v>5042</v>
       </c>
       <c r="B83">
-        <v>5101</v>
+        <v>5042</v>
       </c>
       <c r="C83">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C83,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E83">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -3596,20 +3596,20 @@
         <v>5101</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="D84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C84,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E84">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -3650,11 +3650,11 @@
         <v>5101</v>
       </c>
       <c r="C86">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C86,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E86">
         <v>10</v>
@@ -3671,26 +3671,26 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="B87">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="C87">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C87,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>シールド</v>
       </c>
       <c r="E87">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -3698,20 +3698,20 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="B88">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="C88">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C88,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>スクイッド</v>
       </c>
       <c r="E88">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -3731,20 +3731,20 @@
         <v>5102</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="D89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C89,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E89">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -3785,11 +3785,11 @@
         <v>5102</v>
       </c>
       <c r="C91">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C91,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E91">
         <v>20</v>
@@ -3806,26 +3806,26 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="B92">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="C92">
-        <v>1002</v>
+        <v>8</v>
       </c>
       <c r="D92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C92,[1]TextData!A:A))</f>
-        <v>エリザベート</v>
+        <v>シールド</v>
       </c>
       <c r="E92">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -3833,20 +3833,20 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="B93">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="C93">
-        <v>1003</v>
+        <v>11</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C93,[1]TextData!A:A))</f>
-        <v>アリエス</v>
+        <v>スクイッド</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -3866,17 +3866,17 @@
         <v>6021</v>
       </c>
       <c r="C94">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C94,[1]TextData!A:A))</f>
-        <v>シイナ</v>
+        <v>エリザベート</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -3893,11 +3893,11 @@
         <v>6021</v>
       </c>
       <c r="C95">
-        <v>8</v>
+        <v>1003</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C95,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>アリエス</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3920,11 +3920,11 @@
         <v>6021</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>1004</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C96,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>シイナ</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -3941,23 +3941,23 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="B97">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="C97">
-        <v>1011</v>
+        <v>8</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C97,[1]TextData!A:A))</f>
-        <v>セリナ</v>
+        <v>シールド</v>
       </c>
       <c r="E97">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -3968,17 +3968,17 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="B98">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="C98">
-        <v>1005</v>
+        <v>1</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C98,[1]TextData!A:A))</f>
-        <v>レダ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -4001,20 +4001,20 @@
         <v>6022</v>
       </c>
       <c r="C99">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C99,[1]TextData!A:A))</f>
-        <v>メリアドール</v>
+        <v>セリナ</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -4028,11 +4028,11 @@
         <v>6022</v>
       </c>
       <c r="C100">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C100,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>レダ</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -4055,11 +4055,11 @@
         <v>6022</v>
       </c>
       <c r="C101">
-        <v>14</v>
+        <v>1010</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C101,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>メリアドール</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -4068,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -4076,26 +4076,26 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="B102">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="C102">
-        <v>1001</v>
+        <v>10</v>
       </c>
       <c r="D102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C102,[1]TextData!A:A))</f>
-        <v>ミカ</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E102">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102">
         <v>0</v>
@@ -4103,17 +4103,17 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="B103">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="C103">
-        <v>1006</v>
+        <v>14</v>
       </c>
       <c r="D103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C103,[1]TextData!A:A))</f>
-        <v>リシェリ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -4136,17 +4136,17 @@
         <v>6031</v>
       </c>
       <c r="C104">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="D104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C104,[1]TextData!A:A))</f>
-        <v>マリーベル</v>
+        <v>ミカ</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -4163,11 +4163,11 @@
         <v>6031</v>
       </c>
       <c r="C105">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C105,[1]TextData!A:A))</f>
-        <v>ユニ</v>
+        <v>リシェリ</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -4190,11 +4190,11 @@
         <v>6031</v>
       </c>
       <c r="C106">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C106,[1]TextData!A:A))</f>
-        <v>ナツキ</v>
+        <v>マリーベル</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -4211,26 +4211,26 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="B107">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="C107">
-        <v>201</v>
+        <v>1007</v>
       </c>
       <c r="D107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C107,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>ユニ</v>
       </c>
       <c r="E107">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -4238,17 +4238,17 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="B108">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="C108">
-        <v>15</v>
+        <v>1009</v>
       </c>
       <c r="D108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C108,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ナツキ</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -4271,20 +4271,20 @@
         <v>6101</v>
       </c>
       <c r="C109">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C109,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>アンリマユ</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -4298,11 +4298,11 @@
         <v>6101</v>
       </c>
       <c r="C110">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C110,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ソード</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -4311,7 +4311,7 @@
         <v>0</v>
       </c>
       <c r="G110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -4325,22 +4325,76 @@
         <v>6101</v>
       </c>
       <c r="C111">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C111,[1]TextData!A:A))</f>
+        <v>スクイッド</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112">
+        <v>6101</v>
+      </c>
+      <c r="B112">
+        <v>6101</v>
+      </c>
+      <c r="C112">
+        <v>5</v>
+      </c>
+      <c r="D112" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C112,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113">
+        <v>6101</v>
+      </c>
+      <c r="B113">
+        <v>6101</v>
+      </c>
+      <c r="C113">
+        <v>13</v>
+      </c>
+      <c r="D113" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C113,[1]TextData!A:A))</f>
         <v>インプ</v>
       </c>
-      <c r="E111">
-        <v>0</v>
-      </c>
-      <c r="F111">
-        <v>0</v>
-      </c>
-      <c r="G111">
-        <v>1</v>
-      </c>
-      <c r="H111">
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>1</v>
+      </c>
+      <c r="H113">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,9 +48,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -62,68 +62,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -138,6 +79,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -145,7 +108,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -159,11 +129,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -184,23 +169,38 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,7 +215,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,25 +245,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,13 +275,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,7 +317,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -299,61 +359,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -365,19 +383,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,13 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,6 +420,63 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -449,63 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,16 +514,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -532,127 +532,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1340,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1673,23 +1673,23 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>1030</v>
+        <v>2010</v>
       </c>
       <c r="B13">
-        <v>1030</v>
+        <v>2010</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>アモン</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>1040</v>
+        <v>2010</v>
       </c>
       <c r="B14">
-        <v>1040</v>
+        <v>2010</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -1713,10 +1713,10 @@
         <v>ウルフ</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1727,17 +1727,17 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>1100</v>
+        <v>2041</v>
       </c>
       <c r="B15">
-        <v>1100</v>
+        <v>2041</v>
       </c>
       <c r="C15">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>ウルフ</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -1754,20 +1754,20 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>1110</v>
+        <v>2041</v>
       </c>
       <c r="B16">
-        <v>1110</v>
+        <v>2041</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C16,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>カースド</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1781,20 +1781,20 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>1120</v>
+        <v>2041</v>
       </c>
       <c r="B17">
-        <v>1120</v>
+        <v>2041</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D17" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C17,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1808,20 +1808,20 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B18">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スクイッド</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1835,10 +1835,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B19">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -1848,7 +1848,7 @@
         <v>カースド</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B20">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="C20">
         <v>14</v>
@@ -1875,7 +1875,7 @@
         <v>ゴーストアーマー</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1889,20 +1889,20 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>2042</v>
+        <v>2100</v>
       </c>
       <c r="B21">
-        <v>2042</v>
+        <v>2100</v>
       </c>
       <c r="C21">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="D21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C21,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ベリト</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1916,20 +1916,20 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>2042</v>
+        <v>2101</v>
       </c>
       <c r="B22">
-        <v>2042</v>
+        <v>2101</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1943,26 +1943,26 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>2042</v>
+        <v>2201</v>
       </c>
       <c r="B23">
-        <v>2042</v>
+        <v>2201</v>
       </c>
       <c r="C23">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ドライアド</v>
       </c>
       <c r="E23">
         <v>5</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1970,23 +1970,23 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>2100</v>
+        <v>2201</v>
       </c>
       <c r="B24">
-        <v>2100</v>
+        <v>2201</v>
       </c>
       <c r="C24">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>ウルフ</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>2101</v>
+        <v>2201</v>
       </c>
       <c r="B25">
-        <v>2101</v>
+        <v>2201</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -2037,16 +2037,16 @@
         <v>ドライアド</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2073,31 +2073,31 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B28">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>クロウ</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2105,17 +2105,17 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B29">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ビー</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2127,22 +2127,22 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B30">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2172,16 +2172,16 @@
         <v>クロウ</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2208,31 +2208,31 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="B33">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>シールド</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -2240,17 +2240,17 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="B34">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>サーチャー</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2262,22 +2262,22 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="B35">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>サーチャー</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2289,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2307,16 +2307,16 @@
         <v>シールド</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2343,31 +2343,31 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B38">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -2375,17 +2375,17 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B39">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="C39">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C39,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2397,22 +2397,22 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B40">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2442,16 +2442,16 @@
         <v>ネームレス</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2478,31 +2478,31 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="B43">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="C43">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D43" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C43,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -2510,17 +2510,17 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="B44">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="C44">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D44" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C44,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>カースド</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2532,22 +2532,22 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="B45">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="C45">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C45,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>カースド</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2577,16 +2577,16 @@
         <v>クリーパー</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2613,31 +2613,31 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="B48">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D48" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C48,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ネームレス</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -2645,17 +2645,17 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="B49">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="C49">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C49,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>インプ</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2667,22 +2667,22 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="B50">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2694,10 +2694,10 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="12" customHeight="1" spans="1:8">
       <c r="A51">
         <v>3041</v>
       </c>
@@ -2712,13 +2712,13 @@
         <v>ネームレス</v>
       </c>
       <c r="E51">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -2726,23 +2726,23 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="B52">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="C52">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C52,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>カースド</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2753,20 +2753,20 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="B53">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="C53">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C53,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2778,22 +2778,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" ht="12" customHeight="1" spans="1:8">
+    <row r="54" spans="1:8">
       <c r="A54">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="B54">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="C54">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D54" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C54,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>サーチャー</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2813,17 +2813,17 @@
         <v>3042</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C55,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>クリーパー</v>
       </c>
       <c r="E55">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -2834,26 +2834,26 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>3042</v>
+        <v>3100</v>
       </c>
       <c r="B56">
-        <v>3042</v>
+        <v>3100</v>
       </c>
       <c r="C56">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="D56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C56,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>パイモン</v>
       </c>
       <c r="E56">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -2861,17 +2861,17 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>3042</v>
+        <v>3101</v>
       </c>
       <c r="B57">
-        <v>3042</v>
+        <v>3101</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C57,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E57">
         <v>5</v>
@@ -2888,17 +2888,17 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>3042</v>
+        <v>3101</v>
       </c>
       <c r="B58">
-        <v>3042</v>
+        <v>3101</v>
       </c>
       <c r="C58">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D58" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C58,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>クロウ</v>
       </c>
       <c r="E58">
         <v>5</v>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -2915,26 +2915,26 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>3100</v>
+        <v>4041</v>
       </c>
       <c r="B59">
-        <v>3100</v>
+        <v>4041</v>
       </c>
       <c r="C59">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="D59" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C59,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>シールド</v>
       </c>
       <c r="E59">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>3101</v>
+        <v>4041</v>
       </c>
       <c r="B60">
-        <v>3101</v>
+        <v>4041</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -2955,7 +2955,7 @@
         <v>ネレイドジェム</v>
       </c>
       <c r="E60">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2969,26 +2969,26 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>3101</v>
+        <v>4041</v>
       </c>
       <c r="B61">
-        <v>3101</v>
+        <v>4041</v>
       </c>
       <c r="C61">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D61" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C61,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E61">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -3002,17 +3002,17 @@
         <v>4041</v>
       </c>
       <c r="C62">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C62,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>スクイッド</v>
       </c>
       <c r="E62">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -3029,11 +3029,11 @@
         <v>4041</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D63" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C63,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スクイッド</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -3050,26 +3050,26 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="B64">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C64,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ビー</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -3077,20 +3077,20 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="B65">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="C65">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C65,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ソード</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3104,20 +3104,20 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="B66">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="C66">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C66,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3137,20 +3137,20 @@
         <v>4042</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C67,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E67">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -3164,11 +3164,11 @@
         <v>4042</v>
       </c>
       <c r="C68">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C68,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ビー</v>
       </c>
       <c r="E68">
         <v>5</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -3185,26 +3185,26 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>4042</v>
+        <v>4101</v>
       </c>
       <c r="B69">
-        <v>4042</v>
+        <v>4101</v>
       </c>
       <c r="C69">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="D69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C69,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>アンドラス</v>
       </c>
       <c r="E69">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -3212,26 +3212,26 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>4042</v>
+        <v>4102</v>
       </c>
       <c r="B70">
-        <v>4042</v>
+        <v>4102</v>
       </c>
       <c r="C70">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="D70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C70,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>アンドラス</v>
       </c>
       <c r="E70">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -3239,23 +3239,23 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>4042</v>
+        <v>5041</v>
       </c>
       <c r="B71">
-        <v>4042</v>
+        <v>5041</v>
       </c>
       <c r="C71">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C71,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E71">
         <v>5</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -3266,26 +3266,26 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
-        <v>4101</v>
+        <v>5041</v>
       </c>
       <c r="B72">
-        <v>4101</v>
+        <v>5041</v>
       </c>
       <c r="C72">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="D72" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C72,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>クリーパー</v>
       </c>
       <c r="E72">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -3293,26 +3293,26 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>4102</v>
+        <v>5041</v>
       </c>
       <c r="B73">
-        <v>4102</v>
+        <v>5041</v>
       </c>
       <c r="C73">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="D73" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C73,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>クリーパー</v>
       </c>
       <c r="E73">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -3326,20 +3326,20 @@
         <v>5041</v>
       </c>
       <c r="C74">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C74,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E74">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -3353,11 +3353,11 @@
         <v>5041</v>
       </c>
       <c r="C75">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D75" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C75,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -3374,23 +3374,23 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="B76">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="C76">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C76,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -3401,26 +3401,26 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="B77">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C77,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ネームレス</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F77">
         <v>0</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -3428,26 +3428,26 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="B78">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C78,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F78">
         <v>0</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -3468,10 +3468,10 @@
         <v>ウルフ</v>
       </c>
       <c r="E79">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -3488,11 +3488,11 @@
         <v>5042</v>
       </c>
       <c r="C80">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C80,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ウルフ</v>
       </c>
       <c r="E80">
         <v>5</v>
@@ -3501,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -3509,23 +3509,23 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81">
-        <v>5042</v>
+        <v>5101</v>
       </c>
       <c r="B81">
-        <v>5042</v>
+        <v>5101</v>
       </c>
       <c r="C81">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="D81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C81,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E81">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -3536,20 +3536,20 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82">
-        <v>5042</v>
+        <v>5101</v>
       </c>
       <c r="B82">
-        <v>5042</v>
+        <v>5101</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C82,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>シールド</v>
       </c>
       <c r="E82">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -3563,20 +3563,20 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83">
-        <v>5042</v>
+        <v>5101</v>
       </c>
       <c r="B83">
-        <v>5042</v>
+        <v>5101</v>
       </c>
       <c r="C83">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C83,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E83">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -3596,20 +3596,20 @@
         <v>5101</v>
       </c>
       <c r="C84">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C84,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>シールド</v>
       </c>
       <c r="E84">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -3623,11 +3623,11 @@
         <v>5101</v>
       </c>
       <c r="C85">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C85,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>スクイッド</v>
       </c>
       <c r="E85">
         <v>10</v>
@@ -3644,26 +3644,26 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="B86">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="D86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C86,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E86">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="B87">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="C87">
         <v>8</v>
@@ -3684,7 +3684,7 @@
         <v>シールド</v>
       </c>
       <c r="E87">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -3698,20 +3698,20 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="B88">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="C88">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C88,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E88">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -3731,20 +3731,20 @@
         <v>5102</v>
       </c>
       <c r="C89">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C89,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>シールド</v>
       </c>
       <c r="E89">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -3758,11 +3758,11 @@
         <v>5102</v>
       </c>
       <c r="C90">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C90,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>スクイッド</v>
       </c>
       <c r="E90">
         <v>20</v>
@@ -3779,26 +3779,26 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="B91">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="D91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C91,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>エリザベート</v>
       </c>
       <c r="E91">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -3806,20 +3806,20 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="B92">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="C92">
-        <v>8</v>
+        <v>1003</v>
       </c>
       <c r="D92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C92,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>アリエス</v>
       </c>
       <c r="E92">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -3833,26 +3833,26 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="B93">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="C93">
-        <v>11</v>
+        <v>1004</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C93,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>シイナ</v>
       </c>
       <c r="E93">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F93">
         <v>0</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -3866,20 +3866,20 @@
         <v>6021</v>
       </c>
       <c r="C94">
-        <v>1002</v>
+        <v>8</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C94,[1]TextData!A:A))</f>
-        <v>エリザベート</v>
+        <v>シールド</v>
       </c>
       <c r="E94">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -3893,11 +3893,11 @@
         <v>6021</v>
       </c>
       <c r="C95">
-        <v>1003</v>
+        <v>1</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C95,[1]TextData!A:A))</f>
-        <v>アリエス</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3914,26 +3914,26 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="B96">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="C96">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C96,[1]TextData!A:A))</f>
-        <v>シイナ</v>
+        <v>セリナ</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -3941,17 +3941,17 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="B97">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="C97">
-        <v>8</v>
+        <v>1005</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C97,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>レダ</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3968,17 +3968,17 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="B98">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C98,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>メリアドール</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -4001,20 +4001,20 @@
         <v>6022</v>
       </c>
       <c r="C99">
-        <v>1011</v>
+        <v>10</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C99,[1]TextData!A:A))</f>
-        <v>セリナ</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E99">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -4028,11 +4028,11 @@
         <v>6022</v>
       </c>
       <c r="C100">
-        <v>1005</v>
+        <v>14</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C100,[1]TextData!A:A))</f>
-        <v>レダ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -4049,26 +4049,26 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="B101">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="C101">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C101,[1]TextData!A:A))</f>
-        <v>メリアドール</v>
+        <v>ミカ</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -4076,17 +4076,17 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="B102">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="C102">
-        <v>10</v>
+        <v>1006</v>
       </c>
       <c r="D102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C102,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>リシェリ</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="G102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102">
         <v>0</v>
@@ -4103,17 +4103,17 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="B103">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="C103">
-        <v>14</v>
+        <v>1008</v>
       </c>
       <c r="D103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C103,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>マリーベル</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -4136,17 +4136,17 @@
         <v>6031</v>
       </c>
       <c r="C104">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="D104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C104,[1]TextData!A:A))</f>
-        <v>ミカ</v>
+        <v>ユニ</v>
       </c>
       <c r="E104">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -4163,11 +4163,11 @@
         <v>6031</v>
       </c>
       <c r="C105">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C105,[1]TextData!A:A))</f>
-        <v>リシェリ</v>
+        <v>ナツキ</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -4184,26 +4184,26 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="B106">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="C106">
-        <v>1008</v>
+        <v>201</v>
       </c>
       <c r="D106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C106,[1]TextData!A:A))</f>
-        <v>マリーベル</v>
+        <v>アンリマユ</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -4211,17 +4211,17 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="B107">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="C107">
-        <v>1007</v>
+        <v>15</v>
       </c>
       <c r="D107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C107,[1]TextData!A:A))</f>
-        <v>ユニ</v>
+        <v>ソード</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -4238,17 +4238,17 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="B108">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="C108">
-        <v>1009</v>
+        <v>11</v>
       </c>
       <c r="D108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C108,[1]TextData!A:A))</f>
-        <v>ナツキ</v>
+        <v>スクイッド</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -4271,17 +4271,17 @@
         <v>6101</v>
       </c>
       <c r="C109">
-        <v>201</v>
+        <v>5</v>
       </c>
       <c r="D109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C109,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>クロウ</v>
       </c>
       <c r="E109">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -4298,11 +4298,11 @@
         <v>6101</v>
       </c>
       <c r="C110">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C110,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>インプ</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -4311,90 +4311,9 @@
         <v>0</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
-      <c r="A111">
-        <v>6101</v>
-      </c>
-      <c r="B111">
-        <v>6101</v>
-      </c>
-      <c r="C111">
-        <v>11</v>
-      </c>
-      <c r="D111" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C111,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
-      </c>
-      <c r="E111">
-        <v>0</v>
-      </c>
-      <c r="F111">
-        <v>0</v>
-      </c>
-      <c r="G111">
-        <v>0</v>
-      </c>
-      <c r="H111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
-      <c r="A112">
-        <v>6101</v>
-      </c>
-      <c r="B112">
-        <v>6101</v>
-      </c>
-      <c r="C112">
-        <v>5</v>
-      </c>
-      <c r="D112" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C112,[1]TextData!A:A))</f>
-        <v>クロウ</v>
-      </c>
-      <c r="E112">
-        <v>0</v>
-      </c>
-      <c r="F112">
-        <v>0</v>
-      </c>
-      <c r="G112">
-        <v>1</v>
-      </c>
-      <c r="H112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
-      <c r="A113">
-        <v>6101</v>
-      </c>
-      <c r="B113">
-        <v>6101</v>
-      </c>
-      <c r="C113">
-        <v>13</v>
-      </c>
-      <c r="D113" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C113,[1]TextData!A:A))</f>
-        <v>インプ</v>
-      </c>
-      <c r="E113">
-        <v>0</v>
-      </c>
-      <c r="F113">
-        <v>0</v>
-      </c>
-      <c r="G113">
-        <v>1</v>
-      </c>
-      <c r="H113">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -62,46 +62,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -121,16 +83,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -144,11 +98,48 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -169,6 +160,30 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -177,15 +192,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -193,14 +201,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,25 +215,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,13 +245,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -269,37 +275,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -317,19 +311,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -347,7 +359,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,43 +389,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,6 +406,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -433,24 +448,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -466,17 +463,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,7 +514,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -523,7 +523,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -532,127 +532,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1340,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>2010</v>
+        <v>2041</v>
       </c>
       <c r="B14">
-        <v>2010</v>
+        <v>2041</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -1716,7 +1716,7 @@
         <v>5</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1733,17 +1733,17 @@
         <v>2041</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>カースド</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1760,11 +1760,11 @@
         <v>2041</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C16,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1781,23 +1781,23 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B17">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="C17">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D17" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C17,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スクイッド</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1814,17 +1814,17 @@
         <v>2042</v>
       </c>
       <c r="C18">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>カースド</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1841,11 +1841,11 @@
         <v>2042</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -1862,23 +1862,23 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>2042</v>
+        <v>2100</v>
       </c>
       <c r="B20">
-        <v>2042</v>
+        <v>2100</v>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ベリト</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1889,23 +1889,23 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B21">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="C21">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="D21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C21,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>ウルフ</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1916,26 +1916,26 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>2101</v>
+        <v>2201</v>
       </c>
       <c r="B22">
-        <v>2101</v>
+        <v>2201</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ドライアド</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1949,20 +1949,20 @@
         <v>2201</v>
       </c>
       <c r="C23">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -2003,11 +2003,11 @@
         <v>2201</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D25" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C25,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ドライアド</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -2030,11 +2030,11 @@
         <v>2201</v>
       </c>
       <c r="C26">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2046,34 +2046,34 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B27">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>クロウ</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -2084,20 +2084,20 @@
         <v>2202</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ビー</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2138,11 +2138,11 @@
         <v>2202</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>クロウ</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2165,11 +2165,11 @@
         <v>2202</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ビー</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2181,34 +2181,34 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="B32">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>シールド</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2219,20 +2219,20 @@
         <v>2203</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>サーチャー</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -2273,11 +2273,11 @@
         <v>2203</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>シールド</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2289,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2300,11 +2300,11 @@
         <v>2203</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>サーチャー</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2316,34 +2316,34 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B37">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -2354,20 +2354,20 @@
         <v>2204</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -2408,11 +2408,11 @@
         <v>2204</v>
       </c>
       <c r="C40">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2435,11 +2435,11 @@
         <v>2204</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2451,34 +2451,34 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="B42">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="C42">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2489,20 +2489,20 @@
         <v>2205</v>
       </c>
       <c r="C43">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D43" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C43,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>カースド</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -2543,11 +2543,11 @@
         <v>2205</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C45,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>クリーパー</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2570,11 +2570,11 @@
         <v>2205</v>
       </c>
       <c r="C46">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C46,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>カースド</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2586,34 +2586,34 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="B47">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ネームレス</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2624,20 +2624,20 @@
         <v>3041</v>
       </c>
       <c r="C48">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D48" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C48,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>インプ</v>
       </c>
       <c r="E48">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -2651,11 +2651,11 @@
         <v>3041</v>
       </c>
       <c r="C49">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C49,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" ht="12" customHeight="1" spans="1:8">
       <c r="A50">
         <v>3041</v>
       </c>
@@ -2678,11 +2678,11 @@
         <v>3041</v>
       </c>
       <c r="C50">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2697,25 +2697,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" ht="12" customHeight="1" spans="1:8">
+    <row r="51" spans="1:8">
       <c r="A51">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="B51">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>カースド</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2732,17 +2732,17 @@
         <v>3042</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C52,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>クリーパー</v>
       </c>
       <c r="E52">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2759,11 +2759,11 @@
         <v>3042</v>
       </c>
       <c r="C53">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C53,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>サーチャー</v>
       </c>
       <c r="E53">
         <v>5</v>
@@ -2786,11 +2786,11 @@
         <v>3042</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D54" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C54,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E54">
         <v>5</v>
@@ -2807,26 +2807,26 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>3042</v>
+        <v>3100</v>
       </c>
       <c r="B55">
-        <v>3042</v>
+        <v>3100</v>
       </c>
       <c r="C55">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="D55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C55,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>パイモン</v>
       </c>
       <c r="E55">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -2834,26 +2834,26 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="B56">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="C56">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="D56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C56,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E56">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -2867,11 +2867,11 @@
         <v>3101</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C57,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>クロウ</v>
       </c>
       <c r="E57">
         <v>5</v>
@@ -2880,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -2888,26 +2888,26 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>3101</v>
+        <v>4041</v>
       </c>
       <c r="B58">
-        <v>3101</v>
+        <v>4041</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D58" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C58,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>シールド</v>
       </c>
       <c r="E58">
         <v>5</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -2921,17 +2921,17 @@
         <v>4041</v>
       </c>
       <c r="C59">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D59" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C59,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E59">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -2975,11 +2975,11 @@
         <v>4041</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D61" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C61,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スクイッド</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -3023,26 +3023,26 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="B63">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="C63">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D63" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C63,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ビー</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -3056,20 +3056,20 @@
         <v>4042</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C64,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ソード</v>
       </c>
       <c r="E64">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -3083,11 +3083,11 @@
         <v>4042</v>
       </c>
       <c r="C65">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C65,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E65">
         <v>5</v>
@@ -3137,11 +3137,11 @@
         <v>4042</v>
       </c>
       <c r="C67">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C67,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ビー</v>
       </c>
       <c r="E67">
         <v>5</v>
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -3158,23 +3158,23 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>4042</v>
+        <v>4101</v>
       </c>
       <c r="B68">
-        <v>4042</v>
+        <v>4101</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C68,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>アンドラス</v>
       </c>
       <c r="E68">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -3185,10 +3185,10 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>4101</v>
+        <v>4102</v>
       </c>
       <c r="B69">
-        <v>4101</v>
+        <v>4102</v>
       </c>
       <c r="C69">
         <v>104</v>
@@ -3198,7 +3198,7 @@
         <v>アンドラス</v>
       </c>
       <c r="E69">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F69">
         <v>1</v>
@@ -3212,20 +3212,20 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>4102</v>
+        <v>5041</v>
       </c>
       <c r="B70">
-        <v>4102</v>
+        <v>5041</v>
       </c>
       <c r="C70">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="D70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C70,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>クリーパー</v>
       </c>
       <c r="E70">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -3252,13 +3252,13 @@
         <v>クリーパー</v>
       </c>
       <c r="E71">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -3299,11 +3299,11 @@
         <v>5041</v>
       </c>
       <c r="C73">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D73" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C73,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -3347,23 +3347,23 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="B75">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D75" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C75,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ウルフ</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -3380,20 +3380,20 @@
         <v>5042</v>
       </c>
       <c r="C76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C76,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネームレス</v>
       </c>
       <c r="E76">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -3407,11 +3407,11 @@
         <v>5042</v>
       </c>
       <c r="C77">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C77,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E77">
         <v>5</v>
@@ -3434,11 +3434,11 @@
         <v>5042</v>
       </c>
       <c r="C78">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C78,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E78">
         <v>5</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -3482,26 +3482,26 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
-        <v>5042</v>
+        <v>5101</v>
       </c>
       <c r="B80">
-        <v>5042</v>
+        <v>5101</v>
       </c>
       <c r="C80">
-        <v>4</v>
+        <v>105</v>
       </c>
       <c r="D80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C80,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E80">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -3515,20 +3515,20 @@
         <v>5101</v>
       </c>
       <c r="C81">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C81,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>シールド</v>
       </c>
       <c r="E81">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -3542,11 +3542,11 @@
         <v>5101</v>
       </c>
       <c r="C82">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C82,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E82">
         <v>10</v>
@@ -3569,11 +3569,11 @@
         <v>5101</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C83,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>シールド</v>
       </c>
       <c r="E83">
         <v>10</v>
@@ -3596,11 +3596,11 @@
         <v>5101</v>
       </c>
       <c r="C84">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C84,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>スクイッド</v>
       </c>
       <c r="E84">
         <v>10</v>
@@ -3617,26 +3617,26 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="B85">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="C85">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="D85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C85,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E85">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -3650,20 +3650,20 @@
         <v>5102</v>
       </c>
       <c r="C86">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C86,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>シールド</v>
       </c>
       <c r="E86">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -3677,11 +3677,11 @@
         <v>5102</v>
       </c>
       <c r="C87">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C87,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E87">
         <v>20</v>
@@ -3704,11 +3704,11 @@
         <v>5102</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C88,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>シールド</v>
       </c>
       <c r="E88">
         <v>20</v>
@@ -3731,11 +3731,11 @@
         <v>5102</v>
       </c>
       <c r="C89">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C89,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>スクイッド</v>
       </c>
       <c r="E89">
         <v>20</v>
@@ -3752,26 +3752,26 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="B90">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="C90">
-        <v>11</v>
+        <v>1002</v>
       </c>
       <c r="D90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C90,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>エリザベート</v>
       </c>
       <c r="E90">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -3785,20 +3785,20 @@
         <v>6021</v>
       </c>
       <c r="C91">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C91,[1]TextData!A:A))</f>
-        <v>エリザベート</v>
+        <v>アリエス</v>
       </c>
       <c r="E91">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -3812,11 +3812,11 @@
         <v>6021</v>
       </c>
       <c r="C92">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C92,[1]TextData!A:A))</f>
-        <v>アリエス</v>
+        <v>シイナ</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -3839,11 +3839,11 @@
         <v>6021</v>
       </c>
       <c r="C93">
-        <v>1004</v>
+        <v>8</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C93,[1]TextData!A:A))</f>
-        <v>シイナ</v>
+        <v>シールド</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3852,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -3866,11 +3866,11 @@
         <v>6021</v>
       </c>
       <c r="C94">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C94,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3887,23 +3887,23 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="B95">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>1011</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C95,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>セリナ</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -3920,17 +3920,17 @@
         <v>6022</v>
       </c>
       <c r="C96">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C96,[1]TextData!A:A))</f>
-        <v>セリナ</v>
+        <v>レダ</v>
       </c>
       <c r="E96">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -3947,11 +3947,11 @@
         <v>6022</v>
       </c>
       <c r="C97">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C97,[1]TextData!A:A))</f>
-        <v>レダ</v>
+        <v>メリアドール</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3960,7 +3960,7 @@
         <v>0</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -3974,11 +3974,11 @@
         <v>6022</v>
       </c>
       <c r="C98">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C98,[1]TextData!A:A))</f>
-        <v>メリアドール</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -4001,11 +4001,11 @@
         <v>6022</v>
       </c>
       <c r="C99">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C99,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -4014,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -4022,23 +4022,23 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="B100">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="C100">
-        <v>14</v>
+        <v>1001</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C100,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ミカ</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -4055,17 +4055,17 @@
         <v>6031</v>
       </c>
       <c r="C101">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C101,[1]TextData!A:A))</f>
-        <v>ミカ</v>
+        <v>リシェリ</v>
       </c>
       <c r="E101">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -4082,11 +4082,11 @@
         <v>6031</v>
       </c>
       <c r="C102">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="D102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C102,[1]TextData!A:A))</f>
-        <v>リシェリ</v>
+        <v>マリーベル</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -4109,11 +4109,11 @@
         <v>6031</v>
       </c>
       <c r="C103">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C103,[1]TextData!A:A))</f>
-        <v>マリーベル</v>
+        <v>ユニ</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -4136,11 +4136,11 @@
         <v>6031</v>
       </c>
       <c r="C104">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="D104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C104,[1]TextData!A:A))</f>
-        <v>ユニ</v>
+        <v>ナツキ</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -4157,26 +4157,26 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="B105">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="C105">
-        <v>1009</v>
+        <v>201</v>
       </c>
       <c r="D105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C105,[1]TextData!A:A))</f>
-        <v>ナツキ</v>
+        <v>アンリマユ</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -4190,20 +4190,20 @@
         <v>6101</v>
       </c>
       <c r="C106">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="D106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C106,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>ソード</v>
       </c>
       <c r="E106">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -4217,11 +4217,11 @@
         <v>6101</v>
       </c>
       <c r="C107">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C107,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>スクイッド</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -4244,11 +4244,11 @@
         <v>6101</v>
       </c>
       <c r="C108">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C108,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>クロウ</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -4271,11 +4271,11 @@
         <v>6101</v>
       </c>
       <c r="C109">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C109,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>インプ</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -4287,33 +4287,6 @@
         <v>1</v>
       </c>
       <c r="H109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
-      <c r="A110">
-        <v>6101</v>
-      </c>
-      <c r="B110">
-        <v>6101</v>
-      </c>
-      <c r="C110">
-        <v>13</v>
-      </c>
-      <c r="D110" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C110,[1]TextData!A:A))</f>
-        <v>インプ</v>
-      </c>
-      <c r="E110">
-        <v>0</v>
-      </c>
-      <c r="F110">
-        <v>0</v>
-      </c>
-      <c r="G110">
-        <v>1</v>
-      </c>
-      <c r="H110">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -59,13 +59,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -83,45 +76,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -137,7 +93,44 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -152,40 +145,16 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -200,9 +169,40 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -215,7 +215,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,13 +269,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,43 +323,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -293,73 +335,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,13 +359,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,6 +381,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -409,17 +409,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -435,15 +429,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -465,9 +450,35 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -495,17 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -63,12 +63,42 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -84,9 +114,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -99,17 +167,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -121,9 +183,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -138,71 +200,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -215,7 +215,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,7 +275,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -239,37 +311,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -281,43 +359,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -329,13 +371,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -347,25 +383,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,24 +399,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -406,15 +406,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -433,6 +424,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -444,17 +455,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1340,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1679,17 +1679,17 @@
         <v>2010</v>
       </c>
       <c r="C13">
-        <v>101</v>
+        <v>3</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>ビー</v>
       </c>
       <c r="E13">
         <v>5</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1700,17 +1700,17 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>2041</v>
+        <v>2010</v>
       </c>
       <c r="B14">
-        <v>2041</v>
+        <v>2010</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C14,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>クロウ</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -1727,20 +1727,20 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>2041</v>
+        <v>2010</v>
       </c>
       <c r="B15">
-        <v>2041</v>
+        <v>2010</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ドライアド</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1760,17 +1760,17 @@
         <v>2041</v>
       </c>
       <c r="C16">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C16,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1781,23 +1781,23 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B17">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D17" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C17,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>カースド</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1808,20 +1808,20 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B18">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1841,17 +1841,17 @@
         <v>2042</v>
       </c>
       <c r="C19">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スクイッド</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1862,23 +1862,23 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>2100</v>
+        <v>2042</v>
       </c>
       <c r="B20">
-        <v>2100</v>
+        <v>2042</v>
       </c>
       <c r="C20">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>カースド</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1889,20 +1889,20 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>2101</v>
+        <v>2042</v>
       </c>
       <c r="B21">
-        <v>2101</v>
+        <v>2042</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C21,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1916,26 +1916,26 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>2201</v>
+        <v>2100</v>
       </c>
       <c r="B22">
-        <v>2201</v>
+        <v>2100</v>
       </c>
       <c r="C22">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ベリト</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="B23">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -1976,20 +1976,20 @@
         <v>2201</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ドライアド</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -2003,11 +2003,11 @@
         <v>2201</v>
       </c>
       <c r="C25">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D25" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C25,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -2046,49 +2046,49 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="B27">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ドライアド</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="B28">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2111,20 +2111,20 @@
         <v>2202</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>クロウ</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2138,11 +2138,11 @@
         <v>2202</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ビー</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2181,49 +2181,49 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="B32">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>クロウ</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="B33">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ビー</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2246,20 +2246,20 @@
         <v>2203</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>シールド</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2273,11 +2273,11 @@
         <v>2203</v>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>サーチャー</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2289,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2316,49 +2316,49 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="B37">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>シールド</v>
       </c>
       <c r="E37">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="B38">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="C38">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>サーチャー</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2381,20 +2381,20 @@
         <v>2204</v>
       </c>
       <c r="C39">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C39,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -2408,11 +2408,11 @@
         <v>2204</v>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2451,49 +2451,49 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="B42">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C42">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="B43">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D43" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C43,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -2505,7 +2505,7 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2516,20 +2516,20 @@
         <v>2205</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D44" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C44,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>クリーパー</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -2543,11 +2543,11 @@
         <v>2205</v>
       </c>
       <c r="C45">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C45,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>カースド</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2586,49 +2586,49 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>3041</v>
+        <v>2205</v>
       </c>
       <c r="B47">
-        <v>3041</v>
+        <v>2205</v>
       </c>
       <c r="C47">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>クリーパー</v>
       </c>
       <c r="E47">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>3041</v>
+        <v>2205</v>
       </c>
       <c r="B48">
-        <v>3041</v>
+        <v>2205</v>
       </c>
       <c r="C48">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D48" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C48,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>カースド</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2651,26 +2651,26 @@
         <v>3041</v>
       </c>
       <c r="C49">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C49,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49">
         <v>0</v>
       </c>
     </row>
-    <row r="50" ht="12" customHeight="1" spans="1:8">
+    <row r="50" spans="1:8">
       <c r="A50">
         <v>3041</v>
       </c>
@@ -2678,11 +2678,11 @@
         <v>3041</v>
       </c>
       <c r="C50">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>インプ</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2699,23 +2699,23 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="B51">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E51">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2724,22 +2724,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" ht="12" customHeight="1" spans="1:8">
       <c r="A52">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="B52">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="C52">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C52,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E52">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2759,17 +2759,17 @@
         <v>3042</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C53,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>カースド</v>
       </c>
       <c r="E53">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2807,26 +2807,26 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>3100</v>
+        <v>3042</v>
       </c>
       <c r="B55">
-        <v>3100</v>
+        <v>3042</v>
       </c>
       <c r="C55">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="D55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C55,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>サーチャー</v>
       </c>
       <c r="E55">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -2834,17 +2834,17 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>3101</v>
+        <v>3042</v>
       </c>
       <c r="B56">
-        <v>3101</v>
+        <v>3042</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C56,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>クリーパー</v>
       </c>
       <c r="E56">
         <v>5</v>
@@ -2861,23 +2861,23 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="B57">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="C57">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C57,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>パイモン</v>
       </c>
       <c r="E57">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -2888,23 +2888,23 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>4041</v>
+        <v>3101</v>
       </c>
       <c r="B58">
-        <v>4041</v>
+        <v>3101</v>
       </c>
       <c r="C58">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D58" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C58,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E58">
         <v>5</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -2915,26 +2915,26 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>4041</v>
+        <v>3101</v>
       </c>
       <c r="B59">
-        <v>4041</v>
+        <v>3101</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D59" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C59,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>クロウ</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -2948,17 +2948,17 @@
         <v>4041</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C60,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>シールド</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -2975,11 +2975,11 @@
         <v>4041</v>
       </c>
       <c r="C61">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D61" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C61,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -3002,11 +3002,11 @@
         <v>4041</v>
       </c>
       <c r="C62">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C62,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3023,26 +3023,26 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="B63">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D63" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C63,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>スクイッド</v>
       </c>
       <c r="E63">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -3050,20 +3050,20 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="B64">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="C64">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C64,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>スクイッド</v>
       </c>
       <c r="E64">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3083,20 +3083,20 @@
         <v>4042</v>
       </c>
       <c r="C65">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C65,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ビー</v>
       </c>
       <c r="E65">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -3110,11 +3110,11 @@
         <v>4042</v>
       </c>
       <c r="C66">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C66,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ソード</v>
       </c>
       <c r="E66">
         <v>5</v>
@@ -3137,11 +3137,11 @@
         <v>4042</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C67,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E67">
         <v>5</v>
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -3158,26 +3158,26 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>4101</v>
+        <v>4042</v>
       </c>
       <c r="B68">
-        <v>4101</v>
+        <v>4042</v>
       </c>
       <c r="C68">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C68,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E68">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -3185,23 +3185,23 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>4102</v>
+        <v>4042</v>
       </c>
       <c r="B69">
-        <v>4102</v>
+        <v>4042</v>
       </c>
       <c r="C69">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="D69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C69,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>ビー</v>
       </c>
       <c r="E69">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -3212,20 +3212,20 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>5041</v>
+        <v>4101</v>
       </c>
       <c r="B70">
-        <v>5041</v>
+        <v>4101</v>
       </c>
       <c r="C70">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="D70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C70,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>アンドラス</v>
       </c>
       <c r="E70">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -3239,26 +3239,26 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>5041</v>
+        <v>4102</v>
       </c>
       <c r="B71">
-        <v>5041</v>
+        <v>4102</v>
       </c>
       <c r="C71">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="D71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C71,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>アンドラス</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -3279,13 +3279,13 @@
         <v>クリーパー</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -3299,11 +3299,11 @@
         <v>5041</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D73" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C73,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>クリーパー</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -3326,11 +3326,11 @@
         <v>5041</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C74,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>クリーパー</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -3347,23 +3347,23 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>5042</v>
+        <v>5041</v>
       </c>
       <c r="B75">
-        <v>5042</v>
+        <v>5041</v>
       </c>
       <c r="C75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D75" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C75,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E75">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -3374,26 +3374,26 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>5042</v>
+        <v>5041</v>
       </c>
       <c r="B76">
-        <v>5042</v>
+        <v>5041</v>
       </c>
       <c r="C76">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C76,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E76">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -3407,20 +3407,20 @@
         <v>5042</v>
       </c>
       <c r="C77">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C77,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E77">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -3434,11 +3434,11 @@
         <v>5042</v>
       </c>
       <c r="C78">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C78,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネームレス</v>
       </c>
       <c r="E78">
         <v>5</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -3461,11 +3461,11 @@
         <v>5042</v>
       </c>
       <c r="C79">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C79,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E79">
         <v>5</v>
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -3482,26 +3482,26 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
-        <v>5101</v>
+        <v>5042</v>
       </c>
       <c r="B80">
-        <v>5101</v>
+        <v>5042</v>
       </c>
       <c r="C80">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="D80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C80,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>ウルフ</v>
       </c>
       <c r="E80">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -3509,20 +3509,20 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81">
-        <v>5101</v>
+        <v>5042</v>
       </c>
       <c r="B81">
-        <v>5101</v>
+        <v>5042</v>
       </c>
       <c r="C81">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C81,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E81">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -3542,20 +3542,20 @@
         <v>5101</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C82,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E82">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -3596,11 +3596,11 @@
         <v>5101</v>
       </c>
       <c r="C84">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C84,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E84">
         <v>10</v>
@@ -3617,26 +3617,26 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="B85">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="C85">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C85,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>シールド</v>
       </c>
       <c r="E85">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -3644,20 +3644,20 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="B86">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="C86">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C86,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>スクイッド</v>
       </c>
       <c r="E86">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -3677,20 +3677,20 @@
         <v>5102</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="D87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C87,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E87">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -3731,11 +3731,11 @@
         <v>5102</v>
       </c>
       <c r="C89">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C89,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E89">
         <v>20</v>
@@ -3752,26 +3752,26 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="B90">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="C90">
-        <v>1002</v>
+        <v>8</v>
       </c>
       <c r="D90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C90,[1]TextData!A:A))</f>
-        <v>エリザベート</v>
+        <v>シールド</v>
       </c>
       <c r="E90">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -3779,20 +3779,20 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="B91">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="C91">
-        <v>1003</v>
+        <v>11</v>
       </c>
       <c r="D91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C91,[1]TextData!A:A))</f>
-        <v>アリエス</v>
+        <v>スクイッド</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -3812,17 +3812,17 @@
         <v>6021</v>
       </c>
       <c r="C92">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="D92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C92,[1]TextData!A:A))</f>
-        <v>シイナ</v>
+        <v>エリザベート</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -3839,11 +3839,11 @@
         <v>6021</v>
       </c>
       <c r="C93">
-        <v>8</v>
+        <v>1003</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C93,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>アリエス</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3866,11 +3866,11 @@
         <v>6021</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>1004</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C94,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>シイナ</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3879,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -3887,23 +3887,23 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="B95">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="C95">
-        <v>1011</v>
+        <v>8</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C95,[1]TextData!A:A))</f>
-        <v>セリナ</v>
+        <v>シールド</v>
       </c>
       <c r="E95">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -3914,17 +3914,17 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="B96">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="C96">
-        <v>1005</v>
+        <v>1</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C96,[1]TextData!A:A))</f>
-        <v>レダ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3947,20 +3947,20 @@
         <v>6022</v>
       </c>
       <c r="C97">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C97,[1]TextData!A:A))</f>
-        <v>メリアドール</v>
+        <v>セリナ</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -3974,11 +3974,11 @@
         <v>6022</v>
       </c>
       <c r="C98">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C98,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>レダ</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -4001,11 +4001,11 @@
         <v>6022</v>
       </c>
       <c r="C99">
-        <v>14</v>
+        <v>1010</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C99,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>メリアドール</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -4014,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -4022,26 +4022,26 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="B100">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="C100">
-        <v>1001</v>
+        <v>10</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C100,[1]TextData!A:A))</f>
-        <v>ミカ</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E100">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -4049,17 +4049,17 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="B101">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="C101">
-        <v>1006</v>
+        <v>14</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C101,[1]TextData!A:A))</f>
-        <v>リシェリ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -4082,17 +4082,17 @@
         <v>6031</v>
       </c>
       <c r="C102">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="D102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C102,[1]TextData!A:A))</f>
-        <v>マリーベル</v>
+        <v>ミカ</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -4109,11 +4109,11 @@
         <v>6031</v>
       </c>
       <c r="C103">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C103,[1]TextData!A:A))</f>
-        <v>ユニ</v>
+        <v>リシェリ</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -4136,11 +4136,11 @@
         <v>6031</v>
       </c>
       <c r="C104">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C104,[1]TextData!A:A))</f>
-        <v>ナツキ</v>
+        <v>マリーベル</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -4157,26 +4157,26 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="B105">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="C105">
-        <v>201</v>
+        <v>1007</v>
       </c>
       <c r="D105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C105,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>ユニ</v>
       </c>
       <c r="E105">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -4184,17 +4184,17 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="B106">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="C106">
-        <v>15</v>
+        <v>1009</v>
       </c>
       <c r="D106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C106,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ナツキ</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -4217,20 +4217,20 @@
         <v>6101</v>
       </c>
       <c r="C107">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C107,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>アンリマユ</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -4244,11 +4244,11 @@
         <v>6101</v>
       </c>
       <c r="C108">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C108,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ソード</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="G108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -4271,22 +4271,76 @@
         <v>6101</v>
       </c>
       <c r="C109">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C109,[1]TextData!A:A))</f>
+        <v>スクイッド</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110">
+        <v>6101</v>
+      </c>
+      <c r="B110">
+        <v>6101</v>
+      </c>
+      <c r="C110">
+        <v>5</v>
+      </c>
+      <c r="D110" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C110,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111">
+        <v>6101</v>
+      </c>
+      <c r="B111">
+        <v>6101</v>
+      </c>
+      <c r="C111">
+        <v>13</v>
+      </c>
+      <c r="D111" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C111,[1]TextData!A:A))</f>
         <v>インプ</v>
       </c>
-      <c r="E109">
-        <v>0</v>
-      </c>
-      <c r="F109">
-        <v>0</v>
-      </c>
-      <c r="G109">
-        <v>1</v>
-      </c>
-      <c r="H109">
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
+      <c r="H111">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -70,29 +70,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -107,29 +85,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -145,13 +100,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -161,7 +109,60 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -176,18 +177,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -205,6 +198,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -212,24 +212,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -245,13 +227,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,61 +293,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -329,31 +305,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,19 +329,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,7 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,11 +435,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -462,23 +477,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1686,10 +1686,10 @@
         <v>ビー</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>クロウ</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1740,10 +1740,10 @@
         <v>ドライアド</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -63,7 +63,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -86,23 +94,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -116,71 +123,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -199,8 +144,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,7 +215,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,61 +233,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -299,19 +263,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -329,7 +281,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -341,25 +371,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,31 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,17 +435,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -474,35 +492,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1605,7 +1605,7 @@
         <v>ビー</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1632,7 +1632,7 @@
         <v>ビー</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>ビー</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -63,15 +63,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -86,14 +78,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -101,36 +85,16 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -139,14 +103,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -169,7 +125,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -184,15 +140,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -200,7 +155,52 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,7 +215,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,13 +233,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,7 +371,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,139 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,17 +426,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
@@ -444,11 +433,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -471,23 +466,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -506,6 +495,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1340,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1679,14 +1679,14 @@
         <v>2010</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>クロウ</v>
       </c>
       <c r="E13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1706,17 +1706,17 @@
         <v>2010</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D14" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C14,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1727,20 +1727,20 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>2010</v>
+        <v>2041</v>
       </c>
       <c r="B15">
-        <v>2010</v>
+        <v>2041</v>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1760,17 +1760,17 @@
         <v>2041</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C16,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>カースド</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1787,11 +1787,11 @@
         <v>2041</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D17" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C17,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1808,23 +1808,23 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B18">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="C18">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スクイッド</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1841,17 +1841,17 @@
         <v>2042</v>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>カースド</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1868,11 +1868,11 @@
         <v>2042</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E20">
         <v>5</v>
@@ -1889,23 +1889,23 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>2042</v>
+        <v>2100</v>
       </c>
       <c r="B21">
-        <v>2042</v>
+        <v>2100</v>
       </c>
       <c r="C21">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C21,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ベリト</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1916,23 +1916,23 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B22">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="C22">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>ウルフ</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1943,26 +1943,26 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>2101</v>
+        <v>2201</v>
       </c>
       <c r="B23">
-        <v>2101</v>
+        <v>2201</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ドライアド</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1976,20 +1976,20 @@
         <v>2201</v>
       </c>
       <c r="C24">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -2030,11 +2030,11 @@
         <v>2201</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ドライアド</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2057,11 +2057,11 @@
         <v>2201</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2073,34 +2073,34 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B28">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>クロウ</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2111,20 +2111,20 @@
         <v>2202</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ビー</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2165,11 +2165,11 @@
         <v>2202</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>クロウ</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2181,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2192,11 +2192,11 @@
         <v>2202</v>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ビー</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2208,34 +2208,34 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="B33">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>シールド</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2246,20 +2246,20 @@
         <v>2203</v>
       </c>
       <c r="C34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>サーチャー</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2300,11 +2300,11 @@
         <v>2203</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>シールド</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2327,11 +2327,11 @@
         <v>2203</v>
       </c>
       <c r="C37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>サーチャー</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2343,34 +2343,34 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B38">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2381,20 +2381,20 @@
         <v>2204</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C39,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -2435,11 +2435,11 @@
         <v>2204</v>
       </c>
       <c r="C41">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2451,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2462,11 +2462,11 @@
         <v>2204</v>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2478,34 +2478,34 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="B43">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="C43">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D43" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C43,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2516,20 +2516,20 @@
         <v>2205</v>
       </c>
       <c r="C44">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D44" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C44,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>カースド</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -2570,11 +2570,11 @@
         <v>2205</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C46,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>クリーパー</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2586,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2597,11 +2597,11 @@
         <v>2205</v>
       </c>
       <c r="C47">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>カースド</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2613,34 +2613,34 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="B48">
-        <v>2205</v>
+        <v>3041</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D48" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C48,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ネームレス</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2651,20 +2651,20 @@
         <v>3041</v>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C49,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>インプ</v>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -2678,11 +2678,11 @@
         <v>3041</v>
       </c>
       <c r="C50">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" ht="12" customHeight="1" spans="1:8">
       <c r="A51">
         <v>3041</v>
       </c>
@@ -2705,11 +2705,11 @@
         <v>3041</v>
       </c>
       <c r="C51">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2724,25 +2724,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" ht="12" customHeight="1" spans="1:8">
+    <row r="52" spans="1:8">
       <c r="A52">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="B52">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="C52">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C52,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>カースド</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2759,17 +2759,17 @@
         <v>3042</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C53,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>クリーパー</v>
       </c>
       <c r="E53">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2786,11 +2786,11 @@
         <v>3042</v>
       </c>
       <c r="C54">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D54" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C54,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>サーチャー</v>
       </c>
       <c r="E54">
         <v>5</v>
@@ -2813,11 +2813,11 @@
         <v>3042</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C55,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E55">
         <v>5</v>
@@ -2834,26 +2834,26 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>3042</v>
+        <v>3100</v>
       </c>
       <c r="B56">
-        <v>3042</v>
+        <v>3100</v>
       </c>
       <c r="C56">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="D56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C56,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>パイモン</v>
       </c>
       <c r="E56">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -2861,26 +2861,26 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="B57">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="C57">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C57,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E57">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -2894,11 +2894,11 @@
         <v>3101</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D58" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C58,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>クロウ</v>
       </c>
       <c r="E58">
         <v>5</v>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -2915,26 +2915,26 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>3101</v>
+        <v>4041</v>
       </c>
       <c r="B59">
-        <v>3101</v>
+        <v>4041</v>
       </c>
       <c r="C59">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D59" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C59,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>シールド</v>
       </c>
       <c r="E59">
         <v>5</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -2948,17 +2948,17 @@
         <v>4041</v>
       </c>
       <c r="C60">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C60,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E60">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -3002,11 +3002,11 @@
         <v>4041</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C62,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スクイッド</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3050,26 +3050,26 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="B64">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="C64">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C64,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ビー</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -3083,20 +3083,20 @@
         <v>4042</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C65,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ソード</v>
       </c>
       <c r="E65">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -3110,11 +3110,11 @@
         <v>4042</v>
       </c>
       <c r="C66">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C66,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E66">
         <v>5</v>
@@ -3164,11 +3164,11 @@
         <v>4042</v>
       </c>
       <c r="C68">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C68,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ビー</v>
       </c>
       <c r="E68">
         <v>5</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -3185,23 +3185,23 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>4042</v>
+        <v>4101</v>
       </c>
       <c r="B69">
-        <v>4042</v>
+        <v>4101</v>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="D69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C69,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>アンドラス</v>
       </c>
       <c r="E69">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -3212,10 +3212,10 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>4101</v>
+        <v>4102</v>
       </c>
       <c r="B70">
-        <v>4101</v>
+        <v>4102</v>
       </c>
       <c r="C70">
         <v>104</v>
@@ -3225,7 +3225,7 @@
         <v>アンドラス</v>
       </c>
       <c r="E70">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -3239,20 +3239,20 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>4102</v>
+        <v>5041</v>
       </c>
       <c r="B71">
-        <v>4102</v>
+        <v>5041</v>
       </c>
       <c r="C71">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="D71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C71,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>クリーパー</v>
       </c>
       <c r="E71">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -3279,13 +3279,13 @@
         <v>クリーパー</v>
       </c>
       <c r="E72">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -3326,11 +3326,11 @@
         <v>5041</v>
       </c>
       <c r="C74">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C74,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -3374,23 +3374,23 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="B76">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C76,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ウルフ</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -3407,20 +3407,20 @@
         <v>5042</v>
       </c>
       <c r="C77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C77,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネームレス</v>
       </c>
       <c r="E77">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -3434,11 +3434,11 @@
         <v>5042</v>
       </c>
       <c r="C78">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C78,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E78">
         <v>5</v>
@@ -3461,11 +3461,11 @@
         <v>5042</v>
       </c>
       <c r="C79">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C79,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ウルフ</v>
       </c>
       <c r="E79">
         <v>5</v>
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -3509,26 +3509,26 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81">
-        <v>5042</v>
+        <v>5101</v>
       </c>
       <c r="B81">
-        <v>5042</v>
+        <v>5101</v>
       </c>
       <c r="C81">
-        <v>4</v>
+        <v>105</v>
       </c>
       <c r="D81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C81,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E81">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -3542,20 +3542,20 @@
         <v>5101</v>
       </c>
       <c r="C82">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C82,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>シールド</v>
       </c>
       <c r="E82">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -3569,11 +3569,11 @@
         <v>5101</v>
       </c>
       <c r="C83">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C83,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E83">
         <v>10</v>
@@ -3596,11 +3596,11 @@
         <v>5101</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C84,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>シールド</v>
       </c>
       <c r="E84">
         <v>10</v>
@@ -3623,11 +3623,11 @@
         <v>5101</v>
       </c>
       <c r="C85">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C85,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>スクイッド</v>
       </c>
       <c r="E85">
         <v>10</v>
@@ -3644,26 +3644,26 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="B86">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="C86">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="D86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C86,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E86">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -3677,20 +3677,20 @@
         <v>5102</v>
       </c>
       <c r="C87">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C87,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>シールド</v>
       </c>
       <c r="E87">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -3704,11 +3704,11 @@
         <v>5102</v>
       </c>
       <c r="C88">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C88,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E88">
         <v>20</v>
@@ -3731,11 +3731,11 @@
         <v>5102</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C89,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>シールド</v>
       </c>
       <c r="E89">
         <v>20</v>
@@ -3758,11 +3758,11 @@
         <v>5102</v>
       </c>
       <c r="C90">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C90,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>スクイッド</v>
       </c>
       <c r="E90">
         <v>20</v>
@@ -3779,26 +3779,26 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="B91">
-        <v>5102</v>
+        <v>6021</v>
       </c>
       <c r="C91">
-        <v>11</v>
+        <v>1002</v>
       </c>
       <c r="D91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C91,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>エリザベート</v>
       </c>
       <c r="E91">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -3812,20 +3812,20 @@
         <v>6021</v>
       </c>
       <c r="C92">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C92,[1]TextData!A:A))</f>
-        <v>エリザベート</v>
+        <v>アリエス</v>
       </c>
       <c r="E92">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -3839,11 +3839,11 @@
         <v>6021</v>
       </c>
       <c r="C93">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C93,[1]TextData!A:A))</f>
-        <v>アリエス</v>
+        <v>シイナ</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3852,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -3866,11 +3866,11 @@
         <v>6021</v>
       </c>
       <c r="C94">
-        <v>1004</v>
+        <v>8</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C94,[1]TextData!A:A))</f>
-        <v>シイナ</v>
+        <v>シールド</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3879,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="G94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -3893,11 +3893,11 @@
         <v>6021</v>
       </c>
       <c r="C95">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C95,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3914,23 +3914,23 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="B96">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>1011</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C96,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>セリナ</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -3947,17 +3947,17 @@
         <v>6022</v>
       </c>
       <c r="C97">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C97,[1]TextData!A:A))</f>
-        <v>セリナ</v>
+        <v>レダ</v>
       </c>
       <c r="E97">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -3974,11 +3974,11 @@
         <v>6022</v>
       </c>
       <c r="C98">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C98,[1]TextData!A:A))</f>
-        <v>レダ</v>
+        <v>メリアドール</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -4001,11 +4001,11 @@
         <v>6022</v>
       </c>
       <c r="C99">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C99,[1]TextData!A:A))</f>
-        <v>メリアドール</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -4028,11 +4028,11 @@
         <v>6022</v>
       </c>
       <c r="C100">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C100,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -4049,23 +4049,23 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="B101">
-        <v>6022</v>
+        <v>6031</v>
       </c>
       <c r="C101">
-        <v>14</v>
+        <v>1001</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C101,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ミカ</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -4082,17 +4082,17 @@
         <v>6031</v>
       </c>
       <c r="C102">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="D102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C102,[1]TextData!A:A))</f>
-        <v>ミカ</v>
+        <v>リシェリ</v>
       </c>
       <c r="E102">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -4109,11 +4109,11 @@
         <v>6031</v>
       </c>
       <c r="C103">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="D103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C103,[1]TextData!A:A))</f>
-        <v>リシェリ</v>
+        <v>マリーベル</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -4136,11 +4136,11 @@
         <v>6031</v>
       </c>
       <c r="C104">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C104,[1]TextData!A:A))</f>
-        <v>マリーベル</v>
+        <v>ユニ</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -4163,11 +4163,11 @@
         <v>6031</v>
       </c>
       <c r="C105">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="D105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C105,[1]TextData!A:A))</f>
-        <v>ユニ</v>
+        <v>ナツキ</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -4184,26 +4184,26 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="B106">
-        <v>6031</v>
+        <v>6101</v>
       </c>
       <c r="C106">
-        <v>1009</v>
+        <v>201</v>
       </c>
       <c r="D106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C106,[1]TextData!A:A))</f>
-        <v>ナツキ</v>
+        <v>アンリマユ</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -4217,20 +4217,20 @@
         <v>6101</v>
       </c>
       <c r="C107">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="D107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C107,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>ソード</v>
       </c>
       <c r="E107">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -4244,11 +4244,11 @@
         <v>6101</v>
       </c>
       <c r="C108">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C108,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>スクイッド</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -4271,11 +4271,11 @@
         <v>6101</v>
       </c>
       <c r="C109">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C109,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>クロウ</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>0</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -4298,11 +4298,11 @@
         <v>6101</v>
       </c>
       <c r="C110">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C110,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>インプ</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -4314,33 +4314,6 @@
         <v>1</v>
       </c>
       <c r="H110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
-      <c r="A111">
-        <v>6101</v>
-      </c>
-      <c r="B111">
-        <v>6101</v>
-      </c>
-      <c r="C111">
-        <v>13</v>
-      </c>
-      <c r="D111" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C111,[1]TextData!A:A))</f>
-        <v>インプ</v>
-      </c>
-      <c r="E111">
-        <v>0</v>
-      </c>
-      <c r="F111">
-        <v>0</v>
-      </c>
-      <c r="G111">
-        <v>1</v>
-      </c>
-      <c r="H111">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -63,14 +63,52 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -84,17 +122,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -116,21 +145,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -139,15 +153,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -161,16 +184,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -184,25 +199,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -215,7 +215,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,13 +251,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,7 +275,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -257,37 +347,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -299,25 +365,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -329,73 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,16 +410,27 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -434,16 +445,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -472,15 +483,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -498,11 +500,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1686,7 +1686,7 @@
         <v>クロウ</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F13">
         <v>1</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -63,52 +63,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -129,9 +91,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -145,9 +151,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -161,18 +190,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -181,28 +203,6 @@
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -215,7 +215,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,25 +263,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -257,7 +275,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -269,13 +287,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,67 +311,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -365,13 +329,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -383,7 +377,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,7 +389,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,37 +409,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -484,16 +473,27 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -501,8 +501,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1340,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1679,17 +1679,17 @@
         <v>2010</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>サーチャー</v>
       </c>
       <c r="E13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1706,17 +1706,17 @@
         <v>2010</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D14" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C14,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>クロウ</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1727,23 +1727,23 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>2041</v>
+        <v>2010</v>
       </c>
       <c r="B15">
-        <v>2041</v>
+        <v>2010</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1760,17 +1760,17 @@
         <v>2041</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C16,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1787,11 +1787,11 @@
         <v>2041</v>
       </c>
       <c r="C17">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D17" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C17,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>カースド</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1808,23 +1808,23 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B18">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="C18">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1841,17 +1841,17 @@
         <v>2042</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>スクイッド</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1868,11 +1868,11 @@
         <v>2042</v>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>カースド</v>
       </c>
       <c r="E20">
         <v>5</v>
@@ -1889,23 +1889,23 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>2100</v>
+        <v>2042</v>
       </c>
       <c r="B21">
-        <v>2100</v>
+        <v>2042</v>
       </c>
       <c r="C21">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C21,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1916,23 +1916,23 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="B22">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ベリト</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1943,26 +1943,26 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="B23">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="C23">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1976,20 +1976,20 @@
         <v>2201</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ドライアド</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -2030,11 +2030,11 @@
         <v>2201</v>
       </c>
       <c r="C26">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2057,11 +2057,11 @@
         <v>2201</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ドライアド</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2073,34 +2073,34 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="B28">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ウルフ</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2111,20 +2111,20 @@
         <v>2202</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>クロウ</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2165,11 +2165,11 @@
         <v>2202</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ビー</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2181,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2192,11 +2192,11 @@
         <v>2202</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>クロウ</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2208,34 +2208,34 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="B33">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ビー</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2246,20 +2246,20 @@
         <v>2203</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>シールド</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2300,11 +2300,11 @@
         <v>2203</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>サーチャー</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2327,11 +2327,11 @@
         <v>2203</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>シールド</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2343,34 +2343,34 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="B38">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>サーチャー</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2381,20 +2381,20 @@
         <v>2204</v>
       </c>
       <c r="C39">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C39,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -2435,11 +2435,11 @@
         <v>2204</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2451,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2462,11 +2462,11 @@
         <v>2204</v>
       </c>
       <c r="C42">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2478,34 +2478,34 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="B43">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C43">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D43" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C43,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2516,20 +2516,20 @@
         <v>2205</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D44" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C44,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>クリーパー</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -2570,11 +2570,11 @@
         <v>2205</v>
       </c>
       <c r="C46">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C46,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>カースド</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2586,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2597,11 +2597,11 @@
         <v>2205</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>クリーパー</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2613,34 +2613,34 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>3041</v>
+        <v>2205</v>
       </c>
       <c r="B48">
-        <v>3041</v>
+        <v>2205</v>
       </c>
       <c r="C48">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D48" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C48,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>カースド</v>
       </c>
       <c r="E48">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2651,20 +2651,20 @@
         <v>3041</v>
       </c>
       <c r="C49">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C49,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ネームレス</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -2678,11 +2678,11 @@
         <v>3041</v>
       </c>
       <c r="C50">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>インプ</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" ht="12" customHeight="1" spans="1:8">
+    <row r="51" spans="1:8">
       <c r="A51">
         <v>3041</v>
       </c>
@@ -2705,11 +2705,11 @@
         <v>3041</v>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2724,25 +2724,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" ht="12" customHeight="1" spans="1:8">
       <c r="A52">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="B52">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C52,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ネームレス</v>
       </c>
       <c r="E52">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2759,17 +2759,17 @@
         <v>3042</v>
       </c>
       <c r="C53">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C53,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>カースド</v>
       </c>
       <c r="E53">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2786,11 +2786,11 @@
         <v>3042</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D54" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C54,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E54">
         <v>5</v>
@@ -2813,11 +2813,11 @@
         <v>3042</v>
       </c>
       <c r="C55">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C55,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>サーチャー</v>
       </c>
       <c r="E55">
         <v>5</v>
@@ -2834,26 +2834,26 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>3100</v>
+        <v>3042</v>
       </c>
       <c r="B56">
-        <v>3100</v>
+        <v>3042</v>
       </c>
       <c r="C56">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="D56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C56,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>クリーパー</v>
       </c>
       <c r="E56">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -2861,26 +2861,26 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="B57">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C57,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>パイモン</v>
       </c>
       <c r="E57">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -2894,11 +2894,11 @@
         <v>3101</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D58" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C58,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E58">
         <v>5</v>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -2915,26 +2915,26 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>4041</v>
+        <v>3101</v>
       </c>
       <c r="B59">
-        <v>4041</v>
+        <v>3101</v>
       </c>
       <c r="C59">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D59" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C59,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>クロウ</v>
       </c>
       <c r="E59">
         <v>5</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -2948,17 +2948,17 @@
         <v>4041</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C60,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>シールド</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -3002,11 +3002,11 @@
         <v>4041</v>
       </c>
       <c r="C62">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C62,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3050,26 +3050,26 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="B64">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C64,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>スクイッド</v>
       </c>
       <c r="E64">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -3083,20 +3083,20 @@
         <v>4042</v>
       </c>
       <c r="C65">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C65,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ビー</v>
       </c>
       <c r="E65">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -3110,11 +3110,11 @@
         <v>4042</v>
       </c>
       <c r="C66">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C66,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ソード</v>
       </c>
       <c r="E66">
         <v>5</v>
@@ -3164,11 +3164,11 @@
         <v>4042</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C68,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E68">
         <v>5</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -3185,23 +3185,23 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>4101</v>
+        <v>4042</v>
       </c>
       <c r="B69">
-        <v>4101</v>
+        <v>4042</v>
       </c>
       <c r="C69">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="D69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C69,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>ビー</v>
       </c>
       <c r="E69">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -3212,10 +3212,10 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="B70">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="C70">
         <v>104</v>
@@ -3225,7 +3225,7 @@
         <v>アンドラス</v>
       </c>
       <c r="E70">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -3239,20 +3239,20 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>5041</v>
+        <v>4102</v>
       </c>
       <c r="B71">
-        <v>5041</v>
+        <v>4102</v>
       </c>
       <c r="C71">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="D71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C71,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>アンドラス</v>
       </c>
       <c r="E71">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -3279,13 +3279,13 @@
         <v>クリーパー</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -3326,11 +3326,11 @@
         <v>5041</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C74,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>クリーパー</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -3374,23 +3374,23 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>5042</v>
+        <v>5041</v>
       </c>
       <c r="B76">
-        <v>5042</v>
+        <v>5041</v>
       </c>
       <c r="C76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C76,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E76">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -3407,20 +3407,20 @@
         <v>5042</v>
       </c>
       <c r="C77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C77,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ウルフ</v>
       </c>
       <c r="E77">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -3434,11 +3434,11 @@
         <v>5042</v>
       </c>
       <c r="C78">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C78,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E78">
         <v>5</v>
@@ -3461,11 +3461,11 @@
         <v>5042</v>
       </c>
       <c r="C79">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C79,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E79">
         <v>5</v>
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -3509,26 +3509,26 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81">
-        <v>5101</v>
+        <v>5042</v>
       </c>
       <c r="B81">
-        <v>5101</v>
+        <v>5042</v>
       </c>
       <c r="C81">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="D81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C81,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>ウルフ</v>
       </c>
       <c r="E81">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -3542,20 +3542,20 @@
         <v>5101</v>
       </c>
       <c r="C82">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C82,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E82">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -3569,11 +3569,11 @@
         <v>5101</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C83,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>シールド</v>
       </c>
       <c r="E83">
         <v>10</v>
@@ -3596,11 +3596,11 @@
         <v>5101</v>
       </c>
       <c r="C84">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C84,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E84">
         <v>10</v>
@@ -3623,11 +3623,11 @@
         <v>5101</v>
       </c>
       <c r="C85">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C85,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>シールド</v>
       </c>
       <c r="E85">
         <v>10</v>
@@ -3644,26 +3644,26 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="B86">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="C86">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="D86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C86,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>スクイッド</v>
       </c>
       <c r="E86">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -3677,20 +3677,20 @@
         <v>5102</v>
       </c>
       <c r="C87">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="D87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C87,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E87">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -3704,11 +3704,11 @@
         <v>5102</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C88,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>シールド</v>
       </c>
       <c r="E88">
         <v>20</v>
@@ -3731,11 +3731,11 @@
         <v>5102</v>
       </c>
       <c r="C89">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C89,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E89">
         <v>20</v>
@@ -3758,11 +3758,11 @@
         <v>5102</v>
       </c>
       <c r="C90">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C90,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>シールド</v>
       </c>
       <c r="E90">
         <v>20</v>
@@ -3779,26 +3779,26 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="B91">
-        <v>6021</v>
+        <v>5102</v>
       </c>
       <c r="C91">
-        <v>1002</v>
+        <v>11</v>
       </c>
       <c r="D91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C91,[1]TextData!A:A))</f>
-        <v>エリザベート</v>
+        <v>スクイッド</v>
       </c>
       <c r="E91">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -3812,20 +3812,20 @@
         <v>6021</v>
       </c>
       <c r="C92">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C92,[1]TextData!A:A))</f>
-        <v>アリエス</v>
+        <v>エリザベート</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -3839,11 +3839,11 @@
         <v>6021</v>
       </c>
       <c r="C93">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C93,[1]TextData!A:A))</f>
-        <v>シイナ</v>
+        <v>アリエス</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3852,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -3866,11 +3866,11 @@
         <v>6021</v>
       </c>
       <c r="C94">
-        <v>8</v>
+        <v>1004</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C94,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>シイナ</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3879,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -3893,11 +3893,11 @@
         <v>6021</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C95,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>シールド</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3914,23 +3914,23 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="B96">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="C96">
-        <v>1011</v>
+        <v>1</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C96,[1]TextData!A:A))</f>
-        <v>セリナ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E96">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -3947,17 +3947,17 @@
         <v>6022</v>
       </c>
       <c r="C97">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C97,[1]TextData!A:A))</f>
-        <v>レダ</v>
+        <v>セリナ</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -3974,11 +3974,11 @@
         <v>6022</v>
       </c>
       <c r="C98">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C98,[1]TextData!A:A))</f>
-        <v>メリアドール</v>
+        <v>レダ</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -4001,11 +4001,11 @@
         <v>6022</v>
       </c>
       <c r="C99">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C99,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>メリアドール</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -4028,11 +4028,11 @@
         <v>6022</v>
       </c>
       <c r="C100">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C100,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -4049,23 +4049,23 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="B101">
-        <v>6031</v>
+        <v>6022</v>
       </c>
       <c r="C101">
-        <v>1001</v>
+        <v>14</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C101,[1]TextData!A:A))</f>
-        <v>ミカ</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E101">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -4082,17 +4082,17 @@
         <v>6031</v>
       </c>
       <c r="C102">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="D102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C102,[1]TextData!A:A))</f>
-        <v>リシェリ</v>
+        <v>ミカ</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -4109,11 +4109,11 @@
         <v>6031</v>
       </c>
       <c r="C103">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="D103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C103,[1]TextData!A:A))</f>
-        <v>マリーベル</v>
+        <v>リシェリ</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -4136,11 +4136,11 @@
         <v>6031</v>
       </c>
       <c r="C104">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C104,[1]TextData!A:A))</f>
-        <v>ユニ</v>
+        <v>マリーベル</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -4163,11 +4163,11 @@
         <v>6031</v>
       </c>
       <c r="C105">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C105,[1]TextData!A:A))</f>
-        <v>ナツキ</v>
+        <v>ユニ</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -4184,26 +4184,26 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="B106">
-        <v>6101</v>
+        <v>6031</v>
       </c>
       <c r="C106">
-        <v>201</v>
+        <v>1009</v>
       </c>
       <c r="D106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C106,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>ナツキ</v>
       </c>
       <c r="E106">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -4217,20 +4217,20 @@
         <v>6101</v>
       </c>
       <c r="C107">
-        <v>15</v>
+        <v>201</v>
       </c>
       <c r="D107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C107,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>アンリマユ</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -4244,11 +4244,11 @@
         <v>6101</v>
       </c>
       <c r="C108">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C108,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ソード</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -4271,11 +4271,11 @@
         <v>6101</v>
       </c>
       <c r="C109">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C109,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>スクイッド</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>0</v>
       </c>
       <c r="G109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -4298,22 +4298,49 @@
         <v>6101</v>
       </c>
       <c r="C110">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C110,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111">
+        <v>6101</v>
+      </c>
+      <c r="B111">
+        <v>6101</v>
+      </c>
+      <c r="C111">
+        <v>13</v>
+      </c>
+      <c r="D111" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C111,[1]TextData!A:A))</f>
         <v>インプ</v>
       </c>
-      <c r="E110">
-        <v>0</v>
-      </c>
-      <c r="F110">
-        <v>0</v>
-      </c>
-      <c r="G110">
-        <v>1</v>
-      </c>
-      <c r="H110">
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
+      <c r="H111">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -63,7 +63,44 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -76,16 +113,71 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -100,14 +192,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -115,92 +200,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,31 +215,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,37 +371,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -293,43 +383,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -341,61 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,21 +406,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -442,8 +427,47 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -463,45 +487,21 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1605,7 +1605,7 @@
         <v>ビー</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1632,10 +1632,10 @@
         <v>ビー</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>ビー</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -70,7 +70,69 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -84,30 +146,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -122,54 +163,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -184,7 +178,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -192,15 +186,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,31 +215,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,145 +383,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,80 +406,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -506,6 +432,80 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1686,7 +1686,7 @@
         <v>サーチャー</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>クロウ</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1740,7 +1740,7 @@
         <v>ネレイドジェム</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F15">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -49,9 +49,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -59,98 +59,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -169,9 +77,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -186,7 +124,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -199,8 +137,70 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,187 +215,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,21 +413,45 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -450,9 +474,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -465,47 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1340,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1808,20 +1808,20 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>20010</v>
+        <v>3020</v>
       </c>
       <c r="B18">
-        <v>20010</v>
+        <v>3020</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>インプ</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1835,20 +1835,20 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>20010</v>
+        <v>3020</v>
       </c>
       <c r="B19">
-        <v>20010</v>
+        <v>3020</v>
       </c>
       <c r="C19">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ソード</v>
       </c>
       <c r="E19">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1862,20 +1862,20 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>20010</v>
+        <v>3020</v>
       </c>
       <c r="B20">
-        <v>20010</v>
+        <v>3020</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>インプ</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1889,20 +1889,20 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>20020</v>
+        <v>3030</v>
       </c>
       <c r="B21">
-        <v>20020</v>
+        <v>3030</v>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C21,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>カースド</v>
       </c>
       <c r="E21">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1916,23 +1916,23 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>20020</v>
+        <v>3030</v>
       </c>
       <c r="B22">
-        <v>20020</v>
+        <v>3030</v>
       </c>
       <c r="C22">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>クリーパー</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1943,20 +1943,20 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>20020</v>
+        <v>3030</v>
       </c>
       <c r="B23">
-        <v>20020</v>
+        <v>3030</v>
       </c>
       <c r="C23">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E23">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1970,20 +1970,20 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>20030</v>
+        <v>3040</v>
       </c>
       <c r="B24">
-        <v>20030</v>
+        <v>3040</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ソード</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1997,23 +1997,23 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>20030</v>
+        <v>3040</v>
       </c>
       <c r="B25">
-        <v>20030</v>
+        <v>3040</v>
       </c>
       <c r="C25">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="D25" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C25,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>クリーパー</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -2024,28 +2024,271 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>20030</v>
+        <v>3040</v>
       </c>
       <c r="B26">
-        <v>20030</v>
+        <v>3040</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
+        <v>ゴーストアーマー</v>
+      </c>
+      <c r="E26">
+        <v>12</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27">
+        <v>20010</v>
+      </c>
+      <c r="B27">
+        <v>20010</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
         <v>ウルフ</v>
       </c>
-      <c r="E26">
+      <c r="E27">
+        <v>6</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28">
+        <v>20010</v>
+      </c>
+      <c r="B28">
+        <v>20010</v>
+      </c>
+      <c r="C28">
+        <v>9</v>
+      </c>
+      <c r="D28" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+      <c r="E28">
+        <v>6</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29">
+        <v>20010</v>
+      </c>
+      <c r="B29">
+        <v>20010</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+      <c r="E29">
+        <v>6</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30">
+        <v>20020</v>
+      </c>
+      <c r="B30">
+        <v>20020</v>
+      </c>
+      <c r="C30">
+        <v>9</v>
+      </c>
+      <c r="D30" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31">
+        <v>20020</v>
+      </c>
+      <c r="B31">
+        <v>20020</v>
+      </c>
+      <c r="C31">
+        <v>15</v>
+      </c>
+      <c r="D31" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
+        <v>ソード</v>
+      </c>
+      <c r="E31">
+        <v>8</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32">
+        <v>20020</v>
+      </c>
+      <c r="B32">
+        <v>20020</v>
+      </c>
+      <c r="C32">
+        <v>9</v>
+      </c>
+      <c r="D32" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+      <c r="E32">
+        <v>8</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33">
+        <v>20030</v>
+      </c>
+      <c r="B33">
+        <v>20030</v>
+      </c>
+      <c r="C33">
+        <v>4</v>
+      </c>
+      <c r="D33" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+      <c r="E33">
         <v>10</v>
       </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34">
+        <v>20030</v>
+      </c>
+      <c r="B34">
+        <v>20030</v>
+      </c>
+      <c r="C34">
+        <v>102</v>
+      </c>
+      <c r="D34" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
+        <v>ベリト</v>
+      </c>
+      <c r="E34">
+        <v>10</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35">
+        <v>20030</v>
+      </c>
+      <c r="B35">
+        <v>20030</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+      <c r="D35" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+      <c r="E35">
+        <v>10</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,9 +48,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
@@ -62,14 +62,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -78,7 +70,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -101,15 +114,23 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -124,14 +145,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -139,7 +176,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -154,53 +199,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -221,43 +221,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -269,133 +371,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,7 +413,46 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -436,8 +475,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -457,21 +496,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -482,30 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1686,7 +1686,7 @@
         <v>サーチャー</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>ネレイドジェム</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F15">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,9 +48,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
@@ -62,36 +62,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -106,18 +87,18 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -128,24 +109,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -159,16 +124,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -183,18 +148,46 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -205,6 +198,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,181 +215,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,6 +406,36 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -442,21 +472,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -481,21 +496,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1605,7 +1605,7 @@
         <v>ビー</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1632,7 +1632,7 @@
         <v>ビー</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1659,7 +1659,7 @@
         <v>ビー</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -62,53 +62,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -116,16 +69,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -148,10 +100,71 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -162,15 +175,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -184,7 +191,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -193,14 +200,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,37 +215,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -257,67 +371,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -329,73 +389,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,17 +409,50 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -441,48 +474,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -496,13 +492,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1814,11 +1814,11 @@
         <v>3020</v>
       </c>
       <c r="C18">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>カースド</v>
       </c>
       <c r="E18">
         <v>10</v>
@@ -1868,11 +1868,11 @@
         <v>3020</v>
       </c>
       <c r="C20">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>クリーパー</v>
       </c>
       <c r="E20">
         <v>10</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -49,89 +49,14 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -155,7 +80,21 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -163,6 +102,21 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -177,14 +131,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -198,13 +145,66 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,13 +215,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,13 +323,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,7 +353,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,43 +365,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -311,91 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,54 +406,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -474,20 +426,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -506,6 +462,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,16 +514,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -532,127 +532,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1605,7 +1605,7 @@
         <v>ビー</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1632,7 +1632,7 @@
         <v>ビー</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1659,7 +1659,7 @@
         <v>ビー</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1686,7 +1686,7 @@
         <v>サーチャー</v>
       </c>
       <c r="E13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>クロウ</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1740,7 +1740,7 @@
         <v>ネレイドジェム</v>
       </c>
       <c r="E15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1767,7 +1767,7 @@
         <v>ゴーストアーマー</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1794,7 +1794,7 @@
         <v>ベリト</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1821,7 +1821,7 @@
         <v>カースド</v>
       </c>
       <c r="E18">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>ソード</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1875,7 +1875,7 @@
         <v>クリーパー</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>カースド</v>
       </c>
       <c r="E21">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1929,7 +1929,7 @@
         <v>クリーパー</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1956,7 +1956,7 @@
         <v>ゴーストアーマー</v>
       </c>
       <c r="E23">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1983,7 +1983,7 @@
         <v>ソード</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -2010,7 +2010,7 @@
         <v>クリーパー</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>ゴーストアーマー</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F26">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -59,30 +59,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -100,8 +76,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -115,6 +92,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -122,18 +121,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -153,38 +153,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -199,10 +169,40 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -215,187 +215,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,6 +406,26 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -424,15 +444,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -444,32 +455,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -506,6 +491,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1340,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -2064,7 +2064,7 @@
         <v>ウルフ</v>
       </c>
       <c r="E27">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2084,14 +2084,14 @@
         <v>20010</v>
       </c>
       <c r="C28">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>アモン</v>
       </c>
       <c r="E28">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -2111,14 +2111,14 @@
         <v>20010</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ソード</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -2138,14 +2138,14 @@
         <v>20020</v>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>インプ</v>
       </c>
       <c r="E30">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2165,14 +2165,14 @@
         <v>20020</v>
       </c>
       <c r="C31">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>パイモン</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2192,14 +2192,14 @@
         <v>20020</v>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ネームレス</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2208,87 +2208,6 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33">
-        <v>20030</v>
-      </c>
-      <c r="B33">
-        <v>20030</v>
-      </c>
-      <c r="C33">
-        <v>4</v>
-      </c>
-      <c r="D33" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
-      </c>
-      <c r="E33">
-        <v>10</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34">
-        <v>20030</v>
-      </c>
-      <c r="B34">
-        <v>20030</v>
-      </c>
-      <c r="C34">
-        <v>102</v>
-      </c>
-      <c r="D34" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>ベリト</v>
-      </c>
-      <c r="E34">
-        <v>10</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35">
-        <v>20030</v>
-      </c>
-      <c r="B35">
-        <v>20030</v>
-      </c>
-      <c r="C35">
-        <v>4</v>
-      </c>
-      <c r="D35" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
-      </c>
-      <c r="E35">
-        <v>10</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -49,8 +49,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -59,6 +59,30 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -71,44 +95,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -129,32 +115,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -170,15 +133,38 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -192,6 +178,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -199,8 +192,15 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,187 +215,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,35 +411,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -459,11 +433,43 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -492,17 +498,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,7 +514,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -523,7 +523,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -532,127 +532,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1340,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -2051,23 +2051,23 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>20010</v>
+        <v>4010</v>
       </c>
       <c r="B27">
-        <v>20010</v>
+        <v>4010</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>アンドラス</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -2084,17 +2084,17 @@
         <v>20010</v>
       </c>
       <c r="C28">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>ウルフ</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -2111,17 +2111,17 @@
         <v>20010</v>
       </c>
       <c r="C29">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>アモン</v>
       </c>
       <c r="E29">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -2132,20 +2132,20 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B30">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ソード</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2165,17 +2165,17 @@
         <v>20020</v>
       </c>
       <c r="C31">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>インプ</v>
       </c>
       <c r="E31">
         <v>15</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -2192,22 +2192,49 @@
         <v>20020</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>パイモン</v>
       </c>
       <c r="E32">
         <v>15</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33">
+        <v>20020</v>
+      </c>
+      <c r="B33">
+        <v>20020</v>
+      </c>
+      <c r="C33">
+        <v>6</v>
+      </c>
+      <c r="D33" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
+        <v>ネームレス</v>
+      </c>
+      <c r="E33">
+        <v>15</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -49,9 +49,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -59,30 +59,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -101,7 +77,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -115,6 +91,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -123,17 +107,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -147,9 +144,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -157,35 +161,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -205,6 +181,30 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,187 +215,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,7 +413,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -433,6 +433,35 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -444,17 +473,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -488,24 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1689,7 +1689,7 @@
         <v>8</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1743,7 +1743,7 @@
         <v>8</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -59,6 +59,59 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -76,92 +129,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -175,8 +145,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -187,6 +158,21 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -205,6 +191,20 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,13 +215,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,7 +329,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,157 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,26 +409,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -451,6 +442,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -462,17 +483,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -491,21 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1824,7 +1824,7 @@
         <v>15</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1878,7 +1878,7 @@
         <v>15</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -59,37 +59,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -109,16 +78,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -131,7 +101,30 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -145,9 +138,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -161,9 +162,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -171,6 +171,21 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -184,21 +199,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -215,31 +215,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,151 +371,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,17 +409,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -429,30 +423,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -483,11 +453,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,91 +48,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -155,6 +79,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -163,21 +95,82 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -191,16 +184,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,187 +215,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,39 +406,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -469,16 +436,49 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -493,16 +493,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,16 +514,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -532,127 +532,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1340,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -2091,7 +2091,7 @@
         <v>ウルフ</v>
       </c>
       <c r="E28">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -2118,7 +2118,7 @@
         <v>アモン</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2132,20 +2132,20 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>20010</v>
+        <v>20020</v>
       </c>
       <c r="B30">
-        <v>20010</v>
+        <v>20020</v>
       </c>
       <c r="C30">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>インプ</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2165,17 +2165,17 @@
         <v>20020</v>
       </c>
       <c r="C31">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>パイモン</v>
       </c>
       <c r="E31">
         <v>15</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -2192,49 +2192,22 @@
         <v>20020</v>
       </c>
       <c r="C32">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>ネームレス</v>
       </c>
       <c r="E32">
         <v>15</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33">
-        <v>20020</v>
-      </c>
-      <c r="B33">
-        <v>20020</v>
-      </c>
-      <c r="C33">
-        <v>6</v>
-      </c>
-      <c r="D33" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
-      </c>
-      <c r="E33">
-        <v>15</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,9 +48,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -62,9 +62,90 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -87,29 +168,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -125,20 +192,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -152,59 +205,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,6 +215,90 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -227,175 +311,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,13 +409,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -461,48 +498,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2091,7 +2091,7 @@
         <v>ウルフ</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -2118,7 +2118,7 @@
         <v>アモン</v>
       </c>
       <c r="E29">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F29">
         <v>1</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -49,8 +49,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -62,16 +62,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -91,16 +83,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -122,8 +114,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -131,6 +147,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -145,6 +169,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -153,15 +184,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -176,31 +199,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,37 +215,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -257,145 +383,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,9 +426,29 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -448,11 +468,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -472,37 +498,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,7 +514,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -523,7 +523,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -532,127 +532,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2145,7 +2145,7 @@
         <v>インプ</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         <v>パイモン</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>ネームレス</v>
       </c>
       <c r="E32">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F32">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -49,14 +49,22 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -77,7 +85,62 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -98,9 +161,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -114,62 +192,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -181,30 +205,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,13 +215,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,7 +299,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,43 +377,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -299,103 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,6 +406,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -420,6 +429,51 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -448,60 +502,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1794,7 +1794,7 @@
         <v>ベリト</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -2064,7 +2064,7 @@
         <v>アンドラス</v>
       </c>
       <c r="E27">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F27">
         <v>1</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -59,6 +59,28 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -71,31 +93,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -108,23 +116,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -148,7 +140,28 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -161,10 +174,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -178,7 +192,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -186,21 +200,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,187 +215,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,15 +406,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -429,21 +420,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -480,11 +456,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -492,8 +466,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -506,6 +480,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,16 +514,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -532,127 +532,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1794,7 +1794,7 @@
         <v>ベリト</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F17">
         <v>1</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -69,14 +69,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -84,8 +76,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -99,9 +106,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -116,38 +123,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -167,8 +150,49 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -181,30 +205,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,49 +215,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -269,133 +389,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,31 +409,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -454,44 +448,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -506,6 +473,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1340,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1605,7 +1605,7 @@
         <v>ビー</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1632,7 +1632,7 @@
         <v>ビー</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1659,7 +1659,7 @@
         <v>ビー</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -2078,23 +2078,23 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>20010</v>
+        <v>5010</v>
       </c>
       <c r="B28">
-        <v>20010</v>
+        <v>5010</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>シールド</v>
       </c>
       <c r="E28">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -2105,20 +2105,20 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>20010</v>
+        <v>5010</v>
       </c>
       <c r="B29">
-        <v>20010</v>
+        <v>5010</v>
       </c>
       <c r="C29">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2132,23 +2132,23 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>20020</v>
+        <v>5010</v>
       </c>
       <c r="B30">
-        <v>20020</v>
+        <v>5010</v>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>シールド</v>
       </c>
       <c r="E30">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -2159,23 +2159,23 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B31">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="C31">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>ウルフ</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -2186,28 +2186,109 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B32">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
+        <v>アモン</v>
+      </c>
+      <c r="E32">
+        <v>15</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33">
+        <v>20020</v>
+      </c>
+      <c r="B33">
+        <v>20020</v>
+      </c>
+      <c r="C33">
+        <v>13</v>
+      </c>
+      <c r="D33" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+      <c r="E33">
+        <v>20</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34">
+        <v>20020</v>
+      </c>
+      <c r="B34">
+        <v>20020</v>
+      </c>
+      <c r="C34">
+        <v>103</v>
+      </c>
+      <c r="D34" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
+        <v>パイモン</v>
+      </c>
+      <c r="E34">
+        <v>25</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35">
+        <v>20020</v>
+      </c>
+      <c r="B35">
+        <v>20020</v>
+      </c>
+      <c r="C35">
+        <v>6</v>
+      </c>
+      <c r="D35" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
         <v>ネームレス</v>
       </c>
-      <c r="E32">
+      <c r="E35">
         <v>20</v>
       </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -62,6 +62,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -69,15 +85,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -92,15 +109,68 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -115,7 +185,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -130,81 +200,11 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,6 +215,144 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -227,13 +365,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,102 +383,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -348,48 +390,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -418,32 +418,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -465,17 +450,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -484,15 +458,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -506,6 +495,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,16 +514,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -532,127 +532,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1340,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -2159,23 +2159,23 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>20010</v>
+        <v>6010</v>
       </c>
       <c r="B31">
-        <v>20010</v>
+        <v>6010</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ソード</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -2186,20 +2186,20 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>20010</v>
+        <v>6010</v>
       </c>
       <c r="B32">
-        <v>20010</v>
+        <v>6010</v>
       </c>
       <c r="C32">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>アンリマユ</v>
       </c>
       <c r="E32">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2213,23 +2213,23 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>20020</v>
+        <v>6010</v>
       </c>
       <c r="B33">
-        <v>20020</v>
+        <v>6010</v>
       </c>
       <c r="C33">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ソード</v>
       </c>
       <c r="E33">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -2240,23 +2240,23 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B34">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="C34">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>ウルフ</v>
       </c>
       <c r="E34">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -2267,28 +2267,109 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B35">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
+        <v>アモン</v>
+      </c>
+      <c r="E35">
+        <v>15</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36">
+        <v>20020</v>
+      </c>
+      <c r="B36">
+        <v>20020</v>
+      </c>
+      <c r="C36">
+        <v>13</v>
+      </c>
+      <c r="D36" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+      <c r="E36">
+        <v>20</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37">
+        <v>20020</v>
+      </c>
+      <c r="B37">
+        <v>20020</v>
+      </c>
+      <c r="C37">
+        <v>103</v>
+      </c>
+      <c r="D37" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
+        <v>パイモン</v>
+      </c>
+      <c r="E37">
+        <v>25</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38">
+        <v>20020</v>
+      </c>
+      <c r="B38">
+        <v>20020</v>
+      </c>
+      <c r="C38">
+        <v>6</v>
+      </c>
+      <c r="D38" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
         <v>ネームレス</v>
       </c>
-      <c r="E35">
+      <c r="E38">
         <v>20</v>
       </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,15 +48,119 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -72,37 +176,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -117,75 +191,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -198,13 +205,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,13 +215,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,169 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,11 +409,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -433,21 +454,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -457,17 +463,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -489,15 +498,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -514,16 +514,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -535,124 +535,124 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -869,209 +869,217 @@
         </row>
         <row r="17">
           <cell r="A17">
-            <v>101</v>
+            <v>51</v>
           </cell>
           <cell r="B17" t="str">
-            <v>アモン</v>
+            <v>オーガ</v>
           </cell>
         </row>
         <row r="18">
           <cell r="A18">
-            <v>102</v>
+            <v>101</v>
           </cell>
           <cell r="B18" t="str">
-            <v>ベリト</v>
+            <v>アモン</v>
           </cell>
         </row>
         <row r="19">
           <cell r="A19">
-            <v>103</v>
+            <v>102</v>
           </cell>
           <cell r="B19" t="str">
-            <v>パイモン</v>
+            <v>ベリト</v>
           </cell>
         </row>
         <row r="20">
           <cell r="A20">
-            <v>104</v>
+            <v>103</v>
           </cell>
           <cell r="B20" t="str">
-            <v>アンドラス</v>
+            <v>パイモン</v>
           </cell>
         </row>
         <row r="21">
           <cell r="A21">
-            <v>105</v>
+            <v>104</v>
           </cell>
           <cell r="B21" t="str">
-            <v>ビフロンス</v>
+            <v>アンドラス</v>
           </cell>
         </row>
         <row r="22">
           <cell r="A22">
-            <v>106</v>
+            <v>105</v>
           </cell>
           <cell r="B22" t="str">
-            <v>アイホート</v>
+            <v>ビフロンス</v>
           </cell>
         </row>
         <row r="23">
           <cell r="A23">
-            <v>107</v>
+            <v>106</v>
           </cell>
           <cell r="B23" t="str">
-            <v>ビヤーキー</v>
+            <v>アイホート</v>
           </cell>
         </row>
         <row r="24">
           <cell r="A24">
-            <v>201</v>
+            <v>107</v>
           </cell>
           <cell r="B24" t="str">
-            <v>アンリマユ</v>
+            <v>ビヤーキー</v>
           </cell>
         </row>
         <row r="25">
           <cell r="A25">
-            <v>202</v>
+            <v>201</v>
           </cell>
           <cell r="B25" t="str">
-            <v>ザガン</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="26">
           <cell r="A26">
-            <v>203</v>
+            <v>202</v>
           </cell>
           <cell r="B26" t="str">
-            <v>アスタロト</v>
+            <v>ザガン</v>
           </cell>
         </row>
         <row r="27">
           <cell r="A27">
-            <v>204</v>
+            <v>203</v>
           </cell>
           <cell r="B27" t="str">
-            <v>デカラビア</v>
+            <v>アスタロト</v>
           </cell>
         </row>
         <row r="28">
           <cell r="A28">
-            <v>205</v>
+            <v>204</v>
           </cell>
           <cell r="B28" t="str">
-            <v>インドラ</v>
+            <v>デカラビア</v>
           </cell>
         </row>
         <row r="29">
           <cell r="A29">
-            <v>206</v>
+            <v>205</v>
           </cell>
           <cell r="B29" t="str">
-            <v>ズルワーン</v>
+            <v>インドラ</v>
           </cell>
         </row>
         <row r="30">
           <cell r="A30">
-            <v>207</v>
+            <v>206</v>
           </cell>
           <cell r="B30" t="str">
-            <v>アンリマユ</v>
+            <v>ズルワーン</v>
           </cell>
         </row>
         <row r="31">
           <cell r="A31">
-            <v>301</v>
+            <v>207</v>
           </cell>
           <cell r="B31" t="str">
-            <v>デビルドラゴン</v>
+            <v>アンリマユ</v>
           </cell>
         </row>
         <row r="32">
           <cell r="A32">
-            <v>1001</v>
+            <v>301</v>
           </cell>
           <cell r="B32" t="str">
-            <v>ミカ</v>
+            <v>デビルドラゴン</v>
           </cell>
         </row>
         <row r="33">
           <cell r="A33">
-            <v>1002</v>
+            <v>1001</v>
           </cell>
           <cell r="B33" t="str">
-            <v>エリザベート</v>
+            <v>ミカ</v>
           </cell>
         </row>
         <row r="34">
           <cell r="A34">
-            <v>1003</v>
+            <v>1002</v>
           </cell>
           <cell r="B34" t="str">
-            <v>アリエス</v>
+            <v>エリザベート</v>
           </cell>
         </row>
         <row r="35">
           <cell r="A35">
-            <v>1004</v>
+            <v>1003</v>
           </cell>
           <cell r="B35" t="str">
-            <v>シイナ</v>
+            <v>アリエス</v>
           </cell>
         </row>
         <row r="36">
           <cell r="A36">
-            <v>1005</v>
+            <v>1004</v>
           </cell>
           <cell r="B36" t="str">
-            <v>レダ</v>
+            <v>シイナ</v>
           </cell>
         </row>
         <row r="37">
           <cell r="A37">
-            <v>1006</v>
+            <v>1005</v>
           </cell>
           <cell r="B37" t="str">
-            <v>リシェリ</v>
+            <v>レダ</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38">
-            <v>1007</v>
+            <v>1006</v>
           </cell>
           <cell r="B38" t="str">
-            <v>ユニ</v>
+            <v>リシェリ</v>
           </cell>
         </row>
         <row r="39">
           <cell r="A39">
-            <v>1008</v>
+            <v>1007</v>
           </cell>
           <cell r="B39" t="str">
-            <v>マリーベル</v>
+            <v>ユニ</v>
           </cell>
         </row>
         <row r="40">
           <cell r="A40">
-            <v>1009</v>
+            <v>1008</v>
           </cell>
           <cell r="B40" t="str">
-            <v>ナツキ</v>
+            <v>マリーベル</v>
           </cell>
         </row>
         <row r="41">
           <cell r="A41">
-            <v>1010</v>
+            <v>1009</v>
           </cell>
           <cell r="B41" t="str">
-            <v>メリアドール</v>
+            <v>ナツキ</v>
           </cell>
         </row>
         <row r="42">
           <cell r="A42">
+            <v>1010</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>メリアドール</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
             <v>1011</v>
           </cell>
-          <cell r="B42" t="str">
+          <cell r="B43" t="str">
             <v>セリナ</v>
           </cell>
         </row>
@@ -1340,7 +1348,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1679,17 +1687,17 @@
         <v>2010</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>オーガ</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1706,11 +1714,11 @@
         <v>2010</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="D14" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C14,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>オーガ</v>
       </c>
       <c r="E14">
         <v>11</v>
@@ -1733,17 +1741,17 @@
         <v>2010</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>オーガ</v>
       </c>
       <c r="E15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1754,23 +1762,23 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="B16">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="C16">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D16" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C16,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>サーチャー</v>
       </c>
       <c r="E16">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1781,20 +1789,20 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="B17">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="C17">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="D17" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C17,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>クロウ</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1808,20 +1816,20 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>3020</v>
+        <v>2020</v>
       </c>
       <c r="B18">
-        <v>3020</v>
+        <v>2020</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C18,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1835,23 +1843,23 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B19">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="C19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1862,20 +1870,20 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B20">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ベリト</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1889,10 +1897,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B21">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -1905,7 +1913,7 @@
         <v>15</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1916,23 +1924,23 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B22">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ソード</v>
       </c>
       <c r="E22">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1943,23 +1951,23 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B23">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="C23">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E23">
         <v>15</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1970,17 +1978,17 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B24">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="C24">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>カースド</v>
       </c>
       <c r="E24">
         <v>15</v>
@@ -1997,10 +2005,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B25">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="C25">
         <v>12</v>
@@ -2024,10 +2032,10 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B26">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="C26">
         <v>14</v>
@@ -2051,23 +2059,23 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>4010</v>
+        <v>3040</v>
       </c>
       <c r="B27">
-        <v>4010</v>
+        <v>3040</v>
       </c>
       <c r="C27">
-        <v>104</v>
+        <v>15</v>
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>ソード</v>
       </c>
       <c r="E27">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -2078,23 +2086,23 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>5010</v>
+        <v>3040</v>
       </c>
       <c r="B28">
-        <v>5010</v>
+        <v>3040</v>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>クリーパー</v>
       </c>
       <c r="E28">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -2105,23 +2113,23 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>5010</v>
+        <v>3040</v>
       </c>
       <c r="B29">
-        <v>5010</v>
+        <v>3040</v>
       </c>
       <c r="C29">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E29">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -2132,20 +2140,20 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="B30">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>アンドラス</v>
       </c>
       <c r="E30">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2159,17 +2167,17 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>6010</v>
+        <v>5010</v>
       </c>
       <c r="B31">
-        <v>6010</v>
+        <v>5010</v>
       </c>
       <c r="C31">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>シールド</v>
       </c>
       <c r="E31">
         <v>25</v>
@@ -2186,17 +2194,17 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>6010</v>
+        <v>5010</v>
       </c>
       <c r="B32">
-        <v>6010</v>
+        <v>5010</v>
       </c>
       <c r="C32">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E32">
         <v>30</v>
@@ -2213,17 +2221,17 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>6010</v>
+        <v>5010</v>
       </c>
       <c r="B33">
-        <v>6010</v>
+        <v>5010</v>
       </c>
       <c r="C33">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>シールド</v>
       </c>
       <c r="E33">
         <v>25</v>
@@ -2240,23 +2248,23 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>20010</v>
+        <v>6010</v>
       </c>
       <c r="B34">
-        <v>20010</v>
+        <v>6010</v>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ソード</v>
       </c>
       <c r="E34">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -2267,20 +2275,20 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>20010</v>
+        <v>6010</v>
       </c>
       <c r="B35">
-        <v>20010</v>
+        <v>6010</v>
       </c>
       <c r="C35">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>アンリマユ</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -2294,23 +2302,23 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>20020</v>
+        <v>6010</v>
       </c>
       <c r="B36">
-        <v>20020</v>
+        <v>6010</v>
       </c>
       <c r="C36">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ソード</v>
       </c>
       <c r="E36">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -2321,23 +2329,23 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B37">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="C37">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="D37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>ウルフ</v>
       </c>
       <c r="E37">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -2348,28 +2356,136 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B38">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
+        <v>アモン</v>
+      </c>
+      <c r="E38">
+        <v>15</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39">
+        <v>20010</v>
+      </c>
+      <c r="B39">
+        <v>20010</v>
+      </c>
+      <c r="C39">
+        <v>4</v>
+      </c>
+      <c r="D39" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C39,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+      <c r="E39">
+        <v>12</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40">
+        <v>20020</v>
+      </c>
+      <c r="B40">
+        <v>20020</v>
+      </c>
+      <c r="C40">
+        <v>13</v>
+      </c>
+      <c r="D40" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+      <c r="E40">
+        <v>20</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41">
+        <v>20020</v>
+      </c>
+      <c r="B41">
+        <v>20020</v>
+      </c>
+      <c r="C41">
+        <v>103</v>
+      </c>
+      <c r="D41" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
+        <v>パイモン</v>
+      </c>
+      <c r="E41">
+        <v>25</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42">
+        <v>20020</v>
+      </c>
+      <c r="B42">
+        <v>20020</v>
+      </c>
+      <c r="C42">
+        <v>6</v>
+      </c>
+      <c r="D42" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
         <v>ネームレス</v>
       </c>
-      <c r="E38">
+      <c r="E42">
         <v>20</v>
       </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7960"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,8 +48,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -57,6 +57,22 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -70,7 +86,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -78,20 +102,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -105,9 +115,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -135,14 +167,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -151,15 +175,8 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -174,6 +191,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -181,30 +205,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -221,181 +221,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,6 +406,26 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -439,6 +459,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -467,42 +502,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,7 +514,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -523,7 +523,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -532,127 +532,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1613,7 +1613,7 @@
         <v>ビー</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1640,7 +1640,7 @@
         <v>ビー</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1667,7 +1667,7 @@
         <v>ビー</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -49,8 +49,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -63,15 +63,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -79,7 +71,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -93,17 +99,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -115,31 +114,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -154,7 +131,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -177,6 +154,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -184,7 +169,23 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -198,9 +199,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,187 +215,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,17 +413,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -474,6 +463,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -491,9 +489,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,7 +514,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -535,124 +535,124 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7960"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Troops" sheetId="1" r:id="rId1"/>
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -62,25 +62,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -91,8 +84,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -106,9 +100,77 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -123,38 +185,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -168,43 +199,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,25 +215,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,36 +341,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -287,115 +353,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,22 +413,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -444,30 +429,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -502,7 +463,46 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -672,12 +672,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1081,6 +1081,22 @@
           </cell>
           <cell r="B43" t="str">
             <v>セリナ</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>1101</v>
+          </cell>
+          <cell r="B44" t="str">
+            <v>シグルド</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>1102</v>
+          </cell>
+          <cell r="B45" t="str">
+            <v>ブリュンヒルデ</v>
           </cell>
         </row>
       </sheetData>
@@ -1694,7 +1710,7 @@
         <v>オーガ</v>
       </c>
       <c r="E13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1748,7 +1764,7 @@
         <v>オーガ</v>
       </c>
       <c r="E15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -63,7 +63,90 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -77,8 +160,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -101,38 +193,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -144,67 +205,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,25 +215,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,37 +371,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,7 +383,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -299,103 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,15 +406,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -433,17 +424,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -468,17 +468,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -498,11 +492,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1629,7 +1629,7 @@
         <v>ビー</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1656,7 +1656,7 @@
         <v>ビー</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1683,7 +1683,7 @@
         <v>ビー</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1737,7 +1737,7 @@
         <v>オーガ</v>
       </c>
       <c r="E14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F14">
         <v>1</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -62,15 +62,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -83,17 +84,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -106,31 +98,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -160,17 +130,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -185,15 +168,24 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -205,6 +197,14 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -221,181 +221,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,15 +424,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -450,17 +441,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
@@ -471,8 +451,32 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -492,17 +496,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,7 +514,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -523,13 +523,13 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -538,121 +538,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1629,7 +1629,7 @@
         <v>ビー</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1656,7 +1656,7 @@
         <v>ビー</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1683,7 +1683,7 @@
         <v>ビー</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -62,23 +62,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -92,25 +77,24 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -131,29 +115,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -161,7 +130,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -177,15 +146,46 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -200,7 +200,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,13 +215,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,25 +293,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,139 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,6 +420,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -448,11 +468,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -480,32 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1364,7 +1364,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1554,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1581,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1743,7 +1743,7 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1824,7 +1824,7 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1905,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1959,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1986,7 +1986,7 @@
         <v>1</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2121,7 +2121,7 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2229,7 +2229,7 @@
         <v>1</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -2256,7 +2256,7 @@
         <v>1</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -2310,7 +2310,7 @@
         <v>1</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -2337,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -2378,20 +2378,20 @@
         <v>20010</v>
       </c>
       <c r="C38">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>ウルフ</v>
       </c>
       <c r="E38">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -2426,26 +2426,26 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B40">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="C40">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>アモン</v>
       </c>
       <c r="E40">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2459,17 +2459,17 @@
         <v>20020</v>
       </c>
       <c r="C41">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>インプ</v>
       </c>
       <c r="E41">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -2486,22 +2486,49 @@
         <v>20020</v>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
+        <v>パイモン</v>
+      </c>
+      <c r="E42">
+        <v>25</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43">
+        <v>20020</v>
+      </c>
+      <c r="B43">
+        <v>20020</v>
+      </c>
+      <c r="C43">
+        <v>6</v>
+      </c>
+      <c r="D43" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C43,[1]TextData!A:A))</f>
         <v>ネームレス</v>
       </c>
-      <c r="E42">
+      <c r="E43">
         <v>20</v>
       </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+      <c r="H43">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -49,9 +49,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -63,7 +63,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -77,14 +100,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -92,30 +107,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -130,23 +122,45 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -168,39 +182,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,43 +215,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,139 +389,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,6 +406,36 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -420,6 +450,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -444,41 +489,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -491,21 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2378,17 +2378,17 @@
         <v>20010</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>アモン</v>
       </c>
       <c r="E38">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2432,17 +2432,17 @@
         <v>20010</v>
       </c>
       <c r="C40">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>インプ</v>
       </c>
       <c r="E40">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40">
         <v>4</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -62,8 +62,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -71,43 +80,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -122,15 +94,37 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -151,14 +145,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -166,9 +152,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -191,7 +177,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -200,7 +186,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,31 +215,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,49 +377,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -305,97 +389,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,36 +406,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -489,11 +459,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -936,7 +936,7 @@
             <v>201</v>
           </cell>
           <cell r="B25" t="str">
-            <v>アンリマユ</v>
+            <v>ファフニール</v>
           </cell>
         </row>
         <row r="26">
@@ -1364,7 +1364,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -2270,11 +2270,11 @@
         <v>6010</v>
       </c>
       <c r="C34">
-        <v>15</v>
+        <v>201</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ファフニール</v>
       </c>
       <c r="E34">
         <v>25</v>
@@ -2283,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2291,26 +2291,26 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>6010</v>
+        <v>20010</v>
       </c>
       <c r="B35">
-        <v>6010</v>
+        <v>20010</v>
       </c>
       <c r="C35">
-        <v>201</v>
+        <v>4</v>
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>ウルフ</v>
       </c>
       <c r="E35">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -2318,26 +2318,26 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>6010</v>
+        <v>20010</v>
       </c>
       <c r="B36">
-        <v>6010</v>
+        <v>20010</v>
       </c>
       <c r="C36">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="D36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>アモン</v>
       </c>
       <c r="E36">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -2378,20 +2378,20 @@
         <v>20010</v>
       </c>
       <c r="C38">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>インプ</v>
       </c>
       <c r="E38">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -2399,26 +2399,26 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>20010</v>
+        <v>20020</v>
       </c>
       <c r="B39">
-        <v>20010</v>
+        <v>20020</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C39,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>インプ</v>
       </c>
       <c r="E39">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -2426,26 +2426,26 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>20010</v>
+        <v>20020</v>
       </c>
       <c r="B40">
-        <v>20010</v>
+        <v>20020</v>
       </c>
       <c r="C40">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>パイモン</v>
       </c>
       <c r="E40">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2459,11 +2459,11 @@
         <v>20020</v>
       </c>
       <c r="C41">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ネームレス</v>
       </c>
       <c r="E41">
         <v>20</v>
@@ -2472,63 +2472,9 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42">
-        <v>20020</v>
-      </c>
-      <c r="B42">
-        <v>20020</v>
-      </c>
-      <c r="C42">
-        <v>103</v>
-      </c>
-      <c r="D42" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>パイモン</v>
-      </c>
-      <c r="E42">
-        <v>25</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43">
-        <v>20020</v>
-      </c>
-      <c r="B43">
-        <v>20020</v>
-      </c>
-      <c r="C43">
-        <v>6</v>
-      </c>
-      <c r="D43" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(C43,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
-      </c>
-      <c r="E43">
-        <v>20</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>2</v>
-      </c>
-      <c r="H43">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -62,47 +62,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -117,23 +86,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -145,16 +100,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -162,14 +110,6 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -193,7 +133,52 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -205,6 +190,21 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,43 +215,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,139 +383,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,6 +406,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -424,6 +433,32 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -435,26 +470,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -478,22 +493,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -501,8 +501,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1622,14 +1622,14 @@
         <v>1020</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C10,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1656,7 +1656,7 @@
         <v>ビー</v>
       </c>
       <c r="E11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1676,14 +1676,14 @@
         <v>1020</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C12,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>0</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -49,9 +49,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -62,16 +62,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -79,6 +79,28 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -92,17 +114,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -117,7 +160,30 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -132,65 +198,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -198,13 +205,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,13 +215,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,13 +323,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,19 +347,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -275,19 +371,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -299,103 +389,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,15 +406,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -433,6 +424,39 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -440,6 +464,21 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -459,36 +498,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -497,15 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1703,11 +1703,11 @@
         <v>2010</v>
       </c>
       <c r="C13">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>オーガ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -1757,11 +1757,11 @@
         <v>2010</v>
       </c>
       <c r="C15">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>オーガ</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E15">
         <v>10</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -71,7 +71,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -85,7 +92,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -106,23 +113,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -136,6 +128,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -152,31 +153,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -200,7 +178,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -221,19 +221,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,157 +377,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,15 +442,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -459,10 +450,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -506,6 +495,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,7 +514,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -523,13 +523,13 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -538,121 +538,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFm